--- a/linked_data.xlsx
+++ b/linked_data.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,856 +413,1101 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FN28"/>
+  <dimension ref="A1:HK28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>profile_id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>profile_found</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>school</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>class</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>section</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>horiba</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>submitted_at</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>response_id</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>age</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>age_calculated_at</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
         <is>
           <t>age_completed</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>age_full</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
         <is>
           <t>anemia_status</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>birth_order</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>capillary_attempts</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>capillary_hb_value</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>caste_category</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>child_classification</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>child_id_code</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>child_response_score</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>chronic_illness</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>chronic_illness_history</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>chronic_illness_specify</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>comfortable_testing_process</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>device_sequence</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>deworming_history</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>deworming_tablet</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>diet_type</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>district</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>dob</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>edu_head_family</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>edu_head_level</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>edu_score</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>extra_54</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>extra_55</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>family_income_level</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>family_members_count</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>family_members_total</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>family_type</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>freq_dates</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>freq_eggs</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>freq_fruits</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>freq_green_leafy</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>freq_jaggery</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>freq_meat</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>gender</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>hb_measurement_datetime</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>height_cm</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>height_cms</t>
+        </is>
+      </c>
+      <c r="AY1" t="inlineStr">
         <is>
           <t>hemocue</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>ifa_dose</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>income_score</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>investigator_entry_note</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <t>investigator_name</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BD1" t="inlineStr">
         <is>
           <t>investigator_signature</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BE1" t="inlineStr">
         <is>
           <t>investigator_username</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BF1" t="inlineStr">
         <is>
           <t>iron_rich_food_frequency</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BG1" t="inlineStr">
         <is>
           <t>iron_supplementation</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BH1" t="inlineStr">
         <is>
           <t>iron_supplementation_current</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BI1" t="inlineStr">
         <is>
           <t>kupp_total_score</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BJ1" t="inlineStr">
         <is>
           <t>kuppuswamy_total_score</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BK1" t="inlineStr">
         <is>
           <t>lab_attempts</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BL1" t="inlineStr">
         <is>
           <t>lab_calibration</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BM1" t="inlineStr">
         <is>
           <t>lab_ease</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BN1" t="inlineStr">
         <is>
           <t>lab_end_time</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BO1" t="inlineStr">
+        <is>
+          <t>lab_feas_60_a</t>
+        </is>
+      </c>
+      <c r="BP1" t="inlineStr">
+        <is>
+          <t>lab_feas_63_c</t>
+        </is>
+      </c>
+      <c r="BQ1" t="inlineStr">
         <is>
           <t>lab_flacc_activity</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BR1" t="inlineStr">
         <is>
           <t>lab_flacc_consolability</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BS1" t="inlineStr">
         <is>
           <t>lab_flacc_cry</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BT1" t="inlineStr">
         <is>
           <t>lab_flacc_face</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BU1" t="inlineStr">
         <is>
           <t>lab_flacc_legs</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BV1" t="inlineStr">
         <is>
           <t>lab_flacc_total</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="BW1" t="inlineStr">
         <is>
           <t>lab_hb_value</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="BX1" t="inlineStr">
         <is>
           <t>lab_maintenance</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="BY1" t="inlineStr">
+        <is>
+          <t>lab_overall_feas</t>
+        </is>
+      </c>
+      <c r="BZ1" t="inlineStr">
         <is>
           <t>lab_portability</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="CA1" t="inlineStr">
         <is>
           <t>lab_practicality</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="CB1" t="inlineStr">
         <is>
           <t>lab_recording</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="CC1" t="inlineStr">
         <is>
           <t>lab_reliability</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="CD1" t="inlineStr">
         <is>
           <t>lab_safety</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="CE1" t="inlineStr">
         <is>
           <t>lab_start_time</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="CF1" t="inlineStr">
         <is>
           <t>lab_suitability</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CG1" t="inlineStr">
         <is>
           <t>lab_training</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CH1" t="inlineStr">
         <is>
           <t>linked_at</t>
         </is>
       </c>
-      <c r="CC1" s="1" t="inlineStr">
+      <c r="CI1" t="inlineStr">
         <is>
           <t>location</t>
         </is>
       </c>
-      <c r="CD1" s="1" t="inlineStr">
+      <c r="CJ1" t="inlineStr">
         <is>
           <t>location_type</t>
         </is>
       </c>
-      <c r="CE1" s="1" t="inlineStr">
+      <c r="CK1" t="inlineStr">
         <is>
           <t>low_birth_weight</t>
         </is>
       </c>
-      <c r="CF1" s="1" t="inlineStr">
+      <c r="CL1" t="inlineStr">
         <is>
           <t>low_birth_weight_history</t>
         </is>
       </c>
-      <c r="CG1" s="1" t="inlineStr">
+      <c r="CM1" t="inlineStr">
+        <is>
+          <t>m_feas_28_a</t>
+        </is>
+      </c>
+      <c r="CN1" t="inlineStr">
+        <is>
+          <t>m_feas_28_b</t>
+        </is>
+      </c>
+      <c r="CO1" t="inlineStr">
+        <is>
+          <t>m_feas_29_a</t>
+        </is>
+      </c>
+      <c r="CP1" t="inlineStr">
+        <is>
+          <t>m_feas_29_b</t>
+        </is>
+      </c>
+      <c r="CQ1" t="inlineStr">
+        <is>
+          <t>m_feas_30_a</t>
+        </is>
+      </c>
+      <c r="CR1" t="inlineStr">
+        <is>
+          <t>m_feas_30_b</t>
+        </is>
+      </c>
+      <c r="CS1" t="inlineStr">
+        <is>
+          <t>m_feas_31_a</t>
+        </is>
+      </c>
+      <c r="CT1" t="inlineStr">
+        <is>
+          <t>m_feas_31_b</t>
+        </is>
+      </c>
+      <c r="CU1" t="inlineStr">
+        <is>
+          <t>m_feas_31_c</t>
+        </is>
+      </c>
+      <c r="CV1" t="inlineStr">
+        <is>
+          <t>m_feas_32_a</t>
+        </is>
+      </c>
+      <c r="CW1" t="inlineStr">
+        <is>
+          <t>m_feas_32_b</t>
+        </is>
+      </c>
+      <c r="CX1" t="inlineStr">
+        <is>
+          <t>m_feas_33_a</t>
+        </is>
+      </c>
+      <c r="CY1" t="inlineStr">
+        <is>
+          <t>m_feas_33_b</t>
+        </is>
+      </c>
+      <c r="CZ1" t="inlineStr">
+        <is>
+          <t>m_feas_34_a</t>
+        </is>
+      </c>
+      <c r="DA1" t="inlineStr">
+        <is>
+          <t>m_feas_34_b</t>
+        </is>
+      </c>
+      <c r="DB1" t="inlineStr">
+        <is>
+          <t>m_feas_35_a</t>
+        </is>
+      </c>
+      <c r="DC1" t="inlineStr">
+        <is>
+          <t>m_feas_35_b</t>
+        </is>
+      </c>
+      <c r="DD1" t="inlineStr">
+        <is>
+          <t>m_feas_36_a</t>
+        </is>
+      </c>
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>m_feas_36_b</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>m_feas_37_a</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>m_feas_37_b</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>m_feas_37_c</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>m_feas_37_d</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>m_feas_38_a</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>m_feas_38_b</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
         <is>
           <t>masimo</t>
         </is>
       </c>
-      <c r="CH1" s="1" t="inlineStr">
+      <c r="DM1" t="inlineStr">
         <is>
           <t>masimo_avg_sphb</t>
         </is>
       </c>
-      <c r="CI1" s="1" t="inlineStr">
+      <c r="DN1" t="inlineStr">
         <is>
           <t>masimo_calibration</t>
         </is>
       </c>
-      <c r="CJ1" s="1" t="inlineStr">
+      <c r="DO1" t="inlineStr">
         <is>
           <t>masimo_ease</t>
         </is>
       </c>
-      <c r="CK1" s="1" t="inlineStr">
+      <c r="DP1" t="inlineStr">
         <is>
           <t>masimo_end_time</t>
         </is>
       </c>
-      <c r="CL1" s="1" t="inlineStr">
+      <c r="DQ1" t="inlineStr">
         <is>
           <t>masimo_feasibility_rating</t>
         </is>
       </c>
-      <c r="CM1" s="1" t="inlineStr">
+      <c r="DR1" t="inlineStr">
         <is>
           <t>masimo_flacc_activity</t>
         </is>
       </c>
-      <c r="CN1" s="1" t="inlineStr">
+      <c r="DS1" t="inlineStr">
         <is>
           <t>masimo_flacc_consolability</t>
         </is>
       </c>
-      <c r="CO1" s="1" t="inlineStr">
+      <c r="DT1" t="inlineStr">
         <is>
           <t>masimo_flacc_cry</t>
         </is>
       </c>
-      <c r="CP1" s="1" t="inlineStr">
+      <c r="DU1" t="inlineStr">
         <is>
           <t>masimo_flacc_face</t>
         </is>
       </c>
-      <c r="CQ1" s="1" t="inlineStr">
+      <c r="DV1" t="inlineStr">
         <is>
           <t>masimo_flacc_legs</t>
         </is>
       </c>
-      <c r="CR1" s="1" t="inlineStr">
+      <c r="DW1" t="inlineStr">
         <is>
           <t>masimo_flacc_total</t>
         </is>
       </c>
-      <c r="CS1" s="1" t="inlineStr">
+      <c r="DX1" t="inlineStr">
         <is>
           <t>masimo_maintenance</t>
         </is>
       </c>
-      <c r="CT1" s="1" t="inlineStr">
+      <c r="DY1" t="inlineStr">
         <is>
           <t>masimo_portability</t>
         </is>
       </c>
-      <c r="CU1" s="1" t="inlineStr">
+      <c r="DZ1" t="inlineStr">
         <is>
           <t>masimo_practicality</t>
         </is>
       </c>
-      <c r="CV1" s="1" t="inlineStr">
+      <c r="EA1" t="inlineStr">
         <is>
           <t>masimo_reading</t>
         </is>
       </c>
-      <c r="CW1" s="1" t="inlineStr">
+      <c r="EB1" t="inlineStr">
         <is>
           <t>masimo_reading_1</t>
         </is>
       </c>
-      <c r="CX1" s="1" t="inlineStr">
+      <c r="EC1" t="inlineStr">
         <is>
           <t>masimo_reading_2</t>
         </is>
       </c>
-      <c r="CY1" s="1" t="inlineStr">
+      <c r="ED1" t="inlineStr">
         <is>
           <t>masimo_reading_3</t>
         </is>
       </c>
-      <c r="CZ1" s="1" t="inlineStr">
+      <c r="EE1" t="inlineStr">
         <is>
           <t>masimo_recording</t>
         </is>
       </c>
-      <c r="DA1" s="1" t="inlineStr">
+      <c r="EF1" t="inlineStr">
         <is>
           <t>masimo_reliability</t>
         </is>
       </c>
-      <c r="DB1" s="1" t="inlineStr">
+      <c r="EG1" t="inlineStr">
         <is>
           <t>masimo_safety</t>
         </is>
       </c>
-      <c r="DC1" s="1" t="inlineStr">
+      <c r="EH1" t="inlineStr">
         <is>
           <t>masimo_start_time</t>
         </is>
       </c>
-      <c r="DD1" s="1" t="inlineStr">
+      <c r="EI1" t="inlineStr">
         <is>
           <t>masimo_suitability</t>
         </is>
       </c>
-      <c r="DE1" s="1" t="inlineStr">
+      <c r="EJ1" t="inlineStr">
         <is>
           <t>masimo_training</t>
         </is>
       </c>
-      <c r="DF1" s="1" t="inlineStr">
+      <c r="EK1" t="inlineStr">
         <is>
           <t>measurement_device_sequence</t>
         </is>
       </c>
-      <c r="DG1" s="1" t="inlineStr">
+      <c r="EL1" t="inlineStr">
         <is>
           <t>mobile_no</t>
         </is>
       </c>
-      <c r="DH1" s="1" t="inlineStr">
+      <c r="EM1" t="inlineStr">
         <is>
           <t>monthly_income</t>
         </is>
       </c>
-      <c r="DI1" s="1" t="inlineStr">
+      <c r="EN1" t="inlineStr">
         <is>
           <t>occ_head_level</t>
         </is>
       </c>
-      <c r="DJ1" s="1" t="inlineStr">
+      <c r="EO1" t="inlineStr">
         <is>
           <t>occupation_head_family</t>
         </is>
       </c>
-      <c r="DK1" s="1" t="inlineStr">
+      <c r="EP1" t="inlineStr">
         <is>
           <t>occupation_score</t>
         </is>
       </c>
-      <c r="DL1" s="1" t="inlineStr">
+      <c r="EQ1" t="inlineStr">
         <is>
           <t>parent_child_calm</t>
         </is>
       </c>
-      <c r="DM1" s="1" t="inlineStr">
+      <c r="ER1" t="inlineStr">
         <is>
           <t>parent_child_distress</t>
         </is>
       </c>
-      <c r="DN1" s="1" t="inlineStr">
+      <c r="ES1" t="inlineStr">
         <is>
           <t>parent_comfort</t>
         </is>
       </c>
-      <c r="DO1" s="1" t="inlineStr">
+      <c r="ET1" t="inlineStr">
+        <is>
+          <t>parent_q_73</t>
+        </is>
+      </c>
+      <c r="EU1" t="inlineStr">
+        <is>
+          <t>parent_q_74</t>
+        </is>
+      </c>
+      <c r="EV1" t="inlineStr">
+        <is>
+          <t>parent_q_75</t>
+        </is>
+      </c>
+      <c r="EW1" t="inlineStr">
+        <is>
+          <t>parent_q_76</t>
+        </is>
+      </c>
+      <c r="EX1" t="inlineStr">
+        <is>
+          <t>parent_q_77</t>
+        </is>
+      </c>
+      <c r="EY1" t="inlineStr">
+        <is>
+          <t>parent_q_78</t>
+        </is>
+      </c>
+      <c r="EZ1" t="inlineStr">
+        <is>
+          <t>parent_q_79</t>
+        </is>
+      </c>
+      <c r="FA1" t="inlineStr">
+        <is>
+          <t>parent_q_80</t>
+        </is>
+      </c>
+      <c r="FB1" t="inlineStr">
+        <is>
+          <t>parent_q_81</t>
+        </is>
+      </c>
+      <c r="FC1" t="inlineStr">
         <is>
           <t>parent_test_safety</t>
         </is>
       </c>
-      <c r="DP1" s="1" t="inlineStr">
+      <c r="FD1" t="inlineStr">
         <is>
           <t>parent_total</t>
         </is>
       </c>
-      <c r="DQ1" s="1" t="inlineStr">
+      <c r="FE1" t="inlineStr">
         <is>
           <t>parent_trust_result</t>
         </is>
       </c>
-      <c r="DR1" s="1" t="inlineStr">
+      <c r="FF1" t="inlineStr">
         <is>
           <t>participant_name</t>
         </is>
       </c>
-      <c r="DS1" s="1" t="inlineStr">
+      <c r="FG1" t="inlineStr">
         <is>
           <t>poc_attempts</t>
         </is>
       </c>
-      <c r="DT1" s="1" t="inlineStr">
+      <c r="FH1" t="inlineStr">
         <is>
           <t>poc_calibration</t>
         </is>
       </c>
-      <c r="DU1" s="1" t="inlineStr">
+      <c r="FI1" t="inlineStr">
         <is>
           <t>poc_ease</t>
         </is>
       </c>
-      <c r="DV1" s="1" t="inlineStr">
+      <c r="FJ1" t="inlineStr">
         <is>
           <t>poc_end_time</t>
         </is>
       </c>
-      <c r="DW1" s="1" t="inlineStr">
+      <c r="FK1" t="inlineStr">
+        <is>
+          <t>poc_feas_44_a</t>
+        </is>
+      </c>
+      <c r="FL1" t="inlineStr">
+        <is>
+          <t>poc_feas_47_c</t>
+        </is>
+      </c>
+      <c r="FM1" t="inlineStr">
         <is>
           <t>poc_feasibility_rating</t>
         </is>
       </c>
-      <c r="DX1" s="1" t="inlineStr">
+      <c r="FN1" t="inlineStr">
         <is>
           <t>poc_flacc_activity</t>
         </is>
       </c>
-      <c r="DY1" s="1" t="inlineStr">
+      <c r="FO1" t="inlineStr">
         <is>
           <t>poc_flacc_consolability</t>
         </is>
       </c>
-      <c r="DZ1" s="1" t="inlineStr">
+      <c r="FP1" t="inlineStr">
         <is>
           <t>poc_flacc_cry</t>
         </is>
       </c>
-      <c r="EA1" s="1" t="inlineStr">
+      <c r="FQ1" t="inlineStr">
         <is>
           <t>poc_flacc_face</t>
         </is>
       </c>
-      <c r="EB1" s="1" t="inlineStr">
+      <c r="FR1" t="inlineStr">
         <is>
           <t>poc_flacc_legs</t>
         </is>
       </c>
-      <c r="EC1" s="1" t="inlineStr">
+      <c r="FS1" t="inlineStr">
         <is>
           <t>poc_flacc_total</t>
         </is>
       </c>
-      <c r="ED1" s="1" t="inlineStr">
+      <c r="FT1" t="inlineStr">
         <is>
           <t>poc_hb_value</t>
         </is>
       </c>
-      <c r="EE1" s="1" t="inlineStr">
+      <c r="FU1" t="inlineStr">
         <is>
           <t>poc_maintenance</t>
         </is>
       </c>
-      <c r="EF1" s="1" t="inlineStr">
+      <c r="FV1" t="inlineStr">
+        <is>
+          <t>poc_overall_feas</t>
+        </is>
+      </c>
+      <c r="FW1" t="inlineStr">
         <is>
           <t>poc_portability</t>
         </is>
       </c>
-      <c r="EG1" s="1" t="inlineStr">
+      <c r="FX1" t="inlineStr">
         <is>
           <t>poc_practicality</t>
         </is>
       </c>
-      <c r="EH1" s="1" t="inlineStr">
+      <c r="FY1" t="inlineStr">
         <is>
           <t>poc_recording</t>
         </is>
       </c>
-      <c r="EI1" s="1" t="inlineStr">
+      <c r="FZ1" t="inlineStr">
         <is>
           <t>poc_reliability</t>
         </is>
       </c>
-      <c r="EJ1" s="1" t="inlineStr">
+      <c r="GA1" t="inlineStr">
         <is>
           <t>poc_safety</t>
         </is>
       </c>
-      <c r="EK1" s="1" t="inlineStr">
+      <c r="GB1" t="inlineStr">
         <is>
           <t>poc_start_time</t>
         </is>
       </c>
-      <c r="EL1" s="1" t="inlineStr">
+      <c r="GC1" t="inlineStr">
         <is>
           <t>poc_suitability</t>
         </is>
       </c>
-      <c r="EM1" s="1" t="inlineStr">
+      <c r="GD1" t="inlineStr">
         <is>
           <t>poc_training</t>
         </is>
       </c>
-      <c r="EN1" s="1" t="inlineStr">
+      <c r="GE1" t="inlineStr">
         <is>
           <t>preferred_method</t>
         </is>
       </c>
-      <c r="EO1" s="1" t="inlineStr">
+      <c r="GF1" t="inlineStr">
+        <is>
+          <t>prev_hb_device_other</t>
+        </is>
+      </c>
+      <c r="GG1" t="inlineStr">
+        <is>
+          <t>prev_hb_result</t>
+        </is>
+      </c>
+      <c r="GH1" t="inlineStr">
         <is>
           <t>previous_hb_device</t>
         </is>
       </c>
-      <c r="EP1" s="1" t="inlineStr">
+      <c r="GI1" t="inlineStr">
         <is>
           <t>previous_hb_device_other</t>
         </is>
       </c>
-      <c r="EQ1" s="1" t="inlineStr">
+      <c r="GJ1" t="inlineStr">
         <is>
           <t>previous_hb_result</t>
         </is>
       </c>
-      <c r="ER1" s="1" t="inlineStr">
+      <c r="GK1" t="inlineStr">
         <is>
           <t>previous_hb_tested</t>
         </is>
       </c>
-      <c r="ES1" s="1" t="inlineStr">
+      <c r="GL1" t="inlineStr">
         <is>
           <t>profile_id_code</t>
         </is>
       </c>
-      <c r="ET1" s="1" t="inlineStr">
+      <c r="GM1" t="inlineStr">
         <is>
           <t>profile_id_display</t>
         </is>
       </c>
-      <c r="EU1" s="1" t="inlineStr">
+      <c r="GN1" t="inlineStr">
         <is>
           <t>referral_advised</t>
         </is>
       </c>
-      <c r="EV1" s="1" t="inlineStr">
+      <c r="GO1" t="inlineStr">
         <is>
           <t>referral_date</t>
         </is>
       </c>
-      <c r="EW1" s="1" t="inlineStr">
+      <c r="GP1" t="inlineStr">
         <is>
           <t>referral_destination</t>
         </is>
       </c>
-      <c r="EX1" s="1" t="inlineStr">
+      <c r="GQ1" t="inlineStr">
+        <is>
+          <t>referral_other</t>
+        </is>
+      </c>
+      <c r="GR1" t="inlineStr">
         <is>
           <t>referral_other_specify</t>
         </is>
       </c>
-      <c r="EY1" s="1" t="inlineStr">
+      <c r="GS1" t="inlineStr">
         <is>
           <t>religion</t>
         </is>
       </c>
-      <c r="EZ1" s="1" t="inlineStr">
+      <c r="GT1" t="inlineStr">
+        <is>
+          <t>religion_other</t>
+        </is>
+      </c>
+      <c r="GU1" t="inlineStr">
         <is>
           <t>repeat_screening</t>
         </is>
       </c>
-      <c r="FA1" s="1" t="inlineStr">
+      <c r="GV1" t="inlineStr">
         <is>
           <t>school_anganwadi</t>
         </is>
       </c>
-      <c r="FB1" s="1" t="inlineStr">
+      <c r="GW1" t="inlineStr">
         <is>
           <t>school_anganwadi_name</t>
         </is>
       </c>
-      <c r="FC1" s="1" t="inlineStr">
+      <c r="GX1" t="inlineStr">
         <is>
           <t>ses_class</t>
         </is>
       </c>
-      <c r="FD1" s="1" t="inlineStr">
+      <c r="GY1" t="inlineStr">
         <is>
           <t>ses_class_label</t>
         </is>
       </c>
-      <c r="FE1" s="1" t="inlineStr">
+      <c r="GZ1" t="inlineStr">
         <is>
           <t>sex</t>
         </is>
       </c>
-      <c r="FF1" s="1" t="inlineStr">
+      <c r="HA1" t="inlineStr">
         <is>
           <t>siblings_count</t>
         </is>
       </c>
-      <c r="FG1" s="1" t="inlineStr">
+      <c r="HB1" t="inlineStr">
         <is>
           <t>social_category</t>
         </is>
       </c>
-      <c r="FH1" s="1" t="inlineStr">
+      <c r="HC1" t="inlineStr">
         <is>
           <t>state</t>
         </is>
       </c>
-      <c r="FI1" s="1" t="inlineStr">
+      <c r="HD1" t="inlineStr">
         <is>
           <t>study_date</t>
         </is>
       </c>
-      <c r="FJ1" s="1" t="inlineStr">
+      <c r="HE1" t="inlineStr">
+        <is>
+          <t>study_datetime</t>
+        </is>
+      </c>
+      <c r="HF1" t="inlineStr">
         <is>
           <t>study_id</t>
         </is>
       </c>
-      <c r="FK1" s="1" t="inlineStr">
+      <c r="HG1" t="inlineStr">
         <is>
           <t>venous_hb_value</t>
         </is>
       </c>
-      <c r="FL1" s="1" t="inlineStr">
+      <c r="HH1" t="inlineStr">
         <is>
           <t>weight_kg</t>
         </is>
       </c>
-      <c r="FM1" s="1" t="inlineStr">
+      <c r="HI1" t="inlineStr">
+        <is>
+          <t>weight_kgs</t>
+        </is>
+      </c>
+      <c r="HJ1" t="inlineStr">
         <is>
           <t>worm_infestation</t>
         </is>
       </c>
-      <c r="FN1" s="1" t="inlineStr">
+      <c r="HK1" t="inlineStr">
         <is>
           <t>worm_infestation_history</t>
         </is>
@@ -1357,19 +1590,19 @@
       <c r="AP2" t="inlineStr"/>
       <c r="AQ2" t="inlineStr"/>
       <c r="AR2" t="inlineStr"/>
-      <c r="AS2" t="inlineStr">
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
       </c>
-      <c r="AT2" t="inlineStr"/>
-      <c r="AU2" t="inlineStr"/>
-      <c r="AV2" t="n">
-        <v>12.4</v>
-      </c>
+      <c r="AV2" t="inlineStr"/>
       <c r="AW2" t="inlineStr"/>
       <c r="AX2" t="inlineStr"/>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY2" t="n">
+        <v>12.4</v>
+      </c>
       <c r="AZ2" t="inlineStr"/>
       <c r="BA2" t="inlineStr"/>
       <c r="BB2" t="inlineStr"/>
@@ -1403,9 +1636,7 @@
       <c r="CD2" t="inlineStr"/>
       <c r="CE2" t="inlineStr"/>
       <c r="CF2" t="inlineStr"/>
-      <c r="CG2" t="n">
-        <v>12.8</v>
-      </c>
+      <c r="CG2" t="inlineStr"/>
       <c r="CH2" t="inlineStr"/>
       <c r="CI2" t="inlineStr"/>
       <c r="CJ2" t="inlineStr"/>
@@ -1436,7 +1667,9 @@
       <c r="DI2" t="inlineStr"/>
       <c r="DJ2" t="inlineStr"/>
       <c r="DK2" t="inlineStr"/>
-      <c r="DL2" t="inlineStr"/>
+      <c r="DL2" t="n">
+        <v>12.8</v>
+      </c>
       <c r="DM2" t="inlineStr"/>
       <c r="DN2" t="inlineStr"/>
       <c r="DO2" t="inlineStr"/>
@@ -1491,6 +1724,55 @@
       <c r="FL2" t="inlineStr"/>
       <c r="FM2" t="inlineStr"/>
       <c r="FN2" t="inlineStr"/>
+      <c r="FO2" t="inlineStr"/>
+      <c r="FP2" t="inlineStr"/>
+      <c r="FQ2" t="inlineStr"/>
+      <c r="FR2" t="inlineStr"/>
+      <c r="FS2" t="inlineStr"/>
+      <c r="FT2" t="inlineStr"/>
+      <c r="FU2" t="inlineStr"/>
+      <c r="FV2" t="inlineStr"/>
+      <c r="FW2" t="inlineStr"/>
+      <c r="FX2" t="inlineStr"/>
+      <c r="FY2" t="inlineStr"/>
+      <c r="FZ2" t="inlineStr"/>
+      <c r="GA2" t="inlineStr"/>
+      <c r="GB2" t="inlineStr"/>
+      <c r="GC2" t="inlineStr"/>
+      <c r="GD2" t="inlineStr"/>
+      <c r="GE2" t="inlineStr"/>
+      <c r="GF2" t="inlineStr"/>
+      <c r="GG2" t="inlineStr"/>
+      <c r="GH2" t="inlineStr"/>
+      <c r="GI2" t="inlineStr"/>
+      <c r="GJ2" t="inlineStr"/>
+      <c r="GK2" t="inlineStr"/>
+      <c r="GL2" t="inlineStr"/>
+      <c r="GM2" t="inlineStr"/>
+      <c r="GN2" t="inlineStr"/>
+      <c r="GO2" t="inlineStr"/>
+      <c r="GP2" t="inlineStr"/>
+      <c r="GQ2" t="inlineStr"/>
+      <c r="GR2" t="inlineStr"/>
+      <c r="GS2" t="inlineStr"/>
+      <c r="GT2" t="inlineStr"/>
+      <c r="GU2" t="inlineStr"/>
+      <c r="GV2" t="inlineStr"/>
+      <c r="GW2" t="inlineStr"/>
+      <c r="GX2" t="inlineStr"/>
+      <c r="GY2" t="inlineStr"/>
+      <c r="GZ2" t="inlineStr"/>
+      <c r="HA2" t="inlineStr"/>
+      <c r="HB2" t="inlineStr"/>
+      <c r="HC2" t="inlineStr"/>
+      <c r="HD2" t="inlineStr"/>
+      <c r="HE2" t="inlineStr"/>
+      <c r="HF2" t="inlineStr"/>
+      <c r="HG2" t="inlineStr"/>
+      <c r="HH2" t="inlineStr"/>
+      <c r="HI2" t="inlineStr"/>
+      <c r="HJ2" t="inlineStr"/>
+      <c r="HK2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1535,22 +1817,22 @@
       <c r="J3" t="n">
         <v>2</v>
       </c>
-      <c r="K3" t="n">
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="n">
         <v>3</v>
       </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="n">
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="n">
         <v>2</v>
       </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr">
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr"/>
@@ -1560,66 +1842,66 @@
       <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr"/>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>hyderabad</t>
-        </is>
-      </c>
+      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
+          <t>hyderabad</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr"/>
+      <c r="AF3" t="inlineStr">
+        <is>
           <t>Profession / Honours (Score 7)</t>
         </is>
       </c>
-      <c r="AE3" t="inlineStr"/>
-      <c r="AF3" t="inlineStr"/>
-      <c r="AG3" t="inlineStr">
+      <c r="AG3" t="inlineStr"/>
+      <c r="AH3" t="inlineStr"/>
+      <c r="AI3" t="inlineStr">
         <is>
           <t>RACI0002</t>
         </is>
       </c>
-      <c r="AH3" t="inlineStr">
+      <c r="AJ3" t="inlineStr">
         <is>
           <t>2026-02-10 17:13:05</t>
         </is>
       </c>
-      <c r="AI3" t="inlineStr"/>
-      <c r="AJ3" t="inlineStr"/>
-      <c r="AK3" t="n">
+      <c r="AK3" t="inlineStr"/>
+      <c r="AL3" t="inlineStr"/>
+      <c r="AM3" t="n">
         <v>12</v>
       </c>
-      <c r="AL3" t="inlineStr">
+      <c r="AN3" t="inlineStr">
         <is>
           <t>Nuclear</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr"/>
-      <c r="AN3" t="inlineStr"/>
       <c r="AO3" t="inlineStr"/>
       <c r="AP3" t="inlineStr"/>
       <c r="AQ3" t="inlineStr"/>
       <c r="AR3" t="inlineStr"/>
-      <c r="AS3" t="inlineStr">
+      <c r="AS3" t="inlineStr"/>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AU3" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
       </c>
-      <c r="AT3" t="inlineStr"/>
-      <c r="AU3" t="inlineStr"/>
-      <c r="AV3" t="n">
-        <v>9.9</v>
-      </c>
+      <c r="AV3" t="inlineStr"/>
       <c r="AW3" t="inlineStr"/>
       <c r="AX3" t="inlineStr"/>
-      <c r="AY3" t="inlineStr"/>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>praneeth</t>
-        </is>
-      </c>
+      <c r="AY3" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="AZ3" t="inlineStr"/>
       <c r="BA3" t="inlineStr"/>
       <c r="BB3" t="inlineStr"/>
-      <c r="BC3" t="inlineStr"/>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>praneeth</t>
+        </is>
+      </c>
       <c r="BD3" t="inlineStr"/>
       <c r="BE3" t="inlineStr"/>
       <c r="BF3" t="inlineStr"/>
@@ -1645,19 +1927,17 @@
       <c r="BZ3" t="inlineStr"/>
       <c r="CA3" t="inlineStr"/>
       <c r="CB3" t="inlineStr"/>
-      <c r="CC3" t="inlineStr">
-        <is>
-          <t>Urban</t>
-        </is>
-      </c>
+      <c r="CC3" t="inlineStr"/>
       <c r="CD3" t="inlineStr"/>
       <c r="CE3" t="inlineStr"/>
       <c r="CF3" t="inlineStr"/>
-      <c r="CG3" t="n">
-        <v>12.1</v>
-      </c>
+      <c r="CG3" t="inlineStr"/>
       <c r="CH3" t="inlineStr"/>
-      <c r="CI3" t="inlineStr"/>
+      <c r="CI3" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
       <c r="CJ3" t="inlineStr"/>
       <c r="CK3" t="inlineStr"/>
       <c r="CL3" t="inlineStr"/>
@@ -1686,7 +1966,9 @@
       <c r="DI3" t="inlineStr"/>
       <c r="DJ3" t="inlineStr"/>
       <c r="DK3" t="inlineStr"/>
-      <c r="DL3" t="inlineStr"/>
+      <c r="DL3" t="n">
+        <v>12.1</v>
+      </c>
       <c r="DM3" t="inlineStr"/>
       <c r="DN3" t="inlineStr"/>
       <c r="DO3" t="inlineStr"/>
@@ -1725,48 +2007,97 @@
       <c r="EV3" t="inlineStr"/>
       <c r="EW3" t="inlineStr"/>
       <c r="EX3" t="inlineStr"/>
-      <c r="EY3" t="inlineStr">
-        <is>
-          <t>Hindu</t>
-        </is>
-      </c>
+      <c r="EY3" t="inlineStr"/>
       <c r="EZ3" t="inlineStr"/>
-      <c r="FA3" t="inlineStr">
-        <is>
-          <t>CID</t>
-        </is>
-      </c>
+      <c r="FA3" t="inlineStr"/>
       <c r="FB3" t="inlineStr"/>
       <c r="FC3" t="inlineStr"/>
       <c r="FD3" t="inlineStr"/>
-      <c r="FE3" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-      <c r="FF3" t="n">
-        <v>1</v>
-      </c>
+      <c r="FE3" t="inlineStr"/>
+      <c r="FF3" t="inlineStr"/>
       <c r="FG3" t="inlineStr"/>
-      <c r="FH3" t="inlineStr">
-        <is>
-          <t>telangana</t>
-        </is>
-      </c>
-      <c r="FI3" t="inlineStr">
-        <is>
-          <t>2026-02-02</t>
-        </is>
-      </c>
-      <c r="FJ3" t="inlineStr">
-        <is>
-          <t>RACI0002</t>
-        </is>
-      </c>
+      <c r="FH3" t="inlineStr"/>
+      <c r="FI3" t="inlineStr"/>
+      <c r="FJ3" t="inlineStr"/>
       <c r="FK3" t="inlineStr"/>
       <c r="FL3" t="inlineStr"/>
       <c r="FM3" t="inlineStr"/>
       <c r="FN3" t="inlineStr"/>
+      <c r="FO3" t="inlineStr"/>
+      <c r="FP3" t="inlineStr"/>
+      <c r="FQ3" t="inlineStr"/>
+      <c r="FR3" t="inlineStr"/>
+      <c r="FS3" t="inlineStr"/>
+      <c r="FT3" t="inlineStr"/>
+      <c r="FU3" t="inlineStr"/>
+      <c r="FV3" t="inlineStr"/>
+      <c r="FW3" t="inlineStr"/>
+      <c r="FX3" t="inlineStr"/>
+      <c r="FY3" t="inlineStr"/>
+      <c r="FZ3" t="inlineStr"/>
+      <c r="GA3" t="inlineStr"/>
+      <c r="GB3" t="inlineStr"/>
+      <c r="GC3" t="inlineStr"/>
+      <c r="GD3" t="inlineStr"/>
+      <c r="GE3" t="inlineStr"/>
+      <c r="GF3" t="inlineStr"/>
+      <c r="GG3" t="inlineStr"/>
+      <c r="GH3" t="inlineStr"/>
+      <c r="GI3" t="inlineStr"/>
+      <c r="GJ3" t="inlineStr"/>
+      <c r="GK3" t="inlineStr"/>
+      <c r="GL3" t="inlineStr"/>
+      <c r="GM3" t="inlineStr"/>
+      <c r="GN3" t="inlineStr"/>
+      <c r="GO3" t="inlineStr"/>
+      <c r="GP3" t="inlineStr"/>
+      <c r="GQ3" t="inlineStr"/>
+      <c r="GR3" t="inlineStr"/>
+      <c r="GS3" t="inlineStr">
+        <is>
+          <t>Hindu</t>
+        </is>
+      </c>
+      <c r="GT3" t="inlineStr"/>
+      <c r="GU3" t="inlineStr"/>
+      <c r="GV3" t="inlineStr">
+        <is>
+          <t>CID</t>
+        </is>
+      </c>
+      <c r="GW3" t="inlineStr"/>
+      <c r="GX3" t="inlineStr"/>
+      <c r="GY3" t="inlineStr"/>
+      <c r="GZ3" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="HA3" t="n">
+        <v>1</v>
+      </c>
+      <c r="HB3" t="inlineStr"/>
+      <c r="HC3" t="inlineStr">
+        <is>
+          <t>telangana</t>
+        </is>
+      </c>
+      <c r="HD3" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="HE3" t="inlineStr"/>
+      <c r="HF3" t="inlineStr">
+        <is>
+          <t>RACI0002</t>
+        </is>
+      </c>
+      <c r="HG3" t="inlineStr"/>
+      <c r="HH3" t="inlineStr"/>
+      <c r="HI3" t="inlineStr"/>
+      <c r="HJ3" t="inlineStr"/>
+      <c r="HK3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1811,127 +2142,127 @@
       <c r="J4" t="n">
         <v>1</v>
       </c>
-      <c r="K4" t="n">
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="n">
         <v>3</v>
       </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="n">
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="n">
         <v>1</v>
       </c>
-      <c r="N4" t="n">
+      <c r="P4" t="n">
         <v>1</v>
       </c>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr">
         <is>
           <t>SC</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>Anaemic</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr">
         <is>
           <t>0 – Calm and cooperative</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
         <is>
           <t>Masimo Rad-67</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
         <is>
           <t>Vegetarian</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr"/>
-      <c r="AC4" t="inlineStr">
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr">
         <is>
           <t>2024-07-24</t>
         </is>
       </c>
-      <c r="AD4" t="inlineStr">
+      <c r="AF4" t="inlineStr">
         <is>
           <t>Profession / Honours (Score 7)</t>
         </is>
       </c>
-      <c r="AE4" t="inlineStr"/>
-      <c r="AF4" t="inlineStr"/>
-      <c r="AG4" t="inlineStr">
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr"/>
+      <c r="AI4" t="inlineStr">
         <is>
           <t>LECI0003</t>
         </is>
       </c>
-      <c r="AH4" t="inlineStr">
+      <c r="AJ4" t="inlineStr">
         <is>
           <t>2026-02-18 12:19:02</t>
         </is>
       </c>
-      <c r="AI4" t="inlineStr"/>
-      <c r="AJ4" t="inlineStr"/>
       <c r="AK4" t="inlineStr"/>
-      <c r="AL4" t="inlineStr">
+      <c r="AL4" t="inlineStr"/>
+      <c r="AM4" t="inlineStr"/>
+      <c r="AN4" t="inlineStr">
         <is>
           <t>Nuclear</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr"/>
-      <c r="AN4" t="inlineStr"/>
       <c r="AO4" t="inlineStr"/>
       <c r="AP4" t="inlineStr"/>
       <c r="AQ4" t="inlineStr"/>
       <c r="AR4" t="inlineStr"/>
-      <c r="AS4" t="inlineStr">
+      <c r="AS4" t="inlineStr"/>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AU4" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
       </c>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AU4" t="inlineStr"/>
-      <c r="AV4" t="n">
-        <v>16.4</v>
-      </c>
+      <c r="AV4" t="inlineStr"/>
       <c r="AW4" t="inlineStr"/>
       <c r="AX4" t="inlineStr"/>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AY4" t="n">
+        <v>16.4</v>
+      </c>
       <c r="AZ4" t="inlineStr"/>
       <c r="BA4" t="inlineStr"/>
       <c r="BB4" t="inlineStr"/>
-      <c r="BC4" t="inlineStr">
+      <c r="BC4" t="inlineStr"/>
+      <c r="BD4" t="inlineStr"/>
+      <c r="BE4" t="inlineStr"/>
+      <c r="BF4" t="inlineStr">
         <is>
           <t>Daily</t>
         </is>
       </c>
-      <c r="BD4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="BE4" t="inlineStr"/>
-      <c r="BF4" t="inlineStr"/>
-      <c r="BG4" t="inlineStr"/>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="BH4" t="inlineStr"/>
       <c r="BI4" t="inlineStr"/>
       <c r="BJ4" t="inlineStr"/>
@@ -1953,25 +2284,23 @@
       <c r="BZ4" t="inlineStr"/>
       <c r="CA4" t="inlineStr"/>
       <c r="CB4" t="inlineStr"/>
-      <c r="CC4" t="inlineStr">
+      <c r="CC4" t="inlineStr"/>
+      <c r="CD4" t="inlineStr"/>
+      <c r="CE4" t="inlineStr"/>
+      <c r="CF4" t="inlineStr"/>
+      <c r="CG4" t="inlineStr"/>
+      <c r="CH4" t="inlineStr"/>
+      <c r="CI4" t="inlineStr">
         <is>
           <t>Urban</t>
         </is>
       </c>
-      <c r="CD4" t="inlineStr"/>
-      <c r="CE4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="CF4" t="inlineStr"/>
-      <c r="CG4" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="CH4" t="inlineStr"/>
-      <c r="CI4" t="inlineStr"/>
       <c r="CJ4" t="inlineStr"/>
-      <c r="CK4" t="inlineStr"/>
+      <c r="CK4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="CL4" t="inlineStr"/>
       <c r="CM4" t="inlineStr"/>
       <c r="CN4" t="inlineStr"/>
@@ -1994,19 +2323,13 @@
       <c r="DE4" t="inlineStr"/>
       <c r="DF4" t="inlineStr"/>
       <c r="DG4" t="inlineStr"/>
-      <c r="DH4" t="inlineStr">
-        <is>
-          <t>₹1,59,586+ (Score 12)</t>
-        </is>
-      </c>
+      <c r="DH4" t="inlineStr"/>
       <c r="DI4" t="inlineStr"/>
-      <c r="DJ4" t="inlineStr">
-        <is>
-          <t>Legislators/managers (Score 10)</t>
-        </is>
-      </c>
+      <c r="DJ4" t="inlineStr"/>
       <c r="DK4" t="inlineStr"/>
-      <c r="DL4" t="inlineStr"/>
+      <c r="DL4" t="n">
+        <v>14.8</v>
+      </c>
       <c r="DM4" t="inlineStr"/>
       <c r="DN4" t="inlineStr"/>
       <c r="DO4" t="inlineStr"/>
@@ -2033,53 +2356,33 @@
       <c r="EJ4" t="inlineStr"/>
       <c r="EK4" t="inlineStr"/>
       <c r="EL4" t="inlineStr"/>
-      <c r="EM4" t="inlineStr"/>
-      <c r="EN4" t="inlineStr">
-        <is>
-          <t>Non-invasive</t>
-        </is>
-      </c>
-      <c r="EO4" t="inlineStr"/>
+      <c r="EM4" t="inlineStr">
+        <is>
+          <t>₹1,59,586+ (Score 12)</t>
+        </is>
+      </c>
+      <c r="EN4" t="inlineStr"/>
+      <c r="EO4" t="inlineStr">
+        <is>
+          <t>Legislators/managers (Score 10)</t>
+        </is>
+      </c>
       <c r="EP4" t="inlineStr"/>
       <c r="EQ4" t="inlineStr"/>
       <c r="ER4" t="inlineStr"/>
       <c r="ES4" t="inlineStr"/>
       <c r="ET4" t="inlineStr"/>
-      <c r="EU4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="EU4" t="inlineStr"/>
       <c r="EV4" t="inlineStr"/>
-      <c r="EW4" t="inlineStr">
-        <is>
-          <t>PHC</t>
-        </is>
-      </c>
+      <c r="EW4" t="inlineStr"/>
       <c r="EX4" t="inlineStr"/>
-      <c r="EY4" t="inlineStr">
-        <is>
-          <t>Hindu</t>
-        </is>
-      </c>
-      <c r="EZ4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="EY4" t="inlineStr"/>
+      <c r="EZ4" t="inlineStr"/>
       <c r="FA4" t="inlineStr"/>
       <c r="FB4" t="inlineStr"/>
-      <c r="FC4" t="inlineStr">
-        <is>
-          <t>Upper (26–29)</t>
-        </is>
-      </c>
+      <c r="FC4" t="inlineStr"/>
       <c r="FD4" t="inlineStr"/>
-      <c r="FE4" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
+      <c r="FE4" t="inlineStr"/>
       <c r="FF4" t="inlineStr"/>
       <c r="FG4" t="inlineStr"/>
       <c r="FH4" t="inlineStr"/>
@@ -2087,12 +2390,89 @@
       <c r="FJ4" t="inlineStr"/>
       <c r="FK4" t="inlineStr"/>
       <c r="FL4" t="inlineStr"/>
-      <c r="FM4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="FM4" t="inlineStr"/>
       <c r="FN4" t="inlineStr"/>
+      <c r="FO4" t="inlineStr"/>
+      <c r="FP4" t="inlineStr"/>
+      <c r="FQ4" t="inlineStr"/>
+      <c r="FR4" t="inlineStr"/>
+      <c r="FS4" t="inlineStr"/>
+      <c r="FT4" t="inlineStr"/>
+      <c r="FU4" t="inlineStr"/>
+      <c r="FV4" t="inlineStr"/>
+      <c r="FW4" t="inlineStr"/>
+      <c r="FX4" t="inlineStr"/>
+      <c r="FY4" t="inlineStr"/>
+      <c r="FZ4" t="inlineStr"/>
+      <c r="GA4" t="inlineStr"/>
+      <c r="GB4" t="inlineStr"/>
+      <c r="GC4" t="inlineStr"/>
+      <c r="GD4" t="inlineStr"/>
+      <c r="GE4" t="inlineStr">
+        <is>
+          <t>Non-invasive</t>
+        </is>
+      </c>
+      <c r="GF4" t="inlineStr"/>
+      <c r="GG4" t="inlineStr"/>
+      <c r="GH4" t="inlineStr"/>
+      <c r="GI4" t="inlineStr"/>
+      <c r="GJ4" t="inlineStr"/>
+      <c r="GK4" t="inlineStr"/>
+      <c r="GL4" t="inlineStr"/>
+      <c r="GM4" t="inlineStr"/>
+      <c r="GN4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="GO4" t="inlineStr"/>
+      <c r="GP4" t="inlineStr">
+        <is>
+          <t>PHC</t>
+        </is>
+      </c>
+      <c r="GQ4" t="inlineStr"/>
+      <c r="GR4" t="inlineStr"/>
+      <c r="GS4" t="inlineStr">
+        <is>
+          <t>Hindu</t>
+        </is>
+      </c>
+      <c r="GT4" t="inlineStr"/>
+      <c r="GU4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="GV4" t="inlineStr"/>
+      <c r="GW4" t="inlineStr"/>
+      <c r="GX4" t="inlineStr">
+        <is>
+          <t>Upper (26–29)</t>
+        </is>
+      </c>
+      <c r="GY4" t="inlineStr"/>
+      <c r="GZ4" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="HA4" t="inlineStr"/>
+      <c r="HB4" t="inlineStr"/>
+      <c r="HC4" t="inlineStr"/>
+      <c r="HD4" t="inlineStr"/>
+      <c r="HE4" t="inlineStr"/>
+      <c r="HF4" t="inlineStr"/>
+      <c r="HG4" t="inlineStr"/>
+      <c r="HH4" t="inlineStr"/>
+      <c r="HI4" t="inlineStr"/>
+      <c r="HJ4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="HK4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2147,13 +2527,13 @@
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="inlineStr"/>
-      <c r="AC5" t="inlineStr">
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr">
         <is>
           <t>2023-06-18</t>
         </is>
       </c>
-      <c r="AD5" t="inlineStr"/>
-      <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="inlineStr"/>
       <c r="AH5" t="inlineStr"/>
@@ -2167,19 +2547,19 @@
       <c r="AP5" t="inlineStr"/>
       <c r="AQ5" t="inlineStr"/>
       <c r="AR5" t="inlineStr"/>
-      <c r="AS5" t="inlineStr">
+      <c r="AS5" t="inlineStr"/>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AU5" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
       </c>
-      <c r="AT5" t="inlineStr"/>
-      <c r="AU5" t="inlineStr"/>
-      <c r="AV5" t="n">
-        <v>14</v>
-      </c>
+      <c r="AV5" t="inlineStr"/>
       <c r="AW5" t="inlineStr"/>
       <c r="AX5" t="inlineStr"/>
-      <c r="AY5" t="inlineStr"/>
+      <c r="AY5" t="n">
+        <v>14</v>
+      </c>
       <c r="AZ5" t="inlineStr"/>
       <c r="BA5" t="inlineStr"/>
       <c r="BB5" t="inlineStr"/>
@@ -2213,9 +2593,7 @@
       <c r="CD5" t="inlineStr"/>
       <c r="CE5" t="inlineStr"/>
       <c r="CF5" t="inlineStr"/>
-      <c r="CG5" t="n">
-        <v>14.5</v>
-      </c>
+      <c r="CG5" t="inlineStr"/>
       <c r="CH5" t="inlineStr"/>
       <c r="CI5" t="inlineStr"/>
       <c r="CJ5" t="inlineStr"/>
@@ -2246,7 +2624,9 @@
       <c r="DI5" t="inlineStr"/>
       <c r="DJ5" t="inlineStr"/>
       <c r="DK5" t="inlineStr"/>
-      <c r="DL5" t="inlineStr"/>
+      <c r="DL5" t="n">
+        <v>14.5</v>
+      </c>
       <c r="DM5" t="inlineStr"/>
       <c r="DN5" t="inlineStr"/>
       <c r="DO5" t="inlineStr"/>
@@ -2301,6 +2681,55 @@
       <c r="FL5" t="inlineStr"/>
       <c r="FM5" t="inlineStr"/>
       <c r="FN5" t="inlineStr"/>
+      <c r="FO5" t="inlineStr"/>
+      <c r="FP5" t="inlineStr"/>
+      <c r="FQ5" t="inlineStr"/>
+      <c r="FR5" t="inlineStr"/>
+      <c r="FS5" t="inlineStr"/>
+      <c r="FT5" t="inlineStr"/>
+      <c r="FU5" t="inlineStr"/>
+      <c r="FV5" t="inlineStr"/>
+      <c r="FW5" t="inlineStr"/>
+      <c r="FX5" t="inlineStr"/>
+      <c r="FY5" t="inlineStr"/>
+      <c r="FZ5" t="inlineStr"/>
+      <c r="GA5" t="inlineStr"/>
+      <c r="GB5" t="inlineStr"/>
+      <c r="GC5" t="inlineStr"/>
+      <c r="GD5" t="inlineStr"/>
+      <c r="GE5" t="inlineStr"/>
+      <c r="GF5" t="inlineStr"/>
+      <c r="GG5" t="inlineStr"/>
+      <c r="GH5" t="inlineStr"/>
+      <c r="GI5" t="inlineStr"/>
+      <c r="GJ5" t="inlineStr"/>
+      <c r="GK5" t="inlineStr"/>
+      <c r="GL5" t="inlineStr"/>
+      <c r="GM5" t="inlineStr"/>
+      <c r="GN5" t="inlineStr"/>
+      <c r="GO5" t="inlineStr"/>
+      <c r="GP5" t="inlineStr"/>
+      <c r="GQ5" t="inlineStr"/>
+      <c r="GR5" t="inlineStr"/>
+      <c r="GS5" t="inlineStr"/>
+      <c r="GT5" t="inlineStr"/>
+      <c r="GU5" t="inlineStr"/>
+      <c r="GV5" t="inlineStr"/>
+      <c r="GW5" t="inlineStr"/>
+      <c r="GX5" t="inlineStr"/>
+      <c r="GY5" t="inlineStr"/>
+      <c r="GZ5" t="inlineStr"/>
+      <c r="HA5" t="inlineStr"/>
+      <c r="HB5" t="inlineStr"/>
+      <c r="HC5" t="inlineStr"/>
+      <c r="HD5" t="inlineStr"/>
+      <c r="HE5" t="inlineStr"/>
+      <c r="HF5" t="inlineStr"/>
+      <c r="HG5" t="inlineStr"/>
+      <c r="HH5" t="inlineStr"/>
+      <c r="HI5" t="inlineStr"/>
+      <c r="HJ5" t="inlineStr"/>
+      <c r="HK5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2353,13 +2782,13 @@
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="inlineStr"/>
-      <c r="AC6" t="inlineStr">
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr">
         <is>
           <t>2023-06-18</t>
         </is>
       </c>
-      <c r="AD6" t="inlineStr"/>
-      <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="inlineStr"/>
       <c r="AH6" t="inlineStr"/>
@@ -2373,19 +2802,19 @@
       <c r="AP6" t="inlineStr"/>
       <c r="AQ6" t="inlineStr"/>
       <c r="AR6" t="inlineStr"/>
-      <c r="AS6" t="inlineStr">
+      <c r="AS6" t="inlineStr"/>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AU6" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
       </c>
-      <c r="AT6" t="inlineStr"/>
-      <c r="AU6" t="inlineStr"/>
-      <c r="AV6" t="n">
-        <v>12</v>
-      </c>
+      <c r="AV6" t="inlineStr"/>
       <c r="AW6" t="inlineStr"/>
       <c r="AX6" t="inlineStr"/>
-      <c r="AY6" t="inlineStr"/>
+      <c r="AY6" t="n">
+        <v>12</v>
+      </c>
       <c r="AZ6" t="inlineStr"/>
       <c r="BA6" t="inlineStr"/>
       <c r="BB6" t="inlineStr"/>
@@ -2419,9 +2848,7 @@
       <c r="CD6" t="inlineStr"/>
       <c r="CE6" t="inlineStr"/>
       <c r="CF6" t="inlineStr"/>
-      <c r="CG6" t="n">
-        <v>11.6</v>
-      </c>
+      <c r="CG6" t="inlineStr"/>
       <c r="CH6" t="inlineStr"/>
       <c r="CI6" t="inlineStr"/>
       <c r="CJ6" t="inlineStr"/>
@@ -2452,7 +2879,9 @@
       <c r="DI6" t="inlineStr"/>
       <c r="DJ6" t="inlineStr"/>
       <c r="DK6" t="inlineStr"/>
-      <c r="DL6" t="inlineStr"/>
+      <c r="DL6" t="n">
+        <v>11.6</v>
+      </c>
       <c r="DM6" t="inlineStr"/>
       <c r="DN6" t="inlineStr"/>
       <c r="DO6" t="inlineStr"/>
@@ -2507,6 +2936,55 @@
       <c r="FL6" t="inlineStr"/>
       <c r="FM6" t="inlineStr"/>
       <c r="FN6" t="inlineStr"/>
+      <c r="FO6" t="inlineStr"/>
+      <c r="FP6" t="inlineStr"/>
+      <c r="FQ6" t="inlineStr"/>
+      <c r="FR6" t="inlineStr"/>
+      <c r="FS6" t="inlineStr"/>
+      <c r="FT6" t="inlineStr"/>
+      <c r="FU6" t="inlineStr"/>
+      <c r="FV6" t="inlineStr"/>
+      <c r="FW6" t="inlineStr"/>
+      <c r="FX6" t="inlineStr"/>
+      <c r="FY6" t="inlineStr"/>
+      <c r="FZ6" t="inlineStr"/>
+      <c r="GA6" t="inlineStr"/>
+      <c r="GB6" t="inlineStr"/>
+      <c r="GC6" t="inlineStr"/>
+      <c r="GD6" t="inlineStr"/>
+      <c r="GE6" t="inlineStr"/>
+      <c r="GF6" t="inlineStr"/>
+      <c r="GG6" t="inlineStr"/>
+      <c r="GH6" t="inlineStr"/>
+      <c r="GI6" t="inlineStr"/>
+      <c r="GJ6" t="inlineStr"/>
+      <c r="GK6" t="inlineStr"/>
+      <c r="GL6" t="inlineStr"/>
+      <c r="GM6" t="inlineStr"/>
+      <c r="GN6" t="inlineStr"/>
+      <c r="GO6" t="inlineStr"/>
+      <c r="GP6" t="inlineStr"/>
+      <c r="GQ6" t="inlineStr"/>
+      <c r="GR6" t="inlineStr"/>
+      <c r="GS6" t="inlineStr"/>
+      <c r="GT6" t="inlineStr"/>
+      <c r="GU6" t="inlineStr"/>
+      <c r="GV6" t="inlineStr"/>
+      <c r="GW6" t="inlineStr"/>
+      <c r="GX6" t="inlineStr"/>
+      <c r="GY6" t="inlineStr"/>
+      <c r="GZ6" t="inlineStr"/>
+      <c r="HA6" t="inlineStr"/>
+      <c r="HB6" t="inlineStr"/>
+      <c r="HC6" t="inlineStr"/>
+      <c r="HD6" t="inlineStr"/>
+      <c r="HE6" t="inlineStr"/>
+      <c r="HF6" t="inlineStr"/>
+      <c r="HG6" t="inlineStr"/>
+      <c r="HH6" t="inlineStr"/>
+      <c r="HI6" t="inlineStr"/>
+      <c r="HJ6" t="inlineStr"/>
+      <c r="HK6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2559,13 +3037,13 @@
       <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="inlineStr"/>
       <c r="AB7" t="inlineStr"/>
-      <c r="AC7" t="inlineStr">
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr"/>
+      <c r="AE7" t="inlineStr">
         <is>
           <t>2023-06-15</t>
         </is>
       </c>
-      <c r="AD7" t="inlineStr"/>
-      <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="inlineStr"/>
       <c r="AH7" t="inlineStr"/>
@@ -2579,19 +3057,19 @@
       <c r="AP7" t="inlineStr"/>
       <c r="AQ7" t="inlineStr"/>
       <c r="AR7" t="inlineStr"/>
-      <c r="AS7" t="inlineStr">
+      <c r="AS7" t="inlineStr"/>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AU7" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
       </c>
-      <c r="AT7" t="inlineStr"/>
-      <c r="AU7" t="inlineStr"/>
-      <c r="AV7" t="n">
-        <v>13.1</v>
-      </c>
+      <c r="AV7" t="inlineStr"/>
       <c r="AW7" t="inlineStr"/>
       <c r="AX7" t="inlineStr"/>
-      <c r="AY7" t="inlineStr"/>
+      <c r="AY7" t="n">
+        <v>13.1</v>
+      </c>
       <c r="AZ7" t="inlineStr"/>
       <c r="BA7" t="inlineStr"/>
       <c r="BB7" t="inlineStr"/>
@@ -2625,9 +3103,7 @@
       <c r="CD7" t="inlineStr"/>
       <c r="CE7" t="inlineStr"/>
       <c r="CF7" t="inlineStr"/>
-      <c r="CG7" t="n">
-        <v>11.9</v>
-      </c>
+      <c r="CG7" t="inlineStr"/>
       <c r="CH7" t="inlineStr"/>
       <c r="CI7" t="inlineStr"/>
       <c r="CJ7" t="inlineStr"/>
@@ -2658,7 +3134,9 @@
       <c r="DI7" t="inlineStr"/>
       <c r="DJ7" t="inlineStr"/>
       <c r="DK7" t="inlineStr"/>
-      <c r="DL7" t="inlineStr"/>
+      <c r="DL7" t="n">
+        <v>11.9</v>
+      </c>
       <c r="DM7" t="inlineStr"/>
       <c r="DN7" t="inlineStr"/>
       <c r="DO7" t="inlineStr"/>
@@ -2713,6 +3191,55 @@
       <c r="FL7" t="inlineStr"/>
       <c r="FM7" t="inlineStr"/>
       <c r="FN7" t="inlineStr"/>
+      <c r="FO7" t="inlineStr"/>
+      <c r="FP7" t="inlineStr"/>
+      <c r="FQ7" t="inlineStr"/>
+      <c r="FR7" t="inlineStr"/>
+      <c r="FS7" t="inlineStr"/>
+      <c r="FT7" t="inlineStr"/>
+      <c r="FU7" t="inlineStr"/>
+      <c r="FV7" t="inlineStr"/>
+      <c r="FW7" t="inlineStr"/>
+      <c r="FX7" t="inlineStr"/>
+      <c r="FY7" t="inlineStr"/>
+      <c r="FZ7" t="inlineStr"/>
+      <c r="GA7" t="inlineStr"/>
+      <c r="GB7" t="inlineStr"/>
+      <c r="GC7" t="inlineStr"/>
+      <c r="GD7" t="inlineStr"/>
+      <c r="GE7" t="inlineStr"/>
+      <c r="GF7" t="inlineStr"/>
+      <c r="GG7" t="inlineStr"/>
+      <c r="GH7" t="inlineStr"/>
+      <c r="GI7" t="inlineStr"/>
+      <c r="GJ7" t="inlineStr"/>
+      <c r="GK7" t="inlineStr"/>
+      <c r="GL7" t="inlineStr"/>
+      <c r="GM7" t="inlineStr"/>
+      <c r="GN7" t="inlineStr"/>
+      <c r="GO7" t="inlineStr"/>
+      <c r="GP7" t="inlineStr"/>
+      <c r="GQ7" t="inlineStr"/>
+      <c r="GR7" t="inlineStr"/>
+      <c r="GS7" t="inlineStr"/>
+      <c r="GT7" t="inlineStr"/>
+      <c r="GU7" t="inlineStr"/>
+      <c r="GV7" t="inlineStr"/>
+      <c r="GW7" t="inlineStr"/>
+      <c r="GX7" t="inlineStr"/>
+      <c r="GY7" t="inlineStr"/>
+      <c r="GZ7" t="inlineStr"/>
+      <c r="HA7" t="inlineStr"/>
+      <c r="HB7" t="inlineStr"/>
+      <c r="HC7" t="inlineStr"/>
+      <c r="HD7" t="inlineStr"/>
+      <c r="HE7" t="inlineStr"/>
+      <c r="HF7" t="inlineStr"/>
+      <c r="HG7" t="inlineStr"/>
+      <c r="HH7" t="inlineStr"/>
+      <c r="HI7" t="inlineStr"/>
+      <c r="HJ7" t="inlineStr"/>
+      <c r="HK7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2765,13 +3292,13 @@
       <c r="Z8" t="inlineStr"/>
       <c r="AA8" t="inlineStr"/>
       <c r="AB8" t="inlineStr"/>
-      <c r="AC8" t="inlineStr">
+      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr"/>
+      <c r="AE8" t="inlineStr">
         <is>
           <t>2023-03-08</t>
         </is>
       </c>
-      <c r="AD8" t="inlineStr"/>
-      <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="inlineStr"/>
       <c r="AH8" t="inlineStr"/>
@@ -2785,19 +3312,19 @@
       <c r="AP8" t="inlineStr"/>
       <c r="AQ8" t="inlineStr"/>
       <c r="AR8" t="inlineStr"/>
-      <c r="AS8" t="inlineStr">
+      <c r="AS8" t="inlineStr"/>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AU8" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
       </c>
-      <c r="AT8" t="inlineStr"/>
-      <c r="AU8" t="inlineStr"/>
-      <c r="AV8" t="n">
-        <v>10.8</v>
-      </c>
+      <c r="AV8" t="inlineStr"/>
       <c r="AW8" t="inlineStr"/>
       <c r="AX8" t="inlineStr"/>
-      <c r="AY8" t="inlineStr"/>
+      <c r="AY8" t="n">
+        <v>10.8</v>
+      </c>
       <c r="AZ8" t="inlineStr"/>
       <c r="BA8" t="inlineStr"/>
       <c r="BB8" t="inlineStr"/>
@@ -2831,9 +3358,7 @@
       <c r="CD8" t="inlineStr"/>
       <c r="CE8" t="inlineStr"/>
       <c r="CF8" t="inlineStr"/>
-      <c r="CG8" t="n">
-        <v>11.5</v>
-      </c>
+      <c r="CG8" t="inlineStr"/>
       <c r="CH8" t="inlineStr"/>
       <c r="CI8" t="inlineStr"/>
       <c r="CJ8" t="inlineStr"/>
@@ -2864,7 +3389,9 @@
       <c r="DI8" t="inlineStr"/>
       <c r="DJ8" t="inlineStr"/>
       <c r="DK8" t="inlineStr"/>
-      <c r="DL8" t="inlineStr"/>
+      <c r="DL8" t="n">
+        <v>11.5</v>
+      </c>
       <c r="DM8" t="inlineStr"/>
       <c r="DN8" t="inlineStr"/>
       <c r="DO8" t="inlineStr"/>
@@ -2919,6 +3446,55 @@
       <c r="FL8" t="inlineStr"/>
       <c r="FM8" t="inlineStr"/>
       <c r="FN8" t="inlineStr"/>
+      <c r="FO8" t="inlineStr"/>
+      <c r="FP8" t="inlineStr"/>
+      <c r="FQ8" t="inlineStr"/>
+      <c r="FR8" t="inlineStr"/>
+      <c r="FS8" t="inlineStr"/>
+      <c r="FT8" t="inlineStr"/>
+      <c r="FU8" t="inlineStr"/>
+      <c r="FV8" t="inlineStr"/>
+      <c r="FW8" t="inlineStr"/>
+      <c r="FX8" t="inlineStr"/>
+      <c r="FY8" t="inlineStr"/>
+      <c r="FZ8" t="inlineStr"/>
+      <c r="GA8" t="inlineStr"/>
+      <c r="GB8" t="inlineStr"/>
+      <c r="GC8" t="inlineStr"/>
+      <c r="GD8" t="inlineStr"/>
+      <c r="GE8" t="inlineStr"/>
+      <c r="GF8" t="inlineStr"/>
+      <c r="GG8" t="inlineStr"/>
+      <c r="GH8" t="inlineStr"/>
+      <c r="GI8" t="inlineStr"/>
+      <c r="GJ8" t="inlineStr"/>
+      <c r="GK8" t="inlineStr"/>
+      <c r="GL8" t="inlineStr"/>
+      <c r="GM8" t="inlineStr"/>
+      <c r="GN8" t="inlineStr"/>
+      <c r="GO8" t="inlineStr"/>
+      <c r="GP8" t="inlineStr"/>
+      <c r="GQ8" t="inlineStr"/>
+      <c r="GR8" t="inlineStr"/>
+      <c r="GS8" t="inlineStr"/>
+      <c r="GT8" t="inlineStr"/>
+      <c r="GU8" t="inlineStr"/>
+      <c r="GV8" t="inlineStr"/>
+      <c r="GW8" t="inlineStr"/>
+      <c r="GX8" t="inlineStr"/>
+      <c r="GY8" t="inlineStr"/>
+      <c r="GZ8" t="inlineStr"/>
+      <c r="HA8" t="inlineStr"/>
+      <c r="HB8" t="inlineStr"/>
+      <c r="HC8" t="inlineStr"/>
+      <c r="HD8" t="inlineStr"/>
+      <c r="HE8" t="inlineStr"/>
+      <c r="HF8" t="inlineStr"/>
+      <c r="HG8" t="inlineStr"/>
+      <c r="HH8" t="inlineStr"/>
+      <c r="HI8" t="inlineStr"/>
+      <c r="HJ8" t="inlineStr"/>
+      <c r="HK8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2965,460 +3541,509 @@
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="n">
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="n">
         <v>1</v>
       </c>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr"/>
       <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr">
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr"/>
-      <c r="W9" t="inlineStr"/>
       <c r="X9" t="inlineStr"/>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
+      <c r="Y9" t="inlineStr"/>
       <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>Mixed</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr">
         <is>
+          <t>Mixed</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr"/>
+      <c r="AE9" t="inlineStr">
+        <is>
           <t>2004-01-25</t>
         </is>
       </c>
-      <c r="AD9" t="inlineStr"/>
-      <c r="AE9" t="inlineStr"/>
       <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="inlineStr"/>
       <c r="AH9" t="inlineStr"/>
       <c r="AI9" t="inlineStr"/>
-      <c r="AJ9" t="n">
+      <c r="AJ9" t="inlineStr"/>
+      <c r="AK9" t="inlineStr"/>
+      <c r="AL9" t="n">
         <v>4</v>
       </c>
-      <c r="AK9" t="inlineStr"/>
-      <c r="AL9" t="inlineStr">
+      <c r="AM9" t="inlineStr"/>
+      <c r="AN9" t="inlineStr">
         <is>
           <t>Nuclear</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
+      <c r="AO9" t="inlineStr">
         <is>
           <t>Rarely</t>
         </is>
       </c>
-      <c r="AN9" t="inlineStr">
+      <c r="AP9" t="inlineStr">
         <is>
           <t>Daily</t>
         </is>
       </c>
-      <c r="AO9" t="inlineStr">
+      <c r="AQ9" t="inlineStr">
         <is>
           <t>Daily</t>
         </is>
       </c>
-      <c r="AP9" t="inlineStr">
+      <c r="AR9" t="inlineStr">
         <is>
           <t>3–4/week</t>
         </is>
       </c>
-      <c r="AQ9" t="inlineStr">
+      <c r="AS9" t="inlineStr">
         <is>
           <t>1–2/week</t>
         </is>
       </c>
-      <c r="AR9" t="inlineStr">
+      <c r="AT9" t="inlineStr">
         <is>
           <t>3–4/week</t>
         </is>
       </c>
-      <c r="AS9" t="inlineStr">
+      <c r="AU9" t="inlineStr">
         <is>
           <t>Female</t>
         </is>
       </c>
-      <c r="AT9" t="inlineStr"/>
-      <c r="AU9" t="n">
+      <c r="AV9" t="inlineStr"/>
+      <c r="AW9" t="n">
         <v>156</v>
       </c>
-      <c r="AV9" t="n">
+      <c r="AX9" t="inlineStr"/>
+      <c r="AY9" t="n">
         <v>10.4</v>
       </c>
-      <c r="AW9" t="inlineStr"/>
-      <c r="AX9" t="inlineStr"/>
-      <c r="AY9" t="inlineStr"/>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>lekha</t>
-        </is>
-      </c>
+      <c r="AZ9" t="inlineStr"/>
       <c r="BA9" t="inlineStr"/>
       <c r="BB9" t="inlineStr"/>
-      <c r="BC9" t="inlineStr"/>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>lekha</t>
+        </is>
+      </c>
       <c r="BD9" t="inlineStr"/>
-      <c r="BE9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="BF9" t="n">
+      <c r="BE9" t="inlineStr"/>
+      <c r="BF9" t="inlineStr"/>
+      <c r="BG9" t="inlineStr"/>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BI9" t="n">
         <v>27</v>
       </c>
-      <c r="BG9" t="inlineStr"/>
-      <c r="BH9" t="n">
+      <c r="BJ9" t="inlineStr"/>
+      <c r="BK9" t="n">
         <v>1</v>
       </c>
-      <c r="BI9" t="inlineStr">
+      <c r="BL9" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="BJ9" t="inlineStr">
+      <c r="BM9" t="inlineStr">
         <is>
           <t>Very easy</t>
         </is>
       </c>
-      <c r="BK9" t="inlineStr"/>
-      <c r="BL9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ9" t="inlineStr"/>
-      <c r="BR9" t="inlineStr"/>
-      <c r="BS9" t="inlineStr">
+      <c r="BN9" t="inlineStr"/>
+      <c r="BO9" t="inlineStr"/>
+      <c r="BP9" t="inlineStr"/>
+      <c r="BQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV9" t="inlineStr"/>
+      <c r="BW9" t="inlineStr"/>
+      <c r="BX9" t="inlineStr">
         <is>
           <t>Daily</t>
-        </is>
-      </c>
-      <c r="BT9" t="inlineStr">
-        <is>
-          <t>Highly portable</t>
-        </is>
-      </c>
-      <c r="BU9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="BV9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="BW9" t="inlineStr">
-        <is>
-          <t>Always</t>
-        </is>
-      </c>
-      <c r="BX9" t="inlineStr">
-        <is>
-          <t>Very safe</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr"/>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="CA9" t="inlineStr"/>
-      <c r="CB9" t="inlineStr"/>
-      <c r="CC9" t="inlineStr"/>
+          <t>Highly portable</t>
+        </is>
+      </c>
+      <c r="CA9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CB9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CC9" t="inlineStr">
+        <is>
+          <t>Always</t>
+        </is>
+      </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>Urban</t>
+          <t>Very safe</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr"/>
       <c r="CF9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CG9" t="inlineStr"/>
+      <c r="CH9" t="inlineStr"/>
+      <c r="CI9" t="inlineStr"/>
+      <c r="CJ9" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
+      <c r="CK9" t="inlineStr"/>
+      <c r="CL9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="CG9" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="CH9" t="inlineStr"/>
-      <c r="CI9" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="CJ9" t="inlineStr">
-        <is>
-          <t>Very easy</t>
-        </is>
-      </c>
-      <c r="CK9" t="inlineStr">
-        <is>
-          <t>11:30</t>
-        </is>
-      </c>
-      <c r="CL9" t="n">
-        <v>1</v>
-      </c>
-      <c r="CM9" t="n">
-        <v>1</v>
-      </c>
-      <c r="CN9" t="n">
-        <v>2</v>
-      </c>
-      <c r="CO9" t="n">
-        <v>1</v>
-      </c>
-      <c r="CP9" t="n">
-        <v>1</v>
-      </c>
-      <c r="CQ9" t="n">
-        <v>2</v>
-      </c>
+      <c r="CM9" t="inlineStr"/>
+      <c r="CN9" t="inlineStr"/>
+      <c r="CO9" t="inlineStr"/>
+      <c r="CP9" t="inlineStr"/>
+      <c r="CQ9" t="inlineStr"/>
       <c r="CR9" t="inlineStr"/>
-      <c r="CS9" t="inlineStr">
-        <is>
-          <t>Daily</t>
-        </is>
-      </c>
-      <c r="CT9" t="inlineStr">
-        <is>
-          <t>Highly portable</t>
-        </is>
-      </c>
-      <c r="CU9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="CV9" t="n">
-        <v>56</v>
-      </c>
+      <c r="CS9" t="inlineStr"/>
+      <c r="CT9" t="inlineStr"/>
+      <c r="CU9" t="inlineStr"/>
+      <c r="CV9" t="inlineStr"/>
       <c r="CW9" t="inlineStr"/>
       <c r="CX9" t="inlineStr"/>
       <c r="CY9" t="inlineStr"/>
-      <c r="CZ9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="DA9" t="inlineStr">
-        <is>
-          <t>Always</t>
-        </is>
-      </c>
-      <c r="DB9" t="inlineStr">
-        <is>
-          <t>Very safe</t>
-        </is>
-      </c>
-      <c r="DC9" t="inlineStr">
-        <is>
-          <t>10:35</t>
-        </is>
-      </c>
-      <c r="DD9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="CZ9" t="inlineStr"/>
+      <c r="DA9" t="inlineStr"/>
+      <c r="DB9" t="inlineStr"/>
+      <c r="DC9" t="inlineStr"/>
+      <c r="DD9" t="inlineStr"/>
       <c r="DE9" t="inlineStr"/>
-      <c r="DF9" t="inlineStr">
-        <is>
-          <t>Minimally invasive POC</t>
-        </is>
-      </c>
-      <c r="DG9" t="n">
-        <v>7659032531</v>
-      </c>
+      <c r="DF9" t="inlineStr"/>
+      <c r="DG9" t="inlineStr"/>
       <c r="DH9" t="inlineStr"/>
       <c r="DI9" t="inlineStr"/>
       <c r="DJ9" t="inlineStr"/>
       <c r="DK9" t="inlineStr"/>
       <c r="DL9" t="n">
-        <v>1</v>
-      </c>
-      <c r="DM9" t="n">
-        <v>1</v>
-      </c>
-      <c r="DN9" t="n">
-        <v>1</v>
-      </c>
-      <c r="DO9" t="n">
-        <v>1</v>
-      </c>
-      <c r="DP9" t="inlineStr"/>
+        <v>10.8</v>
+      </c>
+      <c r="DM9" t="inlineStr"/>
+      <c r="DN9" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="DO9" t="inlineStr">
+        <is>
+          <t>Very easy</t>
+        </is>
+      </c>
+      <c r="DP9" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
       <c r="DQ9" t="n">
         <v>1</v>
       </c>
-      <c r="DR9" t="inlineStr">
-        <is>
-          <t>Mucharla Sreelekha</t>
-        </is>
+      <c r="DR9" t="n">
+        <v>1</v>
       </c>
       <c r="DS9" t="n">
+        <v>2</v>
+      </c>
+      <c r="DT9" t="n">
         <v>1</v>
       </c>
-      <c r="DT9" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="DU9" t="inlineStr">
-        <is>
-          <t>Very easy</t>
-        </is>
-      </c>
-      <c r="DV9" t="inlineStr"/>
-      <c r="DW9" t="n">
+      <c r="DU9" t="n">
         <v>1</v>
       </c>
-      <c r="DX9" t="n">
-        <v>0</v>
-      </c>
-      <c r="DY9" t="n">
-        <v>0</v>
-      </c>
-      <c r="DZ9" t="n">
-        <v>0</v>
+      <c r="DV9" t="n">
+        <v>2</v>
+      </c>
+      <c r="DW9" t="inlineStr"/>
+      <c r="DX9" t="inlineStr">
+        <is>
+          <t>Daily</t>
+        </is>
+      </c>
+      <c r="DY9" t="inlineStr">
+        <is>
+          <t>Highly portable</t>
+        </is>
+      </c>
+      <c r="DZ9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
       </c>
       <c r="EA9" t="n">
-        <v>0</v>
-      </c>
-      <c r="EB9" t="n">
-        <v>0</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="EB9" t="inlineStr"/>
       <c r="EC9" t="inlineStr"/>
       <c r="ED9" t="inlineStr"/>
       <c r="EE9" t="inlineStr">
         <is>
-          <t>Daily</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="EF9" t="inlineStr">
         <is>
-          <t>Highly portable</t>
+          <t>Always</t>
         </is>
       </c>
       <c r="EG9" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Very safe</t>
         </is>
       </c>
       <c r="EH9" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="EI9" t="inlineStr">
         <is>
-          <t>Always</t>
-        </is>
-      </c>
-      <c r="EJ9" t="inlineStr">
-        <is>
-          <t>Very safe</t>
-        </is>
-      </c>
-      <c r="EK9" t="inlineStr"/>
-      <c r="EL9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="EJ9" t="inlineStr"/>
+      <c r="EK9" t="inlineStr">
+        <is>
+          <t>Minimally invasive POC</t>
+        </is>
+      </c>
+      <c r="EL9" t="n">
+        <v>7659032531</v>
       </c>
       <c r="EM9" t="inlineStr"/>
       <c r="EN9" t="inlineStr"/>
-      <c r="EO9" t="inlineStr">
-        <is>
-          <t>Minimally invasive</t>
-        </is>
-      </c>
+      <c r="EO9" t="inlineStr"/>
       <c r="EP9" t="inlineStr"/>
-      <c r="EQ9" t="inlineStr"/>
-      <c r="ER9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="ES9" t="inlineStr">
-        <is>
-          <t>MUSR0008</t>
-        </is>
-      </c>
-      <c r="ET9" t="inlineStr">
-        <is>
-          <t>MUSR0008</t>
-        </is>
-      </c>
+      <c r="EQ9" t="n">
+        <v>1</v>
+      </c>
+      <c r="ER9" t="n">
+        <v>1</v>
+      </c>
+      <c r="ES9" t="n">
+        <v>1</v>
+      </c>
+      <c r="ET9" t="inlineStr"/>
       <c r="EU9" t="inlineStr"/>
-      <c r="EV9" t="inlineStr">
-        <is>
-          <t>2026-01-20</t>
-        </is>
-      </c>
+      <c r="EV9" t="inlineStr"/>
       <c r="EW9" t="inlineStr"/>
       <c r="EX9" t="inlineStr"/>
-      <c r="EY9" t="inlineStr">
-        <is>
-          <t>Hindu</t>
-        </is>
-      </c>
+      <c r="EY9" t="inlineStr"/>
       <c r="EZ9" t="inlineStr"/>
       <c r="FA9" t="inlineStr"/>
-      <c r="FB9" t="inlineStr">
-        <is>
-          <t>sri indu college of engineering &amp; technology</t>
-        </is>
-      </c>
-      <c r="FC9" t="inlineStr"/>
-      <c r="FD9" t="inlineStr">
-        <is>
-          <t>Upper</t>
-        </is>
-      </c>
-      <c r="FE9" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
-      </c>
-      <c r="FF9" t="n">
+      <c r="FB9" t="inlineStr"/>
+      <c r="FC9" t="n">
         <v>1</v>
       </c>
-      <c r="FG9" t="inlineStr">
-        <is>
-          <t>SC</t>
-        </is>
-      </c>
-      <c r="FH9" t="inlineStr"/>
-      <c r="FI9" t="inlineStr"/>
+      <c r="FD9" t="inlineStr"/>
+      <c r="FE9" t="n">
+        <v>1</v>
+      </c>
+      <c r="FF9" t="inlineStr">
+        <is>
+          <t>Mucharla Sreelekha</t>
+        </is>
+      </c>
+      <c r="FG9" t="n">
+        <v>1</v>
+      </c>
+      <c r="FH9" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="FI9" t="inlineStr">
+        <is>
+          <t>Very easy</t>
+        </is>
+      </c>
       <c r="FJ9" t="inlineStr"/>
       <c r="FK9" t="inlineStr"/>
-      <c r="FL9" t="n">
+      <c r="FL9" t="inlineStr"/>
+      <c r="FM9" t="n">
+        <v>1</v>
+      </c>
+      <c r="FN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FR9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS9" t="inlineStr"/>
+      <c r="FT9" t="inlineStr"/>
+      <c r="FU9" t="inlineStr">
+        <is>
+          <t>Daily</t>
+        </is>
+      </c>
+      <c r="FV9" t="inlineStr"/>
+      <c r="FW9" t="inlineStr">
+        <is>
+          <t>Highly portable</t>
+        </is>
+      </c>
+      <c r="FX9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="FY9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="FZ9" t="inlineStr">
+        <is>
+          <t>Always</t>
+        </is>
+      </c>
+      <c r="GA9" t="inlineStr">
+        <is>
+          <t>Very safe</t>
+        </is>
+      </c>
+      <c r="GB9" t="inlineStr"/>
+      <c r="GC9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="GD9" t="inlineStr"/>
+      <c r="GE9" t="inlineStr"/>
+      <c r="GF9" t="inlineStr"/>
+      <c r="GG9" t="inlineStr"/>
+      <c r="GH9" t="inlineStr">
+        <is>
+          <t>Minimally invasive</t>
+        </is>
+      </c>
+      <c r="GI9" t="inlineStr"/>
+      <c r="GJ9" t="inlineStr"/>
+      <c r="GK9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="GL9" t="inlineStr">
+        <is>
+          <t>MUSR0008</t>
+        </is>
+      </c>
+      <c r="GM9" t="inlineStr">
+        <is>
+          <t>MUSR0008</t>
+        </is>
+      </c>
+      <c r="GN9" t="inlineStr"/>
+      <c r="GO9" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="GP9" t="inlineStr"/>
+      <c r="GQ9" t="inlineStr"/>
+      <c r="GR9" t="inlineStr"/>
+      <c r="GS9" t="inlineStr">
+        <is>
+          <t>Hindu</t>
+        </is>
+      </c>
+      <c r="GT9" t="inlineStr"/>
+      <c r="GU9" t="inlineStr"/>
+      <c r="GV9" t="inlineStr"/>
+      <c r="GW9" t="inlineStr">
+        <is>
+          <t>sri indu college of engineering &amp; technology</t>
+        </is>
+      </c>
+      <c r="GX9" t="inlineStr"/>
+      <c r="GY9" t="inlineStr">
+        <is>
+          <t>Upper</t>
+        </is>
+      </c>
+      <c r="GZ9" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="HA9" t="n">
+        <v>1</v>
+      </c>
+      <c r="HB9" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="HC9" t="inlineStr"/>
+      <c r="HD9" t="inlineStr"/>
+      <c r="HE9" t="inlineStr"/>
+      <c r="HF9" t="inlineStr"/>
+      <c r="HG9" t="inlineStr"/>
+      <c r="HH9" t="n">
         <v>40</v>
       </c>
-      <c r="FM9" t="inlineStr"/>
-      <c r="FN9" t="inlineStr">
+      <c r="HI9" t="inlineStr"/>
+      <c r="HJ9" t="inlineStr"/>
+      <c r="HK9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -3619,6 +4244,55 @@
       <c r="FL10" t="inlineStr"/>
       <c r="FM10" t="inlineStr"/>
       <c r="FN10" t="inlineStr"/>
+      <c r="FO10" t="inlineStr"/>
+      <c r="FP10" t="inlineStr"/>
+      <c r="FQ10" t="inlineStr"/>
+      <c r="FR10" t="inlineStr"/>
+      <c r="FS10" t="inlineStr"/>
+      <c r="FT10" t="inlineStr"/>
+      <c r="FU10" t="inlineStr"/>
+      <c r="FV10" t="inlineStr"/>
+      <c r="FW10" t="inlineStr"/>
+      <c r="FX10" t="inlineStr"/>
+      <c r="FY10" t="inlineStr"/>
+      <c r="FZ10" t="inlineStr"/>
+      <c r="GA10" t="inlineStr"/>
+      <c r="GB10" t="inlineStr"/>
+      <c r="GC10" t="inlineStr"/>
+      <c r="GD10" t="inlineStr"/>
+      <c r="GE10" t="inlineStr"/>
+      <c r="GF10" t="inlineStr"/>
+      <c r="GG10" t="inlineStr"/>
+      <c r="GH10" t="inlineStr"/>
+      <c r="GI10" t="inlineStr"/>
+      <c r="GJ10" t="inlineStr"/>
+      <c r="GK10" t="inlineStr"/>
+      <c r="GL10" t="inlineStr"/>
+      <c r="GM10" t="inlineStr"/>
+      <c r="GN10" t="inlineStr"/>
+      <c r="GO10" t="inlineStr"/>
+      <c r="GP10" t="inlineStr"/>
+      <c r="GQ10" t="inlineStr"/>
+      <c r="GR10" t="inlineStr"/>
+      <c r="GS10" t="inlineStr"/>
+      <c r="GT10" t="inlineStr"/>
+      <c r="GU10" t="inlineStr"/>
+      <c r="GV10" t="inlineStr"/>
+      <c r="GW10" t="inlineStr"/>
+      <c r="GX10" t="inlineStr"/>
+      <c r="GY10" t="inlineStr"/>
+      <c r="GZ10" t="inlineStr"/>
+      <c r="HA10" t="inlineStr"/>
+      <c r="HB10" t="inlineStr"/>
+      <c r="HC10" t="inlineStr"/>
+      <c r="HD10" t="inlineStr"/>
+      <c r="HE10" t="inlineStr"/>
+      <c r="HF10" t="inlineStr"/>
+      <c r="HG10" t="inlineStr"/>
+      <c r="HH10" t="inlineStr"/>
+      <c r="HI10" t="inlineStr"/>
+      <c r="HJ10" t="inlineStr"/>
+      <c r="HK10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -3815,6 +4489,55 @@
       <c r="FL11" t="inlineStr"/>
       <c r="FM11" t="inlineStr"/>
       <c r="FN11" t="inlineStr"/>
+      <c r="FO11" t="inlineStr"/>
+      <c r="FP11" t="inlineStr"/>
+      <c r="FQ11" t="inlineStr"/>
+      <c r="FR11" t="inlineStr"/>
+      <c r="FS11" t="inlineStr"/>
+      <c r="FT11" t="inlineStr"/>
+      <c r="FU11" t="inlineStr"/>
+      <c r="FV11" t="inlineStr"/>
+      <c r="FW11" t="inlineStr"/>
+      <c r="FX11" t="inlineStr"/>
+      <c r="FY11" t="inlineStr"/>
+      <c r="FZ11" t="inlineStr"/>
+      <c r="GA11" t="inlineStr"/>
+      <c r="GB11" t="inlineStr"/>
+      <c r="GC11" t="inlineStr"/>
+      <c r="GD11" t="inlineStr"/>
+      <c r="GE11" t="inlineStr"/>
+      <c r="GF11" t="inlineStr"/>
+      <c r="GG11" t="inlineStr"/>
+      <c r="GH11" t="inlineStr"/>
+      <c r="GI11" t="inlineStr"/>
+      <c r="GJ11" t="inlineStr"/>
+      <c r="GK11" t="inlineStr"/>
+      <c r="GL11" t="inlineStr"/>
+      <c r="GM11" t="inlineStr"/>
+      <c r="GN11" t="inlineStr"/>
+      <c r="GO11" t="inlineStr"/>
+      <c r="GP11" t="inlineStr"/>
+      <c r="GQ11" t="inlineStr"/>
+      <c r="GR11" t="inlineStr"/>
+      <c r="GS11" t="inlineStr"/>
+      <c r="GT11" t="inlineStr"/>
+      <c r="GU11" t="inlineStr"/>
+      <c r="GV11" t="inlineStr"/>
+      <c r="GW11" t="inlineStr"/>
+      <c r="GX11" t="inlineStr"/>
+      <c r="GY11" t="inlineStr"/>
+      <c r="GZ11" t="inlineStr"/>
+      <c r="HA11" t="inlineStr"/>
+      <c r="HB11" t="inlineStr"/>
+      <c r="HC11" t="inlineStr"/>
+      <c r="HD11" t="inlineStr"/>
+      <c r="HE11" t="inlineStr"/>
+      <c r="HF11" t="inlineStr"/>
+      <c r="HG11" t="inlineStr"/>
+      <c r="HH11" t="inlineStr"/>
+      <c r="HI11" t="inlineStr"/>
+      <c r="HJ11" t="inlineStr"/>
+      <c r="HK11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -4011,6 +4734,55 @@
       <c r="FL12" t="inlineStr"/>
       <c r="FM12" t="inlineStr"/>
       <c r="FN12" t="inlineStr"/>
+      <c r="FO12" t="inlineStr"/>
+      <c r="FP12" t="inlineStr"/>
+      <c r="FQ12" t="inlineStr"/>
+      <c r="FR12" t="inlineStr"/>
+      <c r="FS12" t="inlineStr"/>
+      <c r="FT12" t="inlineStr"/>
+      <c r="FU12" t="inlineStr"/>
+      <c r="FV12" t="inlineStr"/>
+      <c r="FW12" t="inlineStr"/>
+      <c r="FX12" t="inlineStr"/>
+      <c r="FY12" t="inlineStr"/>
+      <c r="FZ12" t="inlineStr"/>
+      <c r="GA12" t="inlineStr"/>
+      <c r="GB12" t="inlineStr"/>
+      <c r="GC12" t="inlineStr"/>
+      <c r="GD12" t="inlineStr"/>
+      <c r="GE12" t="inlineStr"/>
+      <c r="GF12" t="inlineStr"/>
+      <c r="GG12" t="inlineStr"/>
+      <c r="GH12" t="inlineStr"/>
+      <c r="GI12" t="inlineStr"/>
+      <c r="GJ12" t="inlineStr"/>
+      <c r="GK12" t="inlineStr"/>
+      <c r="GL12" t="inlineStr"/>
+      <c r="GM12" t="inlineStr"/>
+      <c r="GN12" t="inlineStr"/>
+      <c r="GO12" t="inlineStr"/>
+      <c r="GP12" t="inlineStr"/>
+      <c r="GQ12" t="inlineStr"/>
+      <c r="GR12" t="inlineStr"/>
+      <c r="GS12" t="inlineStr"/>
+      <c r="GT12" t="inlineStr"/>
+      <c r="GU12" t="inlineStr"/>
+      <c r="GV12" t="inlineStr"/>
+      <c r="GW12" t="inlineStr"/>
+      <c r="GX12" t="inlineStr"/>
+      <c r="GY12" t="inlineStr"/>
+      <c r="GZ12" t="inlineStr"/>
+      <c r="HA12" t="inlineStr"/>
+      <c r="HB12" t="inlineStr"/>
+      <c r="HC12" t="inlineStr"/>
+      <c r="HD12" t="inlineStr"/>
+      <c r="HE12" t="inlineStr"/>
+      <c r="HF12" t="inlineStr"/>
+      <c r="HG12" t="inlineStr"/>
+      <c r="HH12" t="inlineStr"/>
+      <c r="HI12" t="inlineStr"/>
+      <c r="HJ12" t="inlineStr"/>
+      <c r="HK12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -4207,6 +4979,55 @@
       <c r="FL13" t="inlineStr"/>
       <c r="FM13" t="inlineStr"/>
       <c r="FN13" t="inlineStr"/>
+      <c r="FO13" t="inlineStr"/>
+      <c r="FP13" t="inlineStr"/>
+      <c r="FQ13" t="inlineStr"/>
+      <c r="FR13" t="inlineStr"/>
+      <c r="FS13" t="inlineStr"/>
+      <c r="FT13" t="inlineStr"/>
+      <c r="FU13" t="inlineStr"/>
+      <c r="FV13" t="inlineStr"/>
+      <c r="FW13" t="inlineStr"/>
+      <c r="FX13" t="inlineStr"/>
+      <c r="FY13" t="inlineStr"/>
+      <c r="FZ13" t="inlineStr"/>
+      <c r="GA13" t="inlineStr"/>
+      <c r="GB13" t="inlineStr"/>
+      <c r="GC13" t="inlineStr"/>
+      <c r="GD13" t="inlineStr"/>
+      <c r="GE13" t="inlineStr"/>
+      <c r="GF13" t="inlineStr"/>
+      <c r="GG13" t="inlineStr"/>
+      <c r="GH13" t="inlineStr"/>
+      <c r="GI13" t="inlineStr"/>
+      <c r="GJ13" t="inlineStr"/>
+      <c r="GK13" t="inlineStr"/>
+      <c r="GL13" t="inlineStr"/>
+      <c r="GM13" t="inlineStr"/>
+      <c r="GN13" t="inlineStr"/>
+      <c r="GO13" t="inlineStr"/>
+      <c r="GP13" t="inlineStr"/>
+      <c r="GQ13" t="inlineStr"/>
+      <c r="GR13" t="inlineStr"/>
+      <c r="GS13" t="inlineStr"/>
+      <c r="GT13" t="inlineStr"/>
+      <c r="GU13" t="inlineStr"/>
+      <c r="GV13" t="inlineStr"/>
+      <c r="GW13" t="inlineStr"/>
+      <c r="GX13" t="inlineStr"/>
+      <c r="GY13" t="inlineStr"/>
+      <c r="GZ13" t="inlineStr"/>
+      <c r="HA13" t="inlineStr"/>
+      <c r="HB13" t="inlineStr"/>
+      <c r="HC13" t="inlineStr"/>
+      <c r="HD13" t="inlineStr"/>
+      <c r="HE13" t="inlineStr"/>
+      <c r="HF13" t="inlineStr"/>
+      <c r="HG13" t="inlineStr"/>
+      <c r="HH13" t="inlineStr"/>
+      <c r="HI13" t="inlineStr"/>
+      <c r="HJ13" t="inlineStr"/>
+      <c r="HK13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -4255,94 +5076,94 @@
       </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="n">
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="n">
         <v>1</v>
       </c>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr">
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr">
         <is>
           <t>Anaemic</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr"/>
-      <c r="S14" t="inlineStr"/>
       <c r="T14" t="inlineStr"/>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="U14" t="inlineStr"/>
       <c r="V14" t="inlineStr"/>
-      <c r="W14" t="inlineStr"/>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="X14" t="inlineStr"/>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="Y14" t="inlineStr"/>
       <c r="Z14" t="inlineStr"/>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>Vegetarian</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr">
         <is>
+          <t>Vegetarian</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr"/>
+      <c r="AE14" t="inlineStr">
+        <is>
           <t>2020-07-24</t>
         </is>
       </c>
-      <c r="AD14" t="inlineStr"/>
-      <c r="AE14" t="n">
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="n">
         <v>7</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
-      <c r="AG14" t="inlineStr"/>
       <c r="AH14" t="inlineStr"/>
-      <c r="AI14" t="n">
+      <c r="AI14" t="inlineStr"/>
+      <c r="AJ14" t="inlineStr"/>
+      <c r="AK14" t="n">
         <v>12</v>
       </c>
-      <c r="AJ14" t="inlineStr"/>
-      <c r="AK14" t="inlineStr"/>
-      <c r="AL14" t="inlineStr">
+      <c r="AL14" t="inlineStr"/>
+      <c r="AM14" t="inlineStr"/>
+      <c r="AN14" t="inlineStr">
         <is>
           <t>Nuclear</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
+      <c r="AO14" t="inlineStr">
         <is>
           <t>Daily</t>
         </is>
       </c>
-      <c r="AN14" t="inlineStr">
+      <c r="AP14" t="inlineStr">
         <is>
           <t>Daily</t>
         </is>
       </c>
-      <c r="AO14" t="inlineStr">
+      <c r="AQ14" t="inlineStr">
         <is>
           <t>Daily</t>
         </is>
       </c>
-      <c r="AP14" t="inlineStr">
+      <c r="AR14" t="inlineStr">
         <is>
           <t>Daily</t>
         </is>
       </c>
-      <c r="AQ14" t="inlineStr">
+      <c r="AS14" t="inlineStr">
         <is>
           <t>Daily</t>
         </is>
       </c>
-      <c r="AR14" t="inlineStr">
+      <c r="AT14" t="inlineStr">
         <is>
           <t>Daily</t>
         </is>
       </c>
-      <c r="AS14" t="inlineStr"/>
-      <c r="AT14" t="inlineStr"/>
       <c r="AU14" t="inlineStr"/>
       <c r="AV14" t="inlineStr"/>
       <c r="AW14" t="inlineStr"/>
@@ -4353,90 +5174,82 @@
       <c r="BB14" t="inlineStr"/>
       <c r="BC14" t="inlineStr"/>
       <c r="BD14" t="inlineStr"/>
-      <c r="BE14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="BF14" t="n">
+      <c r="BE14" t="inlineStr"/>
+      <c r="BF14" t="inlineStr"/>
+      <c r="BG14" t="inlineStr"/>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BI14" t="n">
         <v>25</v>
       </c>
-      <c r="BG14" t="inlineStr"/>
-      <c r="BH14" t="n">
+      <c r="BJ14" t="inlineStr"/>
+      <c r="BK14" t="n">
         <v>1</v>
       </c>
-      <c r="BI14" t="inlineStr">
+      <c r="BL14" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="BJ14" t="inlineStr">
+      <c r="BM14" t="inlineStr">
         <is>
           <t>Very easy</t>
         </is>
       </c>
-      <c r="BK14" t="inlineStr"/>
-      <c r="BL14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN14" t="n">
+      <c r="BN14" t="inlineStr"/>
+      <c r="BO14" t="inlineStr"/>
+      <c r="BP14" t="inlineStr"/>
+      <c r="BQ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS14" t="n">
         <v>2</v>
       </c>
-      <c r="BO14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP14" t="n">
+      <c r="BT14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU14" t="n">
         <v>2</v>
       </c>
-      <c r="BQ14" t="n">
+      <c r="BV14" t="n">
         <v>4</v>
       </c>
-      <c r="BR14" t="inlineStr"/>
-      <c r="BS14" t="inlineStr">
+      <c r="BW14" t="inlineStr"/>
+      <c r="BX14" t="inlineStr">
         <is>
           <t>Daily</t>
-        </is>
-      </c>
-      <c r="BT14" t="inlineStr">
-        <is>
-          <t>Highly portable</t>
-        </is>
-      </c>
-      <c r="BU14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="BV14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="BW14" t="inlineStr">
-        <is>
-          <t>Always</t>
-        </is>
-      </c>
-      <c r="BX14" t="inlineStr">
-        <is>
-          <t>Very safe</t>
         </is>
       </c>
       <c r="BY14" t="inlineStr"/>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="CA14" t="inlineStr"/>
-      <c r="CB14" t="inlineStr"/>
-      <c r="CC14" t="inlineStr"/>
+          <t>Highly portable</t>
+        </is>
+      </c>
+      <c r="CA14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CB14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CC14" t="inlineStr">
+        <is>
+          <t>Always</t>
+        </is>
+      </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>Urban</t>
+          <t>Very safe</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr"/>
@@ -4447,258 +5260,315 @@
       </c>
       <c r="CG14" t="inlineStr"/>
       <c r="CH14" t="inlineStr"/>
-      <c r="CI14" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
+      <c r="CI14" t="inlineStr"/>
       <c r="CJ14" t="inlineStr">
         <is>
-          <t>Very easy</t>
+          <t>Urban</t>
         </is>
       </c>
       <c r="CK14" t="inlineStr"/>
-      <c r="CL14" t="n">
-        <v>1</v>
-      </c>
-      <c r="CM14" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN14" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO14" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP14" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="CR14" t="n">
-        <v>0</v>
-      </c>
-      <c r="CS14" t="inlineStr">
-        <is>
-          <t>Daily</t>
-        </is>
-      </c>
-      <c r="CT14" t="inlineStr">
-        <is>
-          <t>Highly portable</t>
-        </is>
-      </c>
-      <c r="CU14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="CL14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CM14" t="inlineStr"/>
+      <c r="CN14" t="inlineStr"/>
+      <c r="CO14" t="inlineStr"/>
+      <c r="CP14" t="inlineStr"/>
+      <c r="CQ14" t="inlineStr"/>
+      <c r="CR14" t="inlineStr"/>
+      <c r="CS14" t="inlineStr"/>
+      <c r="CT14" t="inlineStr"/>
+      <c r="CU14" t="inlineStr"/>
       <c r="CV14" t="inlineStr"/>
       <c r="CW14" t="inlineStr"/>
       <c r="CX14" t="inlineStr"/>
       <c r="CY14" t="inlineStr"/>
-      <c r="CZ14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="DA14" t="inlineStr">
-        <is>
-          <t>Always</t>
-        </is>
-      </c>
-      <c r="DB14" t="inlineStr">
-        <is>
-          <t>Very safe</t>
-        </is>
-      </c>
+      <c r="CZ14" t="inlineStr"/>
+      <c r="DA14" t="inlineStr"/>
+      <c r="DB14" t="inlineStr"/>
       <c r="DC14" t="inlineStr"/>
-      <c r="DD14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="DD14" t="inlineStr"/>
       <c r="DE14" t="inlineStr"/>
-      <c r="DF14" t="inlineStr">
-        <is>
-          <t>Masimo Rad-67</t>
-        </is>
-      </c>
+      <c r="DF14" t="inlineStr"/>
       <c r="DG14" t="inlineStr"/>
       <c r="DH14" t="inlineStr"/>
-      <c r="DI14" t="n">
-        <v>6</v>
-      </c>
+      <c r="DI14" t="inlineStr"/>
       <c r="DJ14" t="inlineStr"/>
       <c r="DK14" t="inlineStr"/>
-      <c r="DL14" t="n">
-        <v>1</v>
-      </c>
-      <c r="DM14" t="n">
-        <v>1</v>
-      </c>
-      <c r="DN14" t="n">
-        <v>1</v>
-      </c>
-      <c r="DO14" t="n">
-        <v>3</v>
-      </c>
-      <c r="DP14" t="n">
-        <v>22</v>
-      </c>
+      <c r="DL14" t="inlineStr"/>
+      <c r="DM14" t="inlineStr"/>
+      <c r="DN14" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="DO14" t="inlineStr">
+        <is>
+          <t>Very easy</t>
+        </is>
+      </c>
+      <c r="DP14" t="inlineStr"/>
       <c r="DQ14" t="n">
         <v>1</v>
       </c>
-      <c r="DR14" t="inlineStr">
-        <is>
-          <t>kirthi</t>
-        </is>
+      <c r="DR14" t="n">
+        <v>0</v>
       </c>
       <c r="DS14" t="n">
-        <v>1</v>
-      </c>
-      <c r="DT14" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="DU14" t="inlineStr">
-        <is>
-          <t>Very easy</t>
-        </is>
-      </c>
-      <c r="DV14" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="DT14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV14" t="n">
+        <v>0</v>
+      </c>
       <c r="DW14" t="n">
-        <v>1</v>
-      </c>
-      <c r="DX14" t="n">
-        <v>0</v>
-      </c>
-      <c r="DY14" t="n">
-        <v>0</v>
-      </c>
-      <c r="DZ14" t="n">
-        <v>2</v>
-      </c>
-      <c r="EA14" t="n">
-        <v>0</v>
-      </c>
-      <c r="EB14" t="n">
-        <v>0</v>
-      </c>
-      <c r="EC14" t="n">
-        <v>2</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="DX14" t="inlineStr">
+        <is>
+          <t>Daily</t>
+        </is>
+      </c>
+      <c r="DY14" t="inlineStr">
+        <is>
+          <t>Highly portable</t>
+        </is>
+      </c>
+      <c r="DZ14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="EA14" t="inlineStr"/>
+      <c r="EB14" t="inlineStr"/>
+      <c r="EC14" t="inlineStr"/>
       <c r="ED14" t="inlineStr"/>
       <c r="EE14" t="inlineStr">
         <is>
-          <t>Daily</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="EF14" t="inlineStr">
         <is>
-          <t>Highly portable</t>
+          <t>Always</t>
         </is>
       </c>
       <c r="EG14" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="EH14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>Very safe</t>
+        </is>
+      </c>
+      <c r="EH14" t="inlineStr"/>
       <c r="EI14" t="inlineStr">
         <is>
-          <t>Always</t>
-        </is>
-      </c>
-      <c r="EJ14" t="inlineStr">
-        <is>
-          <t>Very safe</t>
-        </is>
-      </c>
-      <c r="EK14" t="inlineStr"/>
-      <c r="EL14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="EJ14" t="inlineStr"/>
+      <c r="EK14" t="inlineStr">
+        <is>
+          <t>Masimo Rad-67</t>
+        </is>
+      </c>
+      <c r="EL14" t="inlineStr"/>
       <c r="EM14" t="inlineStr"/>
-      <c r="EN14" t="inlineStr"/>
-      <c r="EO14" t="inlineStr">
-        <is>
-          <t>Non-invasive</t>
-        </is>
-      </c>
+      <c r="EN14" t="n">
+        <v>6</v>
+      </c>
+      <c r="EO14" t="inlineStr"/>
       <c r="EP14" t="inlineStr"/>
-      <c r="EQ14" t="inlineStr"/>
-      <c r="ER14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="ES14" t="inlineStr">
-        <is>
-          <t>KR240720MWEH</t>
-        </is>
-      </c>
-      <c r="ET14" t="inlineStr">
-        <is>
-          <t>KR240720MWEH</t>
-        </is>
-      </c>
-      <c r="EU14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="EQ14" t="n">
+        <v>1</v>
+      </c>
+      <c r="ER14" t="n">
+        <v>1</v>
+      </c>
+      <c r="ES14" t="n">
+        <v>1</v>
+      </c>
+      <c r="ET14" t="inlineStr"/>
+      <c r="EU14" t="inlineStr"/>
       <c r="EV14" t="inlineStr"/>
-      <c r="EW14" t="inlineStr">
-        <is>
-          <t>PHC</t>
-        </is>
-      </c>
+      <c r="EW14" t="inlineStr"/>
       <c r="EX14" t="inlineStr"/>
-      <c r="EY14" t="inlineStr">
-        <is>
-          <t>Hindu</t>
-        </is>
-      </c>
+      <c r="EY14" t="inlineStr"/>
       <c r="EZ14" t="inlineStr"/>
       <c r="FA14" t="inlineStr"/>
-      <c r="FB14" t="inlineStr">
-        <is>
-          <t>westside</t>
-        </is>
-      </c>
-      <c r="FC14" t="inlineStr"/>
-      <c r="FD14" t="inlineStr">
-        <is>
-          <t>Upper Middle</t>
-        </is>
-      </c>
-      <c r="FE14" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-      <c r="FF14" t="inlineStr"/>
-      <c r="FG14" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="FH14" t="inlineStr"/>
-      <c r="FI14" t="inlineStr"/>
+      <c r="FB14" t="inlineStr"/>
+      <c r="FC14" t="n">
+        <v>3</v>
+      </c>
+      <c r="FD14" t="n">
+        <v>22</v>
+      </c>
+      <c r="FE14" t="n">
+        <v>1</v>
+      </c>
+      <c r="FF14" t="inlineStr">
+        <is>
+          <t>kirthi</t>
+        </is>
+      </c>
+      <c r="FG14" t="n">
+        <v>1</v>
+      </c>
+      <c r="FH14" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="FI14" t="inlineStr">
+        <is>
+          <t>Very easy</t>
+        </is>
+      </c>
       <c r="FJ14" t="inlineStr"/>
       <c r="FK14" t="inlineStr"/>
       <c r="FL14" t="inlineStr"/>
-      <c r="FM14" t="inlineStr"/>
-      <c r="FN14" t="inlineStr">
+      <c r="FM14" t="n">
+        <v>1</v>
+      </c>
+      <c r="FN14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP14" t="n">
+        <v>2</v>
+      </c>
+      <c r="FQ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FR14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS14" t="n">
+        <v>2</v>
+      </c>
+      <c r="FT14" t="inlineStr"/>
+      <c r="FU14" t="inlineStr">
+        <is>
+          <t>Daily</t>
+        </is>
+      </c>
+      <c r="FV14" t="inlineStr"/>
+      <c r="FW14" t="inlineStr">
+        <is>
+          <t>Highly portable</t>
+        </is>
+      </c>
+      <c r="FX14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="FY14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="FZ14" t="inlineStr">
+        <is>
+          <t>Always</t>
+        </is>
+      </c>
+      <c r="GA14" t="inlineStr">
+        <is>
+          <t>Very safe</t>
+        </is>
+      </c>
+      <c r="GB14" t="inlineStr"/>
+      <c r="GC14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="GD14" t="inlineStr"/>
+      <c r="GE14" t="inlineStr"/>
+      <c r="GF14" t="inlineStr"/>
+      <c r="GG14" t="inlineStr"/>
+      <c r="GH14" t="inlineStr">
+        <is>
+          <t>Non-invasive</t>
+        </is>
+      </c>
+      <c r="GI14" t="inlineStr"/>
+      <c r="GJ14" t="inlineStr"/>
+      <c r="GK14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="GL14" t="inlineStr">
+        <is>
+          <t>KR240720MWEH</t>
+        </is>
+      </c>
+      <c r="GM14" t="inlineStr">
+        <is>
+          <t>KR240720MWEH</t>
+        </is>
+      </c>
+      <c r="GN14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="GO14" t="inlineStr"/>
+      <c r="GP14" t="inlineStr">
+        <is>
+          <t>PHC</t>
+        </is>
+      </c>
+      <c r="GQ14" t="inlineStr"/>
+      <c r="GR14" t="inlineStr"/>
+      <c r="GS14" t="inlineStr">
+        <is>
+          <t>Hindu</t>
+        </is>
+      </c>
+      <c r="GT14" t="inlineStr"/>
+      <c r="GU14" t="inlineStr"/>
+      <c r="GV14" t="inlineStr"/>
+      <c r="GW14" t="inlineStr">
+        <is>
+          <t>westside</t>
+        </is>
+      </c>
+      <c r="GX14" t="inlineStr"/>
+      <c r="GY14" t="inlineStr">
+        <is>
+          <t>Upper Middle</t>
+        </is>
+      </c>
+      <c r="GZ14" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="HA14" t="inlineStr"/>
+      <c r="HB14" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="HC14" t="inlineStr"/>
+      <c r="HD14" t="inlineStr"/>
+      <c r="HE14" t="inlineStr"/>
+      <c r="HF14" t="inlineStr"/>
+      <c r="HG14" t="inlineStr"/>
+      <c r="HH14" t="inlineStr"/>
+      <c r="HI14" t="inlineStr"/>
+      <c r="HJ14" t="inlineStr"/>
+      <c r="HK14" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -4751,94 +5621,94 @@
       </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="n">
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="n">
         <v>1</v>
       </c>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr">
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr">
         <is>
           <t>Anaemic</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr"/>
-      <c r="S15" t="inlineStr"/>
       <c r="T15" t="inlineStr"/>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="U15" t="inlineStr"/>
       <c r="V15" t="inlineStr"/>
-      <c r="W15" t="inlineStr"/>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="X15" t="inlineStr"/>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="Y15" t="inlineStr"/>
       <c r="Z15" t="inlineStr"/>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>Vegetarian</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr">
         <is>
+          <t>Vegetarian</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr"/>
+      <c r="AE15" t="inlineStr">
+        <is>
           <t>2021-06-16</t>
         </is>
       </c>
-      <c r="AD15" t="inlineStr"/>
-      <c r="AE15" t="n">
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="n">
         <v>7</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
-      <c r="AG15" t="inlineStr"/>
       <c r="AH15" t="inlineStr"/>
-      <c r="AI15" t="n">
+      <c r="AI15" t="inlineStr"/>
+      <c r="AJ15" t="inlineStr"/>
+      <c r="AK15" t="n">
         <v>12</v>
       </c>
-      <c r="AJ15" t="inlineStr"/>
-      <c r="AK15" t="inlineStr"/>
-      <c r="AL15" t="inlineStr">
+      <c r="AL15" t="inlineStr"/>
+      <c r="AM15" t="inlineStr"/>
+      <c r="AN15" t="inlineStr">
         <is>
           <t>Nuclear</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
+      <c r="AO15" t="inlineStr">
         <is>
           <t>Daily</t>
         </is>
       </c>
-      <c r="AN15" t="inlineStr">
+      <c r="AP15" t="inlineStr">
         <is>
           <t>Daily</t>
         </is>
       </c>
-      <c r="AO15" t="inlineStr">
+      <c r="AQ15" t="inlineStr">
         <is>
           <t>Daily</t>
         </is>
       </c>
-      <c r="AP15" t="inlineStr">
+      <c r="AR15" t="inlineStr">
         <is>
           <t>Daily</t>
         </is>
       </c>
-      <c r="AQ15" t="inlineStr">
+      <c r="AS15" t="inlineStr">
         <is>
           <t>Daily</t>
         </is>
       </c>
-      <c r="AR15" t="inlineStr">
+      <c r="AT15" t="inlineStr">
         <is>
           <t>Daily</t>
         </is>
       </c>
-      <c r="AS15" t="inlineStr"/>
-      <c r="AT15" t="inlineStr"/>
       <c r="AU15" t="inlineStr"/>
       <c r="AV15" t="inlineStr"/>
       <c r="AW15" t="inlineStr"/>
@@ -4849,88 +5719,80 @@
       <c r="BB15" t="inlineStr"/>
       <c r="BC15" t="inlineStr"/>
       <c r="BD15" t="inlineStr"/>
-      <c r="BE15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="BE15" t="inlineStr"/>
       <c r="BF15" t="inlineStr"/>
       <c r="BG15" t="inlineStr"/>
-      <c r="BH15" t="n">
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BI15" t="inlineStr"/>
+      <c r="BJ15" t="inlineStr"/>
+      <c r="BK15" t="n">
         <v>1</v>
       </c>
-      <c r="BI15" t="inlineStr">
+      <c r="BL15" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="BJ15" t="inlineStr">
+      <c r="BM15" t="inlineStr">
         <is>
           <t>Very easy</t>
         </is>
       </c>
-      <c r="BK15" t="inlineStr"/>
-      <c r="BL15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP15" t="n">
-        <v>0</v>
-      </c>
+      <c r="BN15" t="inlineStr"/>
+      <c r="BO15" t="inlineStr"/>
+      <c r="BP15" t="inlineStr"/>
       <c r="BQ15" t="n">
         <v>0</v>
       </c>
-      <c r="BR15" t="inlineStr"/>
-      <c r="BS15" t="inlineStr">
+      <c r="BR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW15" t="inlineStr"/>
+      <c r="BX15" t="inlineStr">
         <is>
           <t>Daily</t>
-        </is>
-      </c>
-      <c r="BT15" t="inlineStr">
-        <is>
-          <t>Highly portable</t>
-        </is>
-      </c>
-      <c r="BU15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="BV15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="BW15" t="inlineStr">
-        <is>
-          <t>Always</t>
-        </is>
-      </c>
-      <c r="BX15" t="inlineStr">
-        <is>
-          <t>Very safe</t>
         </is>
       </c>
       <c r="BY15" t="inlineStr"/>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="CA15" t="inlineStr"/>
-      <c r="CB15" t="inlineStr"/>
-      <c r="CC15" t="inlineStr"/>
+          <t>Highly portable</t>
+        </is>
+      </c>
+      <c r="CA15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CB15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CC15" t="inlineStr">
+        <is>
+          <t>Always</t>
+        </is>
+      </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>Urban</t>
+          <t>Very safe</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr"/>
@@ -4941,252 +5803,309 @@
       </c>
       <c r="CG15" t="inlineStr"/>
       <c r="CH15" t="inlineStr"/>
-      <c r="CI15" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
+      <c r="CI15" t="inlineStr"/>
       <c r="CJ15" t="inlineStr">
         <is>
-          <t>Very easy</t>
+          <t>Urban</t>
         </is>
       </c>
       <c r="CK15" t="inlineStr"/>
-      <c r="CL15" t="n">
-        <v>1</v>
-      </c>
-      <c r="CM15" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN15" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO15" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP15" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="CR15" t="n">
-        <v>0</v>
-      </c>
-      <c r="CS15" t="inlineStr">
-        <is>
-          <t>Daily</t>
-        </is>
-      </c>
-      <c r="CT15" t="inlineStr">
-        <is>
-          <t>Highly portable</t>
-        </is>
-      </c>
-      <c r="CU15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="CL15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CM15" t="inlineStr"/>
+      <c r="CN15" t="inlineStr"/>
+      <c r="CO15" t="inlineStr"/>
+      <c r="CP15" t="inlineStr"/>
+      <c r="CQ15" t="inlineStr"/>
+      <c r="CR15" t="inlineStr"/>
+      <c r="CS15" t="inlineStr"/>
+      <c r="CT15" t="inlineStr"/>
+      <c r="CU15" t="inlineStr"/>
       <c r="CV15" t="inlineStr"/>
       <c r="CW15" t="inlineStr"/>
       <c r="CX15" t="inlineStr"/>
       <c r="CY15" t="inlineStr"/>
-      <c r="CZ15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="DA15" t="inlineStr">
-        <is>
-          <t>Always</t>
-        </is>
-      </c>
-      <c r="DB15" t="inlineStr">
-        <is>
-          <t>Very safe</t>
-        </is>
-      </c>
+      <c r="CZ15" t="inlineStr"/>
+      <c r="DA15" t="inlineStr"/>
+      <c r="DB15" t="inlineStr"/>
       <c r="DC15" t="inlineStr"/>
-      <c r="DD15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="DD15" t="inlineStr"/>
       <c r="DE15" t="inlineStr"/>
-      <c r="DF15" t="inlineStr">
-        <is>
-          <t>Masimo Rad-67</t>
-        </is>
-      </c>
+      <c r="DF15" t="inlineStr"/>
       <c r="DG15" t="inlineStr"/>
       <c r="DH15" t="inlineStr"/>
-      <c r="DI15" t="n">
-        <v>10</v>
-      </c>
+      <c r="DI15" t="inlineStr"/>
       <c r="DJ15" t="inlineStr"/>
       <c r="DK15" t="inlineStr"/>
-      <c r="DL15" t="n">
-        <v>1</v>
-      </c>
-      <c r="DM15" t="n">
-        <v>1</v>
-      </c>
-      <c r="DN15" t="n">
-        <v>1</v>
-      </c>
-      <c r="DO15" t="n">
-        <v>1</v>
+      <c r="DL15" t="inlineStr"/>
+      <c r="DM15" t="inlineStr"/>
+      <c r="DN15" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="DO15" t="inlineStr">
+        <is>
+          <t>Very easy</t>
+        </is>
       </c>
       <c r="DP15" t="inlineStr"/>
       <c r="DQ15" t="n">
         <v>1</v>
       </c>
-      <c r="DR15" t="inlineStr">
-        <is>
-          <t>Praneeth</t>
-        </is>
+      <c r="DR15" t="n">
+        <v>0</v>
       </c>
       <c r="DS15" t="n">
-        <v>1</v>
-      </c>
-      <c r="DT15" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="DU15" t="inlineStr">
-        <is>
-          <t>Very easy</t>
-        </is>
-      </c>
-      <c r="DV15" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="DT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV15" t="n">
+        <v>0</v>
+      </c>
       <c r="DW15" t="n">
-        <v>1</v>
-      </c>
-      <c r="DX15" t="n">
-        <v>0</v>
-      </c>
-      <c r="DY15" t="n">
-        <v>0</v>
-      </c>
-      <c r="DZ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="EA15" t="n">
-        <v>0</v>
-      </c>
-      <c r="EB15" t="n">
-        <v>0</v>
-      </c>
-      <c r="EC15" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="DX15" t="inlineStr">
+        <is>
+          <t>Daily</t>
+        </is>
+      </c>
+      <c r="DY15" t="inlineStr">
+        <is>
+          <t>Highly portable</t>
+        </is>
+      </c>
+      <c r="DZ15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="EA15" t="inlineStr"/>
+      <c r="EB15" t="inlineStr"/>
+      <c r="EC15" t="inlineStr"/>
       <c r="ED15" t="inlineStr"/>
       <c r="EE15" t="inlineStr">
         <is>
-          <t>Daily</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="EF15" t="inlineStr">
         <is>
-          <t>Highly portable</t>
+          <t>Always</t>
         </is>
       </c>
       <c r="EG15" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="EH15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>Very safe</t>
+        </is>
+      </c>
+      <c r="EH15" t="inlineStr"/>
       <c r="EI15" t="inlineStr">
         <is>
-          <t>Always</t>
-        </is>
-      </c>
-      <c r="EJ15" t="inlineStr">
-        <is>
-          <t>Very safe</t>
-        </is>
-      </c>
-      <c r="EK15" t="inlineStr"/>
-      <c r="EL15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="EJ15" t="inlineStr"/>
+      <c r="EK15" t="inlineStr">
+        <is>
+          <t>Masimo Rad-67</t>
+        </is>
+      </c>
+      <c r="EL15" t="inlineStr"/>
       <c r="EM15" t="inlineStr"/>
-      <c r="EN15" t="inlineStr"/>
-      <c r="EO15" t="inlineStr">
-        <is>
-          <t>Non-invasive</t>
-        </is>
-      </c>
+      <c r="EN15" t="n">
+        <v>10</v>
+      </c>
+      <c r="EO15" t="inlineStr"/>
       <c r="EP15" t="inlineStr"/>
-      <c r="EQ15" t="inlineStr"/>
-      <c r="ER15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="ES15" t="inlineStr">
-        <is>
-          <t>PS160621MWEH</t>
-        </is>
-      </c>
-      <c r="ET15" t="inlineStr">
-        <is>
-          <t>PS160621MWEH</t>
-        </is>
-      </c>
-      <c r="EU15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="EQ15" t="n">
+        <v>1</v>
+      </c>
+      <c r="ER15" t="n">
+        <v>1</v>
+      </c>
+      <c r="ES15" t="n">
+        <v>1</v>
+      </c>
+      <c r="ET15" t="inlineStr"/>
+      <c r="EU15" t="inlineStr"/>
       <c r="EV15" t="inlineStr"/>
-      <c r="EW15" t="inlineStr">
-        <is>
-          <t>PHC</t>
-        </is>
-      </c>
+      <c r="EW15" t="inlineStr"/>
       <c r="EX15" t="inlineStr"/>
-      <c r="EY15" t="inlineStr">
-        <is>
-          <t>Hindu</t>
-        </is>
-      </c>
+      <c r="EY15" t="inlineStr"/>
       <c r="EZ15" t="inlineStr"/>
       <c r="FA15" t="inlineStr"/>
-      <c r="FB15" t="inlineStr">
-        <is>
-          <t>westside</t>
-        </is>
-      </c>
-      <c r="FC15" t="inlineStr"/>
+      <c r="FB15" t="inlineStr"/>
+      <c r="FC15" t="n">
+        <v>1</v>
+      </c>
       <c r="FD15" t="inlineStr"/>
-      <c r="FE15" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-      <c r="FF15" t="inlineStr"/>
-      <c r="FG15" t="inlineStr">
-        <is>
-          <t>SC</t>
-        </is>
-      </c>
-      <c r="FH15" t="inlineStr"/>
-      <c r="FI15" t="inlineStr"/>
+      <c r="FE15" t="n">
+        <v>1</v>
+      </c>
+      <c r="FF15" t="inlineStr">
+        <is>
+          <t>Praneeth</t>
+        </is>
+      </c>
+      <c r="FG15" t="n">
+        <v>1</v>
+      </c>
+      <c r="FH15" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="FI15" t="inlineStr">
+        <is>
+          <t>Very easy</t>
+        </is>
+      </c>
       <c r="FJ15" t="inlineStr"/>
       <c r="FK15" t="inlineStr"/>
       <c r="FL15" t="inlineStr"/>
-      <c r="FM15" t="inlineStr"/>
-      <c r="FN15" t="inlineStr">
+      <c r="FM15" t="n">
+        <v>1</v>
+      </c>
+      <c r="FN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT15" t="inlineStr"/>
+      <c r="FU15" t="inlineStr">
+        <is>
+          <t>Daily</t>
+        </is>
+      </c>
+      <c r="FV15" t="inlineStr"/>
+      <c r="FW15" t="inlineStr">
+        <is>
+          <t>Highly portable</t>
+        </is>
+      </c>
+      <c r="FX15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="FY15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="FZ15" t="inlineStr">
+        <is>
+          <t>Always</t>
+        </is>
+      </c>
+      <c r="GA15" t="inlineStr">
+        <is>
+          <t>Very safe</t>
+        </is>
+      </c>
+      <c r="GB15" t="inlineStr"/>
+      <c r="GC15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="GD15" t="inlineStr"/>
+      <c r="GE15" t="inlineStr"/>
+      <c r="GF15" t="inlineStr"/>
+      <c r="GG15" t="inlineStr"/>
+      <c r="GH15" t="inlineStr">
+        <is>
+          <t>Non-invasive</t>
+        </is>
+      </c>
+      <c r="GI15" t="inlineStr"/>
+      <c r="GJ15" t="inlineStr"/>
+      <c r="GK15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="GL15" t="inlineStr">
+        <is>
+          <t>PS160621MWEH</t>
+        </is>
+      </c>
+      <c r="GM15" t="inlineStr">
+        <is>
+          <t>PS160621MWEH</t>
+        </is>
+      </c>
+      <c r="GN15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="GO15" t="inlineStr"/>
+      <c r="GP15" t="inlineStr">
+        <is>
+          <t>PHC</t>
+        </is>
+      </c>
+      <c r="GQ15" t="inlineStr"/>
+      <c r="GR15" t="inlineStr"/>
+      <c r="GS15" t="inlineStr">
+        <is>
+          <t>Hindu</t>
+        </is>
+      </c>
+      <c r="GT15" t="inlineStr"/>
+      <c r="GU15" t="inlineStr"/>
+      <c r="GV15" t="inlineStr"/>
+      <c r="GW15" t="inlineStr">
+        <is>
+          <t>westside</t>
+        </is>
+      </c>
+      <c r="GX15" t="inlineStr"/>
+      <c r="GY15" t="inlineStr"/>
+      <c r="GZ15" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="HA15" t="inlineStr"/>
+      <c r="HB15" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="HC15" t="inlineStr"/>
+      <c r="HD15" t="inlineStr"/>
+      <c r="HE15" t="inlineStr"/>
+      <c r="HF15" t="inlineStr"/>
+      <c r="HG15" t="inlineStr"/>
+      <c r="HH15" t="inlineStr"/>
+      <c r="HI15" t="inlineStr"/>
+      <c r="HJ15" t="inlineStr"/>
+      <c r="HK15" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -5387,6 +6306,55 @@
       <c r="FL16" t="inlineStr"/>
       <c r="FM16" t="inlineStr"/>
       <c r="FN16" t="inlineStr"/>
+      <c r="FO16" t="inlineStr"/>
+      <c r="FP16" t="inlineStr"/>
+      <c r="FQ16" t="inlineStr"/>
+      <c r="FR16" t="inlineStr"/>
+      <c r="FS16" t="inlineStr"/>
+      <c r="FT16" t="inlineStr"/>
+      <c r="FU16" t="inlineStr"/>
+      <c r="FV16" t="inlineStr"/>
+      <c r="FW16" t="inlineStr"/>
+      <c r="FX16" t="inlineStr"/>
+      <c r="FY16" t="inlineStr"/>
+      <c r="FZ16" t="inlineStr"/>
+      <c r="GA16" t="inlineStr"/>
+      <c r="GB16" t="inlineStr"/>
+      <c r="GC16" t="inlineStr"/>
+      <c r="GD16" t="inlineStr"/>
+      <c r="GE16" t="inlineStr"/>
+      <c r="GF16" t="inlineStr"/>
+      <c r="GG16" t="inlineStr"/>
+      <c r="GH16" t="inlineStr"/>
+      <c r="GI16" t="inlineStr"/>
+      <c r="GJ16" t="inlineStr"/>
+      <c r="GK16" t="inlineStr"/>
+      <c r="GL16" t="inlineStr"/>
+      <c r="GM16" t="inlineStr"/>
+      <c r="GN16" t="inlineStr"/>
+      <c r="GO16" t="inlineStr"/>
+      <c r="GP16" t="inlineStr"/>
+      <c r="GQ16" t="inlineStr"/>
+      <c r="GR16" t="inlineStr"/>
+      <c r="GS16" t="inlineStr"/>
+      <c r="GT16" t="inlineStr"/>
+      <c r="GU16" t="inlineStr"/>
+      <c r="GV16" t="inlineStr"/>
+      <c r="GW16" t="inlineStr"/>
+      <c r="GX16" t="inlineStr"/>
+      <c r="GY16" t="inlineStr"/>
+      <c r="GZ16" t="inlineStr"/>
+      <c r="HA16" t="inlineStr"/>
+      <c r="HB16" t="inlineStr"/>
+      <c r="HC16" t="inlineStr"/>
+      <c r="HD16" t="inlineStr"/>
+      <c r="HE16" t="inlineStr"/>
+      <c r="HF16" t="inlineStr"/>
+      <c r="HG16" t="inlineStr"/>
+      <c r="HH16" t="inlineStr"/>
+      <c r="HI16" t="inlineStr"/>
+      <c r="HJ16" t="inlineStr"/>
+      <c r="HK16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -5583,6 +6551,55 @@
       <c r="FL17" t="inlineStr"/>
       <c r="FM17" t="inlineStr"/>
       <c r="FN17" t="inlineStr"/>
+      <c r="FO17" t="inlineStr"/>
+      <c r="FP17" t="inlineStr"/>
+      <c r="FQ17" t="inlineStr"/>
+      <c r="FR17" t="inlineStr"/>
+      <c r="FS17" t="inlineStr"/>
+      <c r="FT17" t="inlineStr"/>
+      <c r="FU17" t="inlineStr"/>
+      <c r="FV17" t="inlineStr"/>
+      <c r="FW17" t="inlineStr"/>
+      <c r="FX17" t="inlineStr"/>
+      <c r="FY17" t="inlineStr"/>
+      <c r="FZ17" t="inlineStr"/>
+      <c r="GA17" t="inlineStr"/>
+      <c r="GB17" t="inlineStr"/>
+      <c r="GC17" t="inlineStr"/>
+      <c r="GD17" t="inlineStr"/>
+      <c r="GE17" t="inlineStr"/>
+      <c r="GF17" t="inlineStr"/>
+      <c r="GG17" t="inlineStr"/>
+      <c r="GH17" t="inlineStr"/>
+      <c r="GI17" t="inlineStr"/>
+      <c r="GJ17" t="inlineStr"/>
+      <c r="GK17" t="inlineStr"/>
+      <c r="GL17" t="inlineStr"/>
+      <c r="GM17" t="inlineStr"/>
+      <c r="GN17" t="inlineStr"/>
+      <c r="GO17" t="inlineStr"/>
+      <c r="GP17" t="inlineStr"/>
+      <c r="GQ17" t="inlineStr"/>
+      <c r="GR17" t="inlineStr"/>
+      <c r="GS17" t="inlineStr"/>
+      <c r="GT17" t="inlineStr"/>
+      <c r="GU17" t="inlineStr"/>
+      <c r="GV17" t="inlineStr"/>
+      <c r="GW17" t="inlineStr"/>
+      <c r="GX17" t="inlineStr"/>
+      <c r="GY17" t="inlineStr"/>
+      <c r="GZ17" t="inlineStr"/>
+      <c r="HA17" t="inlineStr"/>
+      <c r="HB17" t="inlineStr"/>
+      <c r="HC17" t="inlineStr"/>
+      <c r="HD17" t="inlineStr"/>
+      <c r="HE17" t="inlineStr"/>
+      <c r="HF17" t="inlineStr"/>
+      <c r="HG17" t="inlineStr"/>
+      <c r="HH17" t="inlineStr"/>
+      <c r="HI17" t="inlineStr"/>
+      <c r="HJ17" t="inlineStr"/>
+      <c r="HK17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -5779,6 +6796,55 @@
       <c r="FL18" t="inlineStr"/>
       <c r="FM18" t="inlineStr"/>
       <c r="FN18" t="inlineStr"/>
+      <c r="FO18" t="inlineStr"/>
+      <c r="FP18" t="inlineStr"/>
+      <c r="FQ18" t="inlineStr"/>
+      <c r="FR18" t="inlineStr"/>
+      <c r="FS18" t="inlineStr"/>
+      <c r="FT18" t="inlineStr"/>
+      <c r="FU18" t="inlineStr"/>
+      <c r="FV18" t="inlineStr"/>
+      <c r="FW18" t="inlineStr"/>
+      <c r="FX18" t="inlineStr"/>
+      <c r="FY18" t="inlineStr"/>
+      <c r="FZ18" t="inlineStr"/>
+      <c r="GA18" t="inlineStr"/>
+      <c r="GB18" t="inlineStr"/>
+      <c r="GC18" t="inlineStr"/>
+      <c r="GD18" t="inlineStr"/>
+      <c r="GE18" t="inlineStr"/>
+      <c r="GF18" t="inlineStr"/>
+      <c r="GG18" t="inlineStr"/>
+      <c r="GH18" t="inlineStr"/>
+      <c r="GI18" t="inlineStr"/>
+      <c r="GJ18" t="inlineStr"/>
+      <c r="GK18" t="inlineStr"/>
+      <c r="GL18" t="inlineStr"/>
+      <c r="GM18" t="inlineStr"/>
+      <c r="GN18" t="inlineStr"/>
+      <c r="GO18" t="inlineStr"/>
+      <c r="GP18" t="inlineStr"/>
+      <c r="GQ18" t="inlineStr"/>
+      <c r="GR18" t="inlineStr"/>
+      <c r="GS18" t="inlineStr"/>
+      <c r="GT18" t="inlineStr"/>
+      <c r="GU18" t="inlineStr"/>
+      <c r="GV18" t="inlineStr"/>
+      <c r="GW18" t="inlineStr"/>
+      <c r="GX18" t="inlineStr"/>
+      <c r="GY18" t="inlineStr"/>
+      <c r="GZ18" t="inlineStr"/>
+      <c r="HA18" t="inlineStr"/>
+      <c r="HB18" t="inlineStr"/>
+      <c r="HC18" t="inlineStr"/>
+      <c r="HD18" t="inlineStr"/>
+      <c r="HE18" t="inlineStr"/>
+      <c r="HF18" t="inlineStr"/>
+      <c r="HG18" t="inlineStr"/>
+      <c r="HH18" t="inlineStr"/>
+      <c r="HI18" t="inlineStr"/>
+      <c r="HJ18" t="inlineStr"/>
+      <c r="HK18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -5975,6 +7041,55 @@
       <c r="FL19" t="inlineStr"/>
       <c r="FM19" t="inlineStr"/>
       <c r="FN19" t="inlineStr"/>
+      <c r="FO19" t="inlineStr"/>
+      <c r="FP19" t="inlineStr"/>
+      <c r="FQ19" t="inlineStr"/>
+      <c r="FR19" t="inlineStr"/>
+      <c r="FS19" t="inlineStr"/>
+      <c r="FT19" t="inlineStr"/>
+      <c r="FU19" t="inlineStr"/>
+      <c r="FV19" t="inlineStr"/>
+      <c r="FW19" t="inlineStr"/>
+      <c r="FX19" t="inlineStr"/>
+      <c r="FY19" t="inlineStr"/>
+      <c r="FZ19" t="inlineStr"/>
+      <c r="GA19" t="inlineStr"/>
+      <c r="GB19" t="inlineStr"/>
+      <c r="GC19" t="inlineStr"/>
+      <c r="GD19" t="inlineStr"/>
+      <c r="GE19" t="inlineStr"/>
+      <c r="GF19" t="inlineStr"/>
+      <c r="GG19" t="inlineStr"/>
+      <c r="GH19" t="inlineStr"/>
+      <c r="GI19" t="inlineStr"/>
+      <c r="GJ19" t="inlineStr"/>
+      <c r="GK19" t="inlineStr"/>
+      <c r="GL19" t="inlineStr"/>
+      <c r="GM19" t="inlineStr"/>
+      <c r="GN19" t="inlineStr"/>
+      <c r="GO19" t="inlineStr"/>
+      <c r="GP19" t="inlineStr"/>
+      <c r="GQ19" t="inlineStr"/>
+      <c r="GR19" t="inlineStr"/>
+      <c r="GS19" t="inlineStr"/>
+      <c r="GT19" t="inlineStr"/>
+      <c r="GU19" t="inlineStr"/>
+      <c r="GV19" t="inlineStr"/>
+      <c r="GW19" t="inlineStr"/>
+      <c r="GX19" t="inlineStr"/>
+      <c r="GY19" t="inlineStr"/>
+      <c r="GZ19" t="inlineStr"/>
+      <c r="HA19" t="inlineStr"/>
+      <c r="HB19" t="inlineStr"/>
+      <c r="HC19" t="inlineStr"/>
+      <c r="HD19" t="inlineStr"/>
+      <c r="HE19" t="inlineStr"/>
+      <c r="HF19" t="inlineStr"/>
+      <c r="HG19" t="inlineStr"/>
+      <c r="HH19" t="inlineStr"/>
+      <c r="HI19" t="inlineStr"/>
+      <c r="HJ19" t="inlineStr"/>
+      <c r="HK19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -6171,6 +7286,55 @@
       <c r="FL20" t="inlineStr"/>
       <c r="FM20" t="inlineStr"/>
       <c r="FN20" t="inlineStr"/>
+      <c r="FO20" t="inlineStr"/>
+      <c r="FP20" t="inlineStr"/>
+      <c r="FQ20" t="inlineStr"/>
+      <c r="FR20" t="inlineStr"/>
+      <c r="FS20" t="inlineStr"/>
+      <c r="FT20" t="inlineStr"/>
+      <c r="FU20" t="inlineStr"/>
+      <c r="FV20" t="inlineStr"/>
+      <c r="FW20" t="inlineStr"/>
+      <c r="FX20" t="inlineStr"/>
+      <c r="FY20" t="inlineStr"/>
+      <c r="FZ20" t="inlineStr"/>
+      <c r="GA20" t="inlineStr"/>
+      <c r="GB20" t="inlineStr"/>
+      <c r="GC20" t="inlineStr"/>
+      <c r="GD20" t="inlineStr"/>
+      <c r="GE20" t="inlineStr"/>
+      <c r="GF20" t="inlineStr"/>
+      <c r="GG20" t="inlineStr"/>
+      <c r="GH20" t="inlineStr"/>
+      <c r="GI20" t="inlineStr"/>
+      <c r="GJ20" t="inlineStr"/>
+      <c r="GK20" t="inlineStr"/>
+      <c r="GL20" t="inlineStr"/>
+      <c r="GM20" t="inlineStr"/>
+      <c r="GN20" t="inlineStr"/>
+      <c r="GO20" t="inlineStr"/>
+      <c r="GP20" t="inlineStr"/>
+      <c r="GQ20" t="inlineStr"/>
+      <c r="GR20" t="inlineStr"/>
+      <c r="GS20" t="inlineStr"/>
+      <c r="GT20" t="inlineStr"/>
+      <c r="GU20" t="inlineStr"/>
+      <c r="GV20" t="inlineStr"/>
+      <c r="GW20" t="inlineStr"/>
+      <c r="GX20" t="inlineStr"/>
+      <c r="GY20" t="inlineStr"/>
+      <c r="GZ20" t="inlineStr"/>
+      <c r="HA20" t="inlineStr"/>
+      <c r="HB20" t="inlineStr"/>
+      <c r="HC20" t="inlineStr"/>
+      <c r="HD20" t="inlineStr"/>
+      <c r="HE20" t="inlineStr"/>
+      <c r="HF20" t="inlineStr"/>
+      <c r="HG20" t="inlineStr"/>
+      <c r="HH20" t="inlineStr"/>
+      <c r="HI20" t="inlineStr"/>
+      <c r="HJ20" t="inlineStr"/>
+      <c r="HK20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -6367,6 +7531,55 @@
       <c r="FL21" t="inlineStr"/>
       <c r="FM21" t="inlineStr"/>
       <c r="FN21" t="inlineStr"/>
+      <c r="FO21" t="inlineStr"/>
+      <c r="FP21" t="inlineStr"/>
+      <c r="FQ21" t="inlineStr"/>
+      <c r="FR21" t="inlineStr"/>
+      <c r="FS21" t="inlineStr"/>
+      <c r="FT21" t="inlineStr"/>
+      <c r="FU21" t="inlineStr"/>
+      <c r="FV21" t="inlineStr"/>
+      <c r="FW21" t="inlineStr"/>
+      <c r="FX21" t="inlineStr"/>
+      <c r="FY21" t="inlineStr"/>
+      <c r="FZ21" t="inlineStr"/>
+      <c r="GA21" t="inlineStr"/>
+      <c r="GB21" t="inlineStr"/>
+      <c r="GC21" t="inlineStr"/>
+      <c r="GD21" t="inlineStr"/>
+      <c r="GE21" t="inlineStr"/>
+      <c r="GF21" t="inlineStr"/>
+      <c r="GG21" t="inlineStr"/>
+      <c r="GH21" t="inlineStr"/>
+      <c r="GI21" t="inlineStr"/>
+      <c r="GJ21" t="inlineStr"/>
+      <c r="GK21" t="inlineStr"/>
+      <c r="GL21" t="inlineStr"/>
+      <c r="GM21" t="inlineStr"/>
+      <c r="GN21" t="inlineStr"/>
+      <c r="GO21" t="inlineStr"/>
+      <c r="GP21" t="inlineStr"/>
+      <c r="GQ21" t="inlineStr"/>
+      <c r="GR21" t="inlineStr"/>
+      <c r="GS21" t="inlineStr"/>
+      <c r="GT21" t="inlineStr"/>
+      <c r="GU21" t="inlineStr"/>
+      <c r="GV21" t="inlineStr"/>
+      <c r="GW21" t="inlineStr"/>
+      <c r="GX21" t="inlineStr"/>
+      <c r="GY21" t="inlineStr"/>
+      <c r="GZ21" t="inlineStr"/>
+      <c r="HA21" t="inlineStr"/>
+      <c r="HB21" t="inlineStr"/>
+      <c r="HC21" t="inlineStr"/>
+      <c r="HD21" t="inlineStr"/>
+      <c r="HE21" t="inlineStr"/>
+      <c r="HF21" t="inlineStr"/>
+      <c r="HG21" t="inlineStr"/>
+      <c r="HH21" t="inlineStr"/>
+      <c r="HI21" t="inlineStr"/>
+      <c r="HJ21" t="inlineStr"/>
+      <c r="HK21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -6563,6 +7776,55 @@
       <c r="FL22" t="inlineStr"/>
       <c r="FM22" t="inlineStr"/>
       <c r="FN22" t="inlineStr"/>
+      <c r="FO22" t="inlineStr"/>
+      <c r="FP22" t="inlineStr"/>
+      <c r="FQ22" t="inlineStr"/>
+      <c r="FR22" t="inlineStr"/>
+      <c r="FS22" t="inlineStr"/>
+      <c r="FT22" t="inlineStr"/>
+      <c r="FU22" t="inlineStr"/>
+      <c r="FV22" t="inlineStr"/>
+      <c r="FW22" t="inlineStr"/>
+      <c r="FX22" t="inlineStr"/>
+      <c r="FY22" t="inlineStr"/>
+      <c r="FZ22" t="inlineStr"/>
+      <c r="GA22" t="inlineStr"/>
+      <c r="GB22" t="inlineStr"/>
+      <c r="GC22" t="inlineStr"/>
+      <c r="GD22" t="inlineStr"/>
+      <c r="GE22" t="inlineStr"/>
+      <c r="GF22" t="inlineStr"/>
+      <c r="GG22" t="inlineStr"/>
+      <c r="GH22" t="inlineStr"/>
+      <c r="GI22" t="inlineStr"/>
+      <c r="GJ22" t="inlineStr"/>
+      <c r="GK22" t="inlineStr"/>
+      <c r="GL22" t="inlineStr"/>
+      <c r="GM22" t="inlineStr"/>
+      <c r="GN22" t="inlineStr"/>
+      <c r="GO22" t="inlineStr"/>
+      <c r="GP22" t="inlineStr"/>
+      <c r="GQ22" t="inlineStr"/>
+      <c r="GR22" t="inlineStr"/>
+      <c r="GS22" t="inlineStr"/>
+      <c r="GT22" t="inlineStr"/>
+      <c r="GU22" t="inlineStr"/>
+      <c r="GV22" t="inlineStr"/>
+      <c r="GW22" t="inlineStr"/>
+      <c r="GX22" t="inlineStr"/>
+      <c r="GY22" t="inlineStr"/>
+      <c r="GZ22" t="inlineStr"/>
+      <c r="HA22" t="inlineStr"/>
+      <c r="HB22" t="inlineStr"/>
+      <c r="HC22" t="inlineStr"/>
+      <c r="HD22" t="inlineStr"/>
+      <c r="HE22" t="inlineStr"/>
+      <c r="HF22" t="inlineStr"/>
+      <c r="HG22" t="inlineStr"/>
+      <c r="HH22" t="inlineStr"/>
+      <c r="HI22" t="inlineStr"/>
+      <c r="HJ22" t="inlineStr"/>
+      <c r="HK22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -6611,190 +7873,182 @@
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="n">
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="n">
         <v>1</v>
       </c>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr">
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr">
         <is>
           <t>Anaemic</t>
         </is>
       </c>
-      <c r="R23" t="inlineStr"/>
-      <c r="S23" t="inlineStr"/>
       <c r="T23" t="inlineStr"/>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="U23" t="inlineStr"/>
       <c r="V23" t="inlineStr"/>
-      <c r="W23" t="inlineStr"/>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="X23" t="inlineStr"/>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="Y23" t="inlineStr"/>
       <c r="Z23" t="inlineStr"/>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>Vegetarian</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr"/>
       <c r="AC23" t="inlineStr">
         <is>
+          <t>Vegetarian</t>
+        </is>
+      </c>
+      <c r="AD23" t="inlineStr"/>
+      <c r="AE23" t="inlineStr">
+        <is>
           <t>2022-07-15</t>
         </is>
       </c>
-      <c r="AD23" t="inlineStr"/>
-      <c r="AE23" t="n">
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="n">
         <v>7</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
-      <c r="AG23" t="inlineStr"/>
       <c r="AH23" t="inlineStr"/>
-      <c r="AI23" t="n">
+      <c r="AI23" t="inlineStr"/>
+      <c r="AJ23" t="inlineStr"/>
+      <c r="AK23" t="n">
         <v>12</v>
       </c>
-      <c r="AJ23" t="inlineStr"/>
-      <c r="AK23" t="inlineStr"/>
-      <c r="AL23" t="inlineStr">
+      <c r="AL23" t="inlineStr"/>
+      <c r="AM23" t="inlineStr"/>
+      <c r="AN23" t="inlineStr">
         <is>
           <t>Nuclear</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
+      <c r="AO23" t="inlineStr">
         <is>
           <t>Daily</t>
         </is>
       </c>
-      <c r="AN23" t="inlineStr">
+      <c r="AP23" t="inlineStr">
         <is>
           <t>Daily</t>
         </is>
       </c>
-      <c r="AO23" t="inlineStr">
+      <c r="AQ23" t="inlineStr">
         <is>
           <t>Daily</t>
         </is>
       </c>
-      <c r="AP23" t="inlineStr">
+      <c r="AR23" t="inlineStr">
         <is>
           <t>Daily</t>
         </is>
       </c>
-      <c r="AQ23" t="inlineStr">
+      <c r="AS23" t="inlineStr">
         <is>
           <t>Daily</t>
         </is>
       </c>
-      <c r="AR23" t="inlineStr">
+      <c r="AT23" t="inlineStr">
         <is>
           <t>Daily</t>
         </is>
       </c>
-      <c r="AS23" t="inlineStr"/>
-      <c r="AT23" t="inlineStr"/>
       <c r="AU23" t="inlineStr"/>
       <c r="AV23" t="inlineStr"/>
-      <c r="AW23" t="inlineStr">
-        <is>
-          <t>13+4</t>
-        </is>
-      </c>
+      <c r="AW23" t="inlineStr"/>
       <c r="AX23" t="inlineStr"/>
       <c r="AY23" t="inlineStr"/>
-      <c r="AZ23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>13+4</t>
+        </is>
+      </c>
       <c r="BA23" t="inlineStr"/>
       <c r="BB23" t="inlineStr"/>
       <c r="BC23" t="inlineStr"/>
       <c r="BD23" t="inlineStr"/>
-      <c r="BE23" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="BE23" t="inlineStr"/>
       <c r="BF23" t="inlineStr"/>
       <c r="BG23" t="inlineStr"/>
-      <c r="BH23" t="n">
+      <c r="BH23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BI23" t="inlineStr"/>
+      <c r="BJ23" t="inlineStr"/>
+      <c r="BK23" t="n">
         <v>1</v>
       </c>
-      <c r="BI23" t="inlineStr">
+      <c r="BL23" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="BJ23" t="inlineStr">
+      <c r="BM23" t="inlineStr">
         <is>
           <t>Very easy</t>
         </is>
       </c>
-      <c r="BK23" t="inlineStr"/>
-      <c r="BL23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP23" t="n">
-        <v>0</v>
-      </c>
+      <c r="BN23" t="inlineStr"/>
+      <c r="BO23" t="inlineStr"/>
+      <c r="BP23" t="inlineStr"/>
       <c r="BQ23" t="n">
         <v>0</v>
       </c>
-      <c r="BR23" t="inlineStr"/>
-      <c r="BS23" t="inlineStr">
+      <c r="BR23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW23" t="inlineStr"/>
+      <c r="BX23" t="inlineStr">
         <is>
           <t>Daily</t>
-        </is>
-      </c>
-      <c r="BT23" t="inlineStr">
-        <is>
-          <t>Highly portable</t>
-        </is>
-      </c>
-      <c r="BU23" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="BV23" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="BW23" t="inlineStr">
-        <is>
-          <t>Always</t>
-        </is>
-      </c>
-      <c r="BX23" t="inlineStr">
-        <is>
-          <t>Very safe</t>
         </is>
       </c>
       <c r="BY23" t="inlineStr"/>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="CA23" t="inlineStr"/>
-      <c r="CB23" t="inlineStr"/>
-      <c r="CC23" t="inlineStr"/>
+          <t>Highly portable</t>
+        </is>
+      </c>
+      <c r="CA23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CB23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CC23" t="inlineStr">
+        <is>
+          <t>Always</t>
+        </is>
+      </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>Urban</t>
+          <t>Very safe</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr"/>
@@ -6805,252 +8059,309 @@
       </c>
       <c r="CG23" t="inlineStr"/>
       <c r="CH23" t="inlineStr"/>
-      <c r="CI23" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
+      <c r="CI23" t="inlineStr"/>
       <c r="CJ23" t="inlineStr">
         <is>
-          <t>Very easy</t>
+          <t>Urban</t>
         </is>
       </c>
       <c r="CK23" t="inlineStr"/>
-      <c r="CL23" t="n">
-        <v>1</v>
-      </c>
-      <c r="CM23" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN23" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO23" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP23" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ23" t="n">
-        <v>0</v>
-      </c>
-      <c r="CR23" t="n">
-        <v>0</v>
-      </c>
-      <c r="CS23" t="inlineStr">
-        <is>
-          <t>Daily</t>
-        </is>
-      </c>
-      <c r="CT23" t="inlineStr">
-        <is>
-          <t>Highly portable</t>
-        </is>
-      </c>
-      <c r="CU23" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="CL23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CM23" t="inlineStr"/>
+      <c r="CN23" t="inlineStr"/>
+      <c r="CO23" t="inlineStr"/>
+      <c r="CP23" t="inlineStr"/>
+      <c r="CQ23" t="inlineStr"/>
+      <c r="CR23" t="inlineStr"/>
+      <c r="CS23" t="inlineStr"/>
+      <c r="CT23" t="inlineStr"/>
+      <c r="CU23" t="inlineStr"/>
       <c r="CV23" t="inlineStr"/>
       <c r="CW23" t="inlineStr"/>
       <c r="CX23" t="inlineStr"/>
       <c r="CY23" t="inlineStr"/>
-      <c r="CZ23" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="DA23" t="inlineStr">
-        <is>
-          <t>Always</t>
-        </is>
-      </c>
-      <c r="DB23" t="inlineStr">
-        <is>
-          <t>Very safe</t>
-        </is>
-      </c>
+      <c r="CZ23" t="inlineStr"/>
+      <c r="DA23" t="inlineStr"/>
+      <c r="DB23" t="inlineStr"/>
       <c r="DC23" t="inlineStr"/>
-      <c r="DD23" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="DD23" t="inlineStr"/>
       <c r="DE23" t="inlineStr"/>
-      <c r="DF23" t="inlineStr">
-        <is>
-          <t>Masimo Rad-67</t>
-        </is>
-      </c>
+      <c r="DF23" t="inlineStr"/>
       <c r="DG23" t="inlineStr"/>
       <c r="DH23" t="inlineStr"/>
-      <c r="DI23" t="n">
-        <v>10</v>
-      </c>
+      <c r="DI23" t="inlineStr"/>
       <c r="DJ23" t="inlineStr"/>
       <c r="DK23" t="inlineStr"/>
-      <c r="DL23" t="n">
-        <v>1</v>
-      </c>
-      <c r="DM23" t="n">
-        <v>1</v>
-      </c>
-      <c r="DN23" t="n">
-        <v>1</v>
-      </c>
-      <c r="DO23" t="n">
-        <v>1</v>
+      <c r="DL23" t="inlineStr"/>
+      <c r="DM23" t="inlineStr"/>
+      <c r="DN23" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="DO23" t="inlineStr">
+        <is>
+          <t>Very easy</t>
+        </is>
       </c>
       <c r="DP23" t="inlineStr"/>
       <c r="DQ23" t="n">
         <v>1</v>
       </c>
-      <c r="DR23" t="inlineStr">
-        <is>
-          <t>phani</t>
-        </is>
+      <c r="DR23" t="n">
+        <v>0</v>
       </c>
       <c r="DS23" t="n">
-        <v>1</v>
-      </c>
-      <c r="DT23" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="DU23" t="inlineStr">
-        <is>
-          <t>Very easy</t>
-        </is>
-      </c>
-      <c r="DV23" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="DT23" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU23" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV23" t="n">
+        <v>0</v>
+      </c>
       <c r="DW23" t="n">
-        <v>1</v>
-      </c>
-      <c r="DX23" t="n">
-        <v>0</v>
-      </c>
-      <c r="DY23" t="n">
-        <v>0</v>
-      </c>
-      <c r="DZ23" t="n">
-        <v>0</v>
-      </c>
-      <c r="EA23" t="n">
-        <v>0</v>
-      </c>
-      <c r="EB23" t="n">
-        <v>0</v>
-      </c>
-      <c r="EC23" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="DX23" t="inlineStr">
+        <is>
+          <t>Daily</t>
+        </is>
+      </c>
+      <c r="DY23" t="inlineStr">
+        <is>
+          <t>Highly portable</t>
+        </is>
+      </c>
+      <c r="DZ23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="EA23" t="inlineStr"/>
+      <c r="EB23" t="inlineStr"/>
+      <c r="EC23" t="inlineStr"/>
       <c r="ED23" t="inlineStr"/>
       <c r="EE23" t="inlineStr">
         <is>
-          <t>Daily</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="EF23" t="inlineStr">
         <is>
-          <t>Highly portable</t>
+          <t>Always</t>
         </is>
       </c>
       <c r="EG23" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="EH23" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>Very safe</t>
+        </is>
+      </c>
+      <c r="EH23" t="inlineStr"/>
       <c r="EI23" t="inlineStr">
         <is>
-          <t>Always</t>
-        </is>
-      </c>
-      <c r="EJ23" t="inlineStr">
-        <is>
-          <t>Very safe</t>
-        </is>
-      </c>
-      <c r="EK23" t="inlineStr"/>
-      <c r="EL23" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="EJ23" t="inlineStr"/>
+      <c r="EK23" t="inlineStr">
+        <is>
+          <t>Masimo Rad-67</t>
+        </is>
+      </c>
+      <c r="EL23" t="inlineStr"/>
       <c r="EM23" t="inlineStr"/>
-      <c r="EN23" t="inlineStr"/>
-      <c r="EO23" t="inlineStr">
-        <is>
-          <t>Non-invasive</t>
-        </is>
-      </c>
+      <c r="EN23" t="n">
+        <v>10</v>
+      </c>
+      <c r="EO23" t="inlineStr"/>
       <c r="EP23" t="inlineStr"/>
-      <c r="EQ23" t="inlineStr"/>
-      <c r="ER23" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="ES23" t="inlineStr">
-        <is>
-          <t>PK150722MSIA</t>
-        </is>
-      </c>
-      <c r="ET23" t="inlineStr">
-        <is>
-          <t>PK150722MSIA</t>
-        </is>
-      </c>
-      <c r="EU23" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="EQ23" t="n">
+        <v>1</v>
+      </c>
+      <c r="ER23" t="n">
+        <v>1</v>
+      </c>
+      <c r="ES23" t="n">
+        <v>1</v>
+      </c>
+      <c r="ET23" t="inlineStr"/>
+      <c r="EU23" t="inlineStr"/>
       <c r="EV23" t="inlineStr"/>
-      <c r="EW23" t="inlineStr">
-        <is>
-          <t>PHC</t>
-        </is>
-      </c>
+      <c r="EW23" t="inlineStr"/>
       <c r="EX23" t="inlineStr"/>
-      <c r="EY23" t="inlineStr">
-        <is>
-          <t>Hindu</t>
-        </is>
-      </c>
+      <c r="EY23" t="inlineStr"/>
       <c r="EZ23" t="inlineStr"/>
       <c r="FA23" t="inlineStr"/>
-      <c r="FB23" t="inlineStr">
-        <is>
-          <t>sri indu</t>
-        </is>
-      </c>
-      <c r="FC23" t="inlineStr"/>
+      <c r="FB23" t="inlineStr"/>
+      <c r="FC23" t="n">
+        <v>1</v>
+      </c>
       <c r="FD23" t="inlineStr"/>
-      <c r="FE23" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-      <c r="FF23" t="inlineStr"/>
-      <c r="FG23" t="inlineStr">
-        <is>
-          <t>SC</t>
-        </is>
-      </c>
-      <c r="FH23" t="inlineStr"/>
-      <c r="FI23" t="inlineStr"/>
+      <c r="FE23" t="n">
+        <v>1</v>
+      </c>
+      <c r="FF23" t="inlineStr">
+        <is>
+          <t>phani</t>
+        </is>
+      </c>
+      <c r="FG23" t="n">
+        <v>1</v>
+      </c>
+      <c r="FH23" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="FI23" t="inlineStr">
+        <is>
+          <t>Very easy</t>
+        </is>
+      </c>
       <c r="FJ23" t="inlineStr"/>
       <c r="FK23" t="inlineStr"/>
       <c r="FL23" t="inlineStr"/>
-      <c r="FM23" t="inlineStr"/>
-      <c r="FN23" t="inlineStr">
+      <c r="FM23" t="n">
+        <v>1</v>
+      </c>
+      <c r="FN23" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO23" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP23" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="FR23" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS23" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT23" t="inlineStr"/>
+      <c r="FU23" t="inlineStr">
+        <is>
+          <t>Daily</t>
+        </is>
+      </c>
+      <c r="FV23" t="inlineStr"/>
+      <c r="FW23" t="inlineStr">
+        <is>
+          <t>Highly portable</t>
+        </is>
+      </c>
+      <c r="FX23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="FY23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="FZ23" t="inlineStr">
+        <is>
+          <t>Always</t>
+        </is>
+      </c>
+      <c r="GA23" t="inlineStr">
+        <is>
+          <t>Very safe</t>
+        </is>
+      </c>
+      <c r="GB23" t="inlineStr"/>
+      <c r="GC23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="GD23" t="inlineStr"/>
+      <c r="GE23" t="inlineStr"/>
+      <c r="GF23" t="inlineStr"/>
+      <c r="GG23" t="inlineStr"/>
+      <c r="GH23" t="inlineStr">
+        <is>
+          <t>Non-invasive</t>
+        </is>
+      </c>
+      <c r="GI23" t="inlineStr"/>
+      <c r="GJ23" t="inlineStr"/>
+      <c r="GK23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="GL23" t="inlineStr">
+        <is>
+          <t>PK150722MSIA</t>
+        </is>
+      </c>
+      <c r="GM23" t="inlineStr">
+        <is>
+          <t>PK150722MSIA</t>
+        </is>
+      </c>
+      <c r="GN23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="GO23" t="inlineStr"/>
+      <c r="GP23" t="inlineStr">
+        <is>
+          <t>PHC</t>
+        </is>
+      </c>
+      <c r="GQ23" t="inlineStr"/>
+      <c r="GR23" t="inlineStr"/>
+      <c r="GS23" t="inlineStr">
+        <is>
+          <t>Hindu</t>
+        </is>
+      </c>
+      <c r="GT23" t="inlineStr"/>
+      <c r="GU23" t="inlineStr"/>
+      <c r="GV23" t="inlineStr"/>
+      <c r="GW23" t="inlineStr">
+        <is>
+          <t>sri indu</t>
+        </is>
+      </c>
+      <c r="GX23" t="inlineStr"/>
+      <c r="GY23" t="inlineStr"/>
+      <c r="GZ23" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="HA23" t="inlineStr"/>
+      <c r="HB23" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="HC23" t="inlineStr"/>
+      <c r="HD23" t="inlineStr"/>
+      <c r="HE23" t="inlineStr"/>
+      <c r="HF23" t="inlineStr"/>
+      <c r="HG23" t="inlineStr"/>
+      <c r="HH23" t="inlineStr"/>
+      <c r="HI23" t="inlineStr"/>
+      <c r="HJ23" t="inlineStr"/>
+      <c r="HK23" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -7088,19 +8399,41 @@
         </is>
       </c>
       <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>2026-03-02 22:06:22</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2310f7fb-2efe-41fe-afe5-4b5a5f105ed6</t>
+        </is>
+      </c>
       <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>2/3/2026, 10:05:50 pm</t>
+        </is>
+      </c>
+      <c r="L24" t="n">
+        <v>3</v>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>3 years 7 months 16 days</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr"/>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr"/>
       <c r="S24" t="inlineStr"/>
-      <c r="T24" t="inlineStr"/>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>JR140722MSIH</t>
+        </is>
+      </c>
       <c r="U24" t="inlineStr"/>
       <c r="V24" t="inlineStr"/>
       <c r="W24" t="inlineStr"/>
@@ -7111,8 +8444,16 @@
       <c r="AB24" t="inlineStr"/>
       <c r="AC24" t="inlineStr"/>
       <c r="AD24" t="inlineStr"/>
-      <c r="AE24" t="inlineStr"/>
-      <c r="AF24" t="inlineStr"/>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>2022-07-14</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="AG24" t="inlineStr"/>
       <c r="AH24" t="inlineStr"/>
       <c r="AI24" t="inlineStr"/>
@@ -7135,29 +8476,61 @@
       <c r="AZ24" t="inlineStr"/>
       <c r="BA24" t="inlineStr"/>
       <c r="BB24" t="inlineStr"/>
-      <c r="BC24" t="inlineStr"/>
+      <c r="BC24" t="inlineStr">
+        <is>
+          <t>Jahnavi</t>
+        </is>
+      </c>
       <c r="BD24" t="inlineStr"/>
-      <c r="BE24" t="inlineStr"/>
+      <c r="BE24" t="inlineStr">
+        <is>
+          <t>Jahnavi</t>
+        </is>
+      </c>
       <c r="BF24" t="inlineStr"/>
       <c r="BG24" t="inlineStr"/>
       <c r="BH24" t="inlineStr"/>
       <c r="BI24" t="inlineStr"/>
-      <c r="BJ24" t="inlineStr"/>
+      <c r="BJ24" t="n">
+        <v>29</v>
+      </c>
       <c r="BK24" t="inlineStr"/>
       <c r="BL24" t="inlineStr"/>
       <c r="BM24" t="inlineStr"/>
       <c r="BN24" t="inlineStr"/>
-      <c r="BO24" t="inlineStr"/>
-      <c r="BP24" t="inlineStr"/>
-      <c r="BQ24" t="inlineStr"/>
-      <c r="BR24" t="inlineStr"/>
-      <c r="BS24" t="inlineStr"/>
-      <c r="BT24" t="inlineStr"/>
-      <c r="BU24" t="inlineStr"/>
-      <c r="BV24" t="inlineStr"/>
+      <c r="BO24" t="inlineStr">
+        <is>
+          <t>Very easy</t>
+        </is>
+      </c>
+      <c r="BP24" t="inlineStr">
+        <is>
+          <t>&lt;1 min</t>
+        </is>
+      </c>
+      <c r="BQ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV24" t="n">
+        <v>0</v>
+      </c>
       <c r="BW24" t="inlineStr"/>
       <c r="BX24" t="inlineStr"/>
-      <c r="BY24" t="inlineStr"/>
+      <c r="BY24" t="n">
+        <v>1</v>
+      </c>
       <c r="BZ24" t="inlineStr"/>
       <c r="CA24" t="inlineStr"/>
       <c r="CB24" t="inlineStr"/>
@@ -7168,46 +8541,152 @@
       <c r="CG24" t="inlineStr"/>
       <c r="CH24" t="inlineStr"/>
       <c r="CI24" t="inlineStr"/>
-      <c r="CJ24" t="inlineStr"/>
+      <c r="CJ24" t="inlineStr">
+        <is>
+          <t>Urban</t>
+        </is>
+      </c>
       <c r="CK24" t="inlineStr"/>
       <c r="CL24" t="inlineStr"/>
-      <c r="CM24" t="inlineStr"/>
-      <c r="CN24" t="inlineStr"/>
+      <c r="CM24" t="inlineStr">
+        <is>
+          <t>Very easy</t>
+        </is>
+      </c>
+      <c r="CN24" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="CO24" t="inlineStr"/>
-      <c r="CP24" t="inlineStr"/>
-      <c r="CQ24" t="inlineStr"/>
-      <c r="CR24" t="inlineStr"/>
-      <c r="CS24" t="inlineStr"/>
-      <c r="CT24" t="inlineStr"/>
-      <c r="CU24" t="inlineStr"/>
-      <c r="CV24" t="inlineStr"/>
-      <c r="CW24" t="inlineStr"/>
-      <c r="CX24" t="inlineStr"/>
-      <c r="CY24" t="inlineStr"/>
-      <c r="CZ24" t="inlineStr"/>
-      <c r="DA24" t="inlineStr"/>
-      <c r="DB24" t="inlineStr"/>
-      <c r="DC24" t="inlineStr"/>
-      <c r="DD24" t="inlineStr"/>
-      <c r="DE24" t="inlineStr"/>
-      <c r="DF24" t="inlineStr"/>
-      <c r="DG24" t="inlineStr"/>
+      <c r="CP24" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="CQ24" t="inlineStr">
+        <is>
+          <t>Daily</t>
+        </is>
+      </c>
+      <c r="CR24" t="inlineStr">
+        <is>
+          <t>Easily available</t>
+        </is>
+      </c>
+      <c r="CS24" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CT24" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CU24" t="inlineStr">
+        <is>
+          <t>&lt;1 min</t>
+        </is>
+      </c>
+      <c r="CV24" t="inlineStr">
+        <is>
+          <t>Always</t>
+        </is>
+      </c>
+      <c r="CW24" t="inlineStr">
+        <is>
+          <t>Not affected</t>
+        </is>
+      </c>
+      <c r="CX24" t="inlineStr">
+        <is>
+          <t>Highly portable</t>
+        </is>
+      </c>
+      <c r="CY24" t="inlineStr">
+        <is>
+          <t>Battery operated</t>
+        </is>
+      </c>
+      <c r="CZ24" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="DA24" t="inlineStr">
+        <is>
+          <t>Daily</t>
+        </is>
+      </c>
+      <c r="DB24" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="DC24" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="DD24" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="DE24" t="inlineStr">
+        <is>
+          <t>Always</t>
+        </is>
+      </c>
+      <c r="DF24" t="inlineStr">
+        <is>
+          <t>Very safe</t>
+        </is>
+      </c>
+      <c r="DG24" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="DH24" t="inlineStr"/>
-      <c r="DI24" t="inlineStr"/>
-      <c r="DJ24" t="inlineStr"/>
-      <c r="DK24" t="inlineStr"/>
+      <c r="DI24" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="DJ24" t="n">
+        <v>1</v>
+      </c>
+      <c r="DK24" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="DL24" t="inlineStr"/>
       <c r="DM24" t="inlineStr"/>
       <c r="DN24" t="inlineStr"/>
       <c r="DO24" t="inlineStr"/>
       <c r="DP24" t="inlineStr"/>
       <c r="DQ24" t="inlineStr"/>
-      <c r="DR24" t="inlineStr"/>
-      <c r="DS24" t="inlineStr"/>
-      <c r="DT24" t="inlineStr"/>
-      <c r="DU24" t="inlineStr"/>
-      <c r="DV24" t="inlineStr"/>
-      <c r="DW24" t="inlineStr"/>
+      <c r="DR24" t="n">
+        <v>0</v>
+      </c>
+      <c r="DS24" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT24" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU24" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV24" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW24" t="n">
+        <v>0</v>
+      </c>
       <c r="DX24" t="inlineStr"/>
       <c r="DY24" t="inlineStr"/>
       <c r="DZ24" t="inlineStr"/>
@@ -7223,34 +8702,161 @@
       <c r="EJ24" t="inlineStr"/>
       <c r="EK24" t="inlineStr"/>
       <c r="EL24" t="inlineStr"/>
-      <c r="EM24" t="inlineStr"/>
+      <c r="EM24" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="EN24" t="inlineStr"/>
-      <c r="EO24" t="inlineStr"/>
+      <c r="EO24" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="EP24" t="inlineStr"/>
       <c r="EQ24" t="inlineStr"/>
       <c r="ER24" t="inlineStr"/>
       <c r="ES24" t="inlineStr"/>
-      <c r="ET24" t="inlineStr"/>
-      <c r="EU24" t="inlineStr"/>
-      <c r="EV24" t="inlineStr"/>
-      <c r="EW24" t="inlineStr"/>
-      <c r="EX24" t="inlineStr"/>
-      <c r="EY24" t="inlineStr"/>
-      <c r="EZ24" t="inlineStr"/>
-      <c r="FA24" t="inlineStr"/>
-      <c r="FB24" t="inlineStr"/>
+      <c r="ET24" t="n">
+        <v>1</v>
+      </c>
+      <c r="EU24" t="n">
+        <v>1</v>
+      </c>
+      <c r="EV24" t="n">
+        <v>1</v>
+      </c>
+      <c r="EW24" t="n">
+        <v>1</v>
+      </c>
+      <c r="EX24" t="n">
+        <v>1</v>
+      </c>
+      <c r="EY24" t="n">
+        <v>1</v>
+      </c>
+      <c r="EZ24" t="n">
+        <v>1</v>
+      </c>
+      <c r="FA24" t="n">
+        <v>1</v>
+      </c>
+      <c r="FB24" t="n">
+        <v>1</v>
+      </c>
       <c r="FC24" t="inlineStr"/>
-      <c r="FD24" t="inlineStr"/>
+      <c r="FD24" t="n">
+        <v>13</v>
+      </c>
       <c r="FE24" t="inlineStr"/>
-      <c r="FF24" t="inlineStr"/>
+      <c r="FF24" t="inlineStr">
+        <is>
+          <t>jhon</t>
+        </is>
+      </c>
       <c r="FG24" t="inlineStr"/>
       <c r="FH24" t="inlineStr"/>
       <c r="FI24" t="inlineStr"/>
       <c r="FJ24" t="inlineStr"/>
-      <c r="FK24" t="inlineStr"/>
-      <c r="FL24" t="inlineStr"/>
+      <c r="FK24" t="inlineStr">
+        <is>
+          <t>Very easy</t>
+        </is>
+      </c>
+      <c r="FL24" t="inlineStr">
+        <is>
+          <t>&lt;1 min</t>
+        </is>
+      </c>
       <c r="FM24" t="inlineStr"/>
-      <c r="FN24" t="inlineStr"/>
+      <c r="FN24" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO24" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP24" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="FR24" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS24" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT24" t="inlineStr"/>
+      <c r="FU24" t="inlineStr"/>
+      <c r="FV24" t="n">
+        <v>1</v>
+      </c>
+      <c r="FW24" t="inlineStr"/>
+      <c r="FX24" t="inlineStr"/>
+      <c r="FY24" t="inlineStr"/>
+      <c r="FZ24" t="inlineStr"/>
+      <c r="GA24" t="inlineStr"/>
+      <c r="GB24" t="inlineStr"/>
+      <c r="GC24" t="inlineStr"/>
+      <c r="GD24" t="inlineStr"/>
+      <c r="GE24" t="inlineStr"/>
+      <c r="GF24" t="inlineStr"/>
+      <c r="GG24" t="inlineStr"/>
+      <c r="GH24" t="inlineStr"/>
+      <c r="GI24" t="inlineStr"/>
+      <c r="GJ24" t="inlineStr"/>
+      <c r="GK24" t="inlineStr"/>
+      <c r="GL24" t="inlineStr"/>
+      <c r="GM24" t="inlineStr"/>
+      <c r="GN24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="GO24" t="inlineStr"/>
+      <c r="GP24" t="inlineStr"/>
+      <c r="GQ24" t="inlineStr"/>
+      <c r="GR24" t="inlineStr"/>
+      <c r="GS24" t="inlineStr"/>
+      <c r="GT24" t="inlineStr"/>
+      <c r="GU24" t="inlineStr"/>
+      <c r="GV24" t="inlineStr"/>
+      <c r="GW24" t="inlineStr">
+        <is>
+          <t>sri indu</t>
+        </is>
+      </c>
+      <c r="GX24" t="inlineStr">
+        <is>
+          <t>Upper</t>
+        </is>
+      </c>
+      <c r="GY24" t="inlineStr"/>
+      <c r="GZ24" t="inlineStr"/>
+      <c r="HA24" t="inlineStr"/>
+      <c r="HB24" t="inlineStr"/>
+      <c r="HC24" t="inlineStr"/>
+      <c r="HD24" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="HE24" t="inlineStr">
+        <is>
+          <t>2026-03-02 22:05:50</t>
+        </is>
+      </c>
+      <c r="HF24" t="inlineStr">
+        <is>
+          <t>JR140722MSIH</t>
+        </is>
+      </c>
+      <c r="HG24" t="inlineStr"/>
+      <c r="HH24" t="inlineStr"/>
+      <c r="HI24" t="inlineStr"/>
+      <c r="HJ24" t="inlineStr"/>
+      <c r="HK24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -7447,6 +9053,55 @@
       <c r="FL25" t="inlineStr"/>
       <c r="FM25" t="inlineStr"/>
       <c r="FN25" t="inlineStr"/>
+      <c r="FO25" t="inlineStr"/>
+      <c r="FP25" t="inlineStr"/>
+      <c r="FQ25" t="inlineStr"/>
+      <c r="FR25" t="inlineStr"/>
+      <c r="FS25" t="inlineStr"/>
+      <c r="FT25" t="inlineStr"/>
+      <c r="FU25" t="inlineStr"/>
+      <c r="FV25" t="inlineStr"/>
+      <c r="FW25" t="inlineStr"/>
+      <c r="FX25" t="inlineStr"/>
+      <c r="FY25" t="inlineStr"/>
+      <c r="FZ25" t="inlineStr"/>
+      <c r="GA25" t="inlineStr"/>
+      <c r="GB25" t="inlineStr"/>
+      <c r="GC25" t="inlineStr"/>
+      <c r="GD25" t="inlineStr"/>
+      <c r="GE25" t="inlineStr"/>
+      <c r="GF25" t="inlineStr"/>
+      <c r="GG25" t="inlineStr"/>
+      <c r="GH25" t="inlineStr"/>
+      <c r="GI25" t="inlineStr"/>
+      <c r="GJ25" t="inlineStr"/>
+      <c r="GK25" t="inlineStr"/>
+      <c r="GL25" t="inlineStr"/>
+      <c r="GM25" t="inlineStr"/>
+      <c r="GN25" t="inlineStr"/>
+      <c r="GO25" t="inlineStr"/>
+      <c r="GP25" t="inlineStr"/>
+      <c r="GQ25" t="inlineStr"/>
+      <c r="GR25" t="inlineStr"/>
+      <c r="GS25" t="inlineStr"/>
+      <c r="GT25" t="inlineStr"/>
+      <c r="GU25" t="inlineStr"/>
+      <c r="GV25" t="inlineStr"/>
+      <c r="GW25" t="inlineStr"/>
+      <c r="GX25" t="inlineStr"/>
+      <c r="GY25" t="inlineStr"/>
+      <c r="GZ25" t="inlineStr"/>
+      <c r="HA25" t="inlineStr"/>
+      <c r="HB25" t="inlineStr"/>
+      <c r="HC25" t="inlineStr"/>
+      <c r="HD25" t="inlineStr"/>
+      <c r="HE25" t="inlineStr"/>
+      <c r="HF25" t="inlineStr"/>
+      <c r="HG25" t="inlineStr"/>
+      <c r="HH25" t="inlineStr"/>
+      <c r="HI25" t="inlineStr"/>
+      <c r="HJ25" t="inlineStr"/>
+      <c r="HK25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -7643,6 +9298,55 @@
       <c r="FL26" t="inlineStr"/>
       <c r="FM26" t="inlineStr"/>
       <c r="FN26" t="inlineStr"/>
+      <c r="FO26" t="inlineStr"/>
+      <c r="FP26" t="inlineStr"/>
+      <c r="FQ26" t="inlineStr"/>
+      <c r="FR26" t="inlineStr"/>
+      <c r="FS26" t="inlineStr"/>
+      <c r="FT26" t="inlineStr"/>
+      <c r="FU26" t="inlineStr"/>
+      <c r="FV26" t="inlineStr"/>
+      <c r="FW26" t="inlineStr"/>
+      <c r="FX26" t="inlineStr"/>
+      <c r="FY26" t="inlineStr"/>
+      <c r="FZ26" t="inlineStr"/>
+      <c r="GA26" t="inlineStr"/>
+      <c r="GB26" t="inlineStr"/>
+      <c r="GC26" t="inlineStr"/>
+      <c r="GD26" t="inlineStr"/>
+      <c r="GE26" t="inlineStr"/>
+      <c r="GF26" t="inlineStr"/>
+      <c r="GG26" t="inlineStr"/>
+      <c r="GH26" t="inlineStr"/>
+      <c r="GI26" t="inlineStr"/>
+      <c r="GJ26" t="inlineStr"/>
+      <c r="GK26" t="inlineStr"/>
+      <c r="GL26" t="inlineStr"/>
+      <c r="GM26" t="inlineStr"/>
+      <c r="GN26" t="inlineStr"/>
+      <c r="GO26" t="inlineStr"/>
+      <c r="GP26" t="inlineStr"/>
+      <c r="GQ26" t="inlineStr"/>
+      <c r="GR26" t="inlineStr"/>
+      <c r="GS26" t="inlineStr"/>
+      <c r="GT26" t="inlineStr"/>
+      <c r="GU26" t="inlineStr"/>
+      <c r="GV26" t="inlineStr"/>
+      <c r="GW26" t="inlineStr"/>
+      <c r="GX26" t="inlineStr"/>
+      <c r="GY26" t="inlineStr"/>
+      <c r="GZ26" t="inlineStr"/>
+      <c r="HA26" t="inlineStr"/>
+      <c r="HB26" t="inlineStr"/>
+      <c r="HC26" t="inlineStr"/>
+      <c r="HD26" t="inlineStr"/>
+      <c r="HE26" t="inlineStr"/>
+      <c r="HF26" t="inlineStr"/>
+      <c r="HG26" t="inlineStr"/>
+      <c r="HH26" t="inlineStr"/>
+      <c r="HI26" t="inlineStr"/>
+      <c r="HJ26" t="inlineStr"/>
+      <c r="HK26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -7691,198 +9395,190 @@
       </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" t="n">
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="n">
         <v>1</v>
       </c>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr">
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="inlineStr">
         <is>
           <t>Anaemic</t>
         </is>
       </c>
-      <c r="R27" t="inlineStr"/>
-      <c r="S27" t="inlineStr"/>
       <c r="T27" t="inlineStr"/>
-      <c r="U27" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="U27" t="inlineStr"/>
       <c r="V27" t="inlineStr"/>
-      <c r="W27" t="inlineStr"/>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="X27" t="inlineStr"/>
-      <c r="Y27" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="Y27" t="inlineStr"/>
       <c r="Z27" t="inlineStr"/>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>Vegetarian</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr"/>
       <c r="AC27" t="inlineStr">
         <is>
+          <t>Vegetarian</t>
+        </is>
+      </c>
+      <c r="AD27" t="inlineStr"/>
+      <c r="AE27" t="inlineStr">
+        <is>
           <t>2022-11-19</t>
         </is>
       </c>
-      <c r="AD27" t="inlineStr"/>
-      <c r="AE27" t="n">
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="n">
         <v>7</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
-      <c r="AG27" t="inlineStr"/>
       <c r="AH27" t="inlineStr"/>
-      <c r="AI27" t="n">
+      <c r="AI27" t="inlineStr"/>
+      <c r="AJ27" t="inlineStr"/>
+      <c r="AK27" t="n">
         <v>12</v>
       </c>
-      <c r="AJ27" t="inlineStr"/>
-      <c r="AK27" t="inlineStr"/>
-      <c r="AL27" t="inlineStr">
+      <c r="AL27" t="inlineStr"/>
+      <c r="AM27" t="inlineStr"/>
+      <c r="AN27" t="inlineStr">
         <is>
           <t>Nuclear</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
+      <c r="AO27" t="inlineStr">
         <is>
           <t>Daily</t>
         </is>
       </c>
-      <c r="AN27" t="inlineStr">
+      <c r="AP27" t="inlineStr">
         <is>
           <t>Daily</t>
         </is>
       </c>
-      <c r="AO27" t="inlineStr">
+      <c r="AQ27" t="inlineStr">
         <is>
           <t>Daily</t>
         </is>
       </c>
-      <c r="AP27" t="inlineStr">
+      <c r="AR27" t="inlineStr">
         <is>
           <t>Daily</t>
         </is>
       </c>
-      <c r="AQ27" t="inlineStr">
+      <c r="AS27" t="inlineStr">
         <is>
           <t>Daily</t>
         </is>
       </c>
-      <c r="AR27" t="inlineStr">
+      <c r="AT27" t="inlineStr">
         <is>
           <t>Daily</t>
         </is>
       </c>
-      <c r="AS27" t="inlineStr"/>
-      <c r="AT27" t="inlineStr"/>
       <c r="AU27" t="inlineStr"/>
       <c r="AV27" t="inlineStr"/>
-      <c r="AW27" t="inlineStr">
-        <is>
-          <t>Enter valid Weight + Horiba Hb</t>
-        </is>
-      </c>
+      <c r="AW27" t="inlineStr"/>
       <c r="AX27" t="inlineStr"/>
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
+          <t>Enter valid Weight + Horiba Hb</t>
+        </is>
+      </c>
+      <c r="BA27" t="inlineStr"/>
+      <c r="BB27" t="inlineStr"/>
+      <c r="BC27" t="inlineStr">
+        <is>
           <t>Jahnavi</t>
         </is>
       </c>
-      <c r="BA27" t="inlineStr"/>
-      <c r="BB27" t="inlineStr">
-        <is>
-          <t>Jahnavi</t>
-        </is>
-      </c>
-      <c r="BC27" t="inlineStr"/>
       <c r="BD27" t="inlineStr"/>
       <c r="BE27" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Jahnavi</t>
         </is>
       </c>
       <c r="BF27" t="inlineStr"/>
       <c r="BG27" t="inlineStr"/>
-      <c r="BH27" t="n">
+      <c r="BH27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BI27" t="inlineStr"/>
+      <c r="BJ27" t="inlineStr"/>
+      <c r="BK27" t="n">
         <v>1</v>
       </c>
-      <c r="BI27" t="inlineStr">
+      <c r="BL27" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="BJ27" t="inlineStr">
+      <c r="BM27" t="inlineStr">
         <is>
           <t>Very easy</t>
         </is>
       </c>
-      <c r="BK27" t="inlineStr"/>
-      <c r="BL27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP27" t="n">
-        <v>0</v>
-      </c>
+      <c r="BN27" t="inlineStr"/>
+      <c r="BO27" t="inlineStr"/>
+      <c r="BP27" t="inlineStr"/>
       <c r="BQ27" t="n">
         <v>0</v>
       </c>
-      <c r="BR27" t="inlineStr"/>
-      <c r="BS27" t="inlineStr">
+      <c r="BR27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW27" t="inlineStr"/>
+      <c r="BX27" t="inlineStr">
         <is>
           <t>Daily</t>
-        </is>
-      </c>
-      <c r="BT27" t="inlineStr">
-        <is>
-          <t>Highly portable</t>
-        </is>
-      </c>
-      <c r="BU27" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="BV27" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="BW27" t="inlineStr">
-        <is>
-          <t>Always</t>
-        </is>
-      </c>
-      <c r="BX27" t="inlineStr">
-        <is>
-          <t>Very safe</t>
         </is>
       </c>
       <c r="BY27" t="inlineStr"/>
       <c r="BZ27" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="CA27" t="inlineStr"/>
-      <c r="CB27" t="inlineStr"/>
-      <c r="CC27" t="inlineStr"/>
+          <t>Highly portable</t>
+        </is>
+      </c>
+      <c r="CA27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CB27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CC27" t="inlineStr">
+        <is>
+          <t>Always</t>
+        </is>
+      </c>
       <c r="CD27" t="inlineStr">
         <is>
-          <t>Urban</t>
+          <t>Very safe</t>
         </is>
       </c>
       <c r="CE27" t="inlineStr"/>
@@ -7893,252 +9589,309 @@
       </c>
       <c r="CG27" t="inlineStr"/>
       <c r="CH27" t="inlineStr"/>
-      <c r="CI27" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
+      <c r="CI27" t="inlineStr"/>
       <c r="CJ27" t="inlineStr">
         <is>
-          <t>Very easy</t>
+          <t>Urban</t>
         </is>
       </c>
       <c r="CK27" t="inlineStr"/>
-      <c r="CL27" t="n">
-        <v>1</v>
-      </c>
-      <c r="CM27" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN27" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO27" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP27" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ27" t="n">
-        <v>0</v>
-      </c>
-      <c r="CR27" t="n">
-        <v>0</v>
-      </c>
-      <c r="CS27" t="inlineStr">
-        <is>
-          <t>Daily</t>
-        </is>
-      </c>
-      <c r="CT27" t="inlineStr">
-        <is>
-          <t>Highly portable</t>
-        </is>
-      </c>
-      <c r="CU27" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="CL27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CM27" t="inlineStr"/>
+      <c r="CN27" t="inlineStr"/>
+      <c r="CO27" t="inlineStr"/>
+      <c r="CP27" t="inlineStr"/>
+      <c r="CQ27" t="inlineStr"/>
+      <c r="CR27" t="inlineStr"/>
+      <c r="CS27" t="inlineStr"/>
+      <c r="CT27" t="inlineStr"/>
+      <c r="CU27" t="inlineStr"/>
       <c r="CV27" t="inlineStr"/>
       <c r="CW27" t="inlineStr"/>
       <c r="CX27" t="inlineStr"/>
       <c r="CY27" t="inlineStr"/>
-      <c r="CZ27" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="DA27" t="inlineStr">
-        <is>
-          <t>Always</t>
-        </is>
-      </c>
-      <c r="DB27" t="inlineStr">
-        <is>
-          <t>Very safe</t>
-        </is>
-      </c>
+      <c r="CZ27" t="inlineStr"/>
+      <c r="DA27" t="inlineStr"/>
+      <c r="DB27" t="inlineStr"/>
       <c r="DC27" t="inlineStr"/>
-      <c r="DD27" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="DD27" t="inlineStr"/>
       <c r="DE27" t="inlineStr"/>
-      <c r="DF27" t="inlineStr">
-        <is>
-          <t>Masimo Rad-67</t>
-        </is>
-      </c>
+      <c r="DF27" t="inlineStr"/>
       <c r="DG27" t="inlineStr"/>
       <c r="DH27" t="inlineStr"/>
-      <c r="DI27" t="n">
-        <v>10</v>
-      </c>
+      <c r="DI27" t="inlineStr"/>
       <c r="DJ27" t="inlineStr"/>
       <c r="DK27" t="inlineStr"/>
-      <c r="DL27" t="n">
-        <v>1</v>
-      </c>
-      <c r="DM27" t="n">
-        <v>1</v>
-      </c>
-      <c r="DN27" t="n">
-        <v>1</v>
-      </c>
-      <c r="DO27" t="n">
-        <v>1</v>
+      <c r="DL27" t="inlineStr"/>
+      <c r="DM27" t="inlineStr"/>
+      <c r="DN27" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="DO27" t="inlineStr">
+        <is>
+          <t>Very easy</t>
+        </is>
       </c>
       <c r="DP27" t="inlineStr"/>
       <c r="DQ27" t="n">
         <v>1</v>
       </c>
-      <c r="DR27" t="inlineStr">
-        <is>
-          <t>vibha</t>
-        </is>
+      <c r="DR27" t="n">
+        <v>0</v>
       </c>
       <c r="DS27" t="n">
-        <v>1</v>
-      </c>
-      <c r="DT27" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="DU27" t="inlineStr">
-        <is>
-          <t>Very easy</t>
-        </is>
-      </c>
-      <c r="DV27" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="DT27" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU27" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV27" t="n">
+        <v>0</v>
+      </c>
       <c r="DW27" t="n">
-        <v>1</v>
-      </c>
-      <c r="DX27" t="n">
-        <v>0</v>
-      </c>
-      <c r="DY27" t="n">
-        <v>0</v>
-      </c>
-      <c r="DZ27" t="n">
-        <v>0</v>
-      </c>
-      <c r="EA27" t="n">
-        <v>0</v>
-      </c>
-      <c r="EB27" t="n">
-        <v>0</v>
-      </c>
-      <c r="EC27" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="DX27" t="inlineStr">
+        <is>
+          <t>Daily</t>
+        </is>
+      </c>
+      <c r="DY27" t="inlineStr">
+        <is>
+          <t>Highly portable</t>
+        </is>
+      </c>
+      <c r="DZ27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="EA27" t="inlineStr"/>
+      <c r="EB27" t="inlineStr"/>
+      <c r="EC27" t="inlineStr"/>
       <c r="ED27" t="inlineStr"/>
       <c r="EE27" t="inlineStr">
         <is>
-          <t>Daily</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="EF27" t="inlineStr">
         <is>
-          <t>Highly portable</t>
+          <t>Always</t>
         </is>
       </c>
       <c r="EG27" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="EH27" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>Very safe</t>
+        </is>
+      </c>
+      <c r="EH27" t="inlineStr"/>
       <c r="EI27" t="inlineStr">
         <is>
-          <t>Always</t>
-        </is>
-      </c>
-      <c r="EJ27" t="inlineStr">
-        <is>
-          <t>Very safe</t>
-        </is>
-      </c>
-      <c r="EK27" t="inlineStr"/>
-      <c r="EL27" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="EJ27" t="inlineStr"/>
+      <c r="EK27" t="inlineStr">
+        <is>
+          <t>Masimo Rad-67</t>
+        </is>
+      </c>
+      <c r="EL27" t="inlineStr"/>
       <c r="EM27" t="inlineStr"/>
-      <c r="EN27" t="inlineStr"/>
-      <c r="EO27" t="inlineStr">
-        <is>
-          <t>Non-invasive</t>
-        </is>
-      </c>
+      <c r="EN27" t="n">
+        <v>10</v>
+      </c>
+      <c r="EO27" t="inlineStr"/>
       <c r="EP27" t="inlineStr"/>
-      <c r="EQ27" t="inlineStr"/>
-      <c r="ER27" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="ES27" t="inlineStr">
-        <is>
-          <t>VV191122FDOH</t>
-        </is>
-      </c>
-      <c r="ET27" t="inlineStr">
-        <is>
-          <t>VV191122FDOH</t>
-        </is>
-      </c>
-      <c r="EU27" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="EQ27" t="n">
+        <v>1</v>
+      </c>
+      <c r="ER27" t="n">
+        <v>1</v>
+      </c>
+      <c r="ES27" t="n">
+        <v>1</v>
+      </c>
+      <c r="ET27" t="inlineStr"/>
+      <c r="EU27" t="inlineStr"/>
       <c r="EV27" t="inlineStr"/>
-      <c r="EW27" t="inlineStr">
-        <is>
-          <t>PHC</t>
-        </is>
-      </c>
+      <c r="EW27" t="inlineStr"/>
       <c r="EX27" t="inlineStr"/>
-      <c r="EY27" t="inlineStr">
-        <is>
-          <t>Hindu</t>
-        </is>
-      </c>
+      <c r="EY27" t="inlineStr"/>
       <c r="EZ27" t="inlineStr"/>
       <c r="FA27" t="inlineStr"/>
-      <c r="FB27" t="inlineStr">
-        <is>
-          <t>donbosco</t>
-        </is>
-      </c>
-      <c r="FC27" t="inlineStr"/>
+      <c r="FB27" t="inlineStr"/>
+      <c r="FC27" t="n">
+        <v>1</v>
+      </c>
       <c r="FD27" t="inlineStr"/>
-      <c r="FE27" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
-      </c>
-      <c r="FF27" t="inlineStr"/>
-      <c r="FG27" t="inlineStr">
-        <is>
-          <t>SC</t>
-        </is>
-      </c>
-      <c r="FH27" t="inlineStr"/>
-      <c r="FI27" t="inlineStr"/>
+      <c r="FE27" t="n">
+        <v>1</v>
+      </c>
+      <c r="FF27" t="inlineStr">
+        <is>
+          <t>vibha</t>
+        </is>
+      </c>
+      <c r="FG27" t="n">
+        <v>1</v>
+      </c>
+      <c r="FH27" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="FI27" t="inlineStr">
+        <is>
+          <t>Very easy</t>
+        </is>
+      </c>
       <c r="FJ27" t="inlineStr"/>
       <c r="FK27" t="inlineStr"/>
       <c r="FL27" t="inlineStr"/>
-      <c r="FM27" t="inlineStr"/>
-      <c r="FN27" t="inlineStr">
+      <c r="FM27" t="n">
+        <v>1</v>
+      </c>
+      <c r="FN27" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO27" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP27" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="FR27" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS27" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT27" t="inlineStr"/>
+      <c r="FU27" t="inlineStr">
+        <is>
+          <t>Daily</t>
+        </is>
+      </c>
+      <c r="FV27" t="inlineStr"/>
+      <c r="FW27" t="inlineStr">
+        <is>
+          <t>Highly portable</t>
+        </is>
+      </c>
+      <c r="FX27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="FY27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="FZ27" t="inlineStr">
+        <is>
+          <t>Always</t>
+        </is>
+      </c>
+      <c r="GA27" t="inlineStr">
+        <is>
+          <t>Very safe</t>
+        </is>
+      </c>
+      <c r="GB27" t="inlineStr"/>
+      <c r="GC27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="GD27" t="inlineStr"/>
+      <c r="GE27" t="inlineStr"/>
+      <c r="GF27" t="inlineStr"/>
+      <c r="GG27" t="inlineStr"/>
+      <c r="GH27" t="inlineStr">
+        <is>
+          <t>Non-invasive</t>
+        </is>
+      </c>
+      <c r="GI27" t="inlineStr"/>
+      <c r="GJ27" t="inlineStr"/>
+      <c r="GK27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="GL27" t="inlineStr">
+        <is>
+          <t>VV191122FDOH</t>
+        </is>
+      </c>
+      <c r="GM27" t="inlineStr">
+        <is>
+          <t>VV191122FDOH</t>
+        </is>
+      </c>
+      <c r="GN27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="GO27" t="inlineStr"/>
+      <c r="GP27" t="inlineStr">
+        <is>
+          <t>PHC</t>
+        </is>
+      </c>
+      <c r="GQ27" t="inlineStr"/>
+      <c r="GR27" t="inlineStr"/>
+      <c r="GS27" t="inlineStr">
+        <is>
+          <t>Hindu</t>
+        </is>
+      </c>
+      <c r="GT27" t="inlineStr"/>
+      <c r="GU27" t="inlineStr"/>
+      <c r="GV27" t="inlineStr"/>
+      <c r="GW27" t="inlineStr">
+        <is>
+          <t>donbosco</t>
+        </is>
+      </c>
+      <c r="GX27" t="inlineStr"/>
+      <c r="GY27" t="inlineStr"/>
+      <c r="GZ27" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="HA27" t="inlineStr"/>
+      <c r="HB27" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="HC27" t="inlineStr"/>
+      <c r="HD27" t="inlineStr"/>
+      <c r="HE27" t="inlineStr"/>
+      <c r="HF27" t="inlineStr"/>
+      <c r="HG27" t="inlineStr"/>
+      <c r="HH27" t="inlineStr"/>
+      <c r="HI27" t="inlineStr"/>
+      <c r="HJ27" t="inlineStr"/>
+      <c r="HK27" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -8191,198 +9944,190 @@
       </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" t="n">
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="n">
         <v>1</v>
       </c>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr">
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="inlineStr">
         <is>
           <t>Anaemic</t>
         </is>
       </c>
-      <c r="R28" t="inlineStr"/>
-      <c r="S28" t="inlineStr"/>
       <c r="T28" t="inlineStr"/>
-      <c r="U28" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="U28" t="inlineStr"/>
       <c r="V28" t="inlineStr"/>
-      <c r="W28" t="inlineStr"/>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="X28" t="inlineStr"/>
-      <c r="Y28" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="Y28" t="inlineStr"/>
       <c r="Z28" t="inlineStr"/>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>Vegetarian</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr"/>
       <c r="AC28" t="inlineStr">
         <is>
+          <t>Vegetarian</t>
+        </is>
+      </c>
+      <c r="AD28" t="inlineStr"/>
+      <c r="AE28" t="inlineStr">
+        <is>
           <t>2022-11-18</t>
         </is>
       </c>
-      <c r="AD28" t="inlineStr"/>
-      <c r="AE28" t="n">
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="n">
         <v>7</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
-      <c r="AG28" t="inlineStr"/>
       <c r="AH28" t="inlineStr"/>
-      <c r="AI28" t="n">
+      <c r="AI28" t="inlineStr"/>
+      <c r="AJ28" t="inlineStr"/>
+      <c r="AK28" t="n">
         <v>12</v>
       </c>
-      <c r="AJ28" t="inlineStr"/>
-      <c r="AK28" t="inlineStr"/>
-      <c r="AL28" t="inlineStr">
+      <c r="AL28" t="inlineStr"/>
+      <c r="AM28" t="inlineStr"/>
+      <c r="AN28" t="inlineStr">
         <is>
           <t>Nuclear</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
+      <c r="AO28" t="inlineStr">
         <is>
           <t>Daily</t>
         </is>
       </c>
-      <c r="AN28" t="inlineStr">
+      <c r="AP28" t="inlineStr">
         <is>
           <t>Daily</t>
         </is>
       </c>
-      <c r="AO28" t="inlineStr">
+      <c r="AQ28" t="inlineStr">
         <is>
           <t>Daily</t>
         </is>
       </c>
-      <c r="AP28" t="inlineStr">
+      <c r="AR28" t="inlineStr">
         <is>
           <t>Daily</t>
         </is>
       </c>
-      <c r="AQ28" t="inlineStr">
+      <c r="AS28" t="inlineStr">
         <is>
           <t>Daily</t>
         </is>
       </c>
-      <c r="AR28" t="inlineStr">
+      <c r="AT28" t="inlineStr">
         <is>
           <t>Daily</t>
         </is>
       </c>
-      <c r="AS28" t="inlineStr"/>
-      <c r="AT28" t="inlineStr"/>
       <c r="AU28" t="inlineStr"/>
       <c r="AV28" t="inlineStr"/>
-      <c r="AW28" t="inlineStr">
-        <is>
-          <t>Enter valid Weight + Horiba Hb</t>
-        </is>
-      </c>
+      <c r="AW28" t="inlineStr"/>
       <c r="AX28" t="inlineStr"/>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
+          <t>Enter valid Weight + Horiba Hb</t>
+        </is>
+      </c>
+      <c r="BA28" t="inlineStr"/>
+      <c r="BB28" t="inlineStr"/>
+      <c r="BC28" t="inlineStr">
+        <is>
           <t>Jahnavi</t>
         </is>
       </c>
-      <c r="BA28" t="inlineStr"/>
-      <c r="BB28" t="inlineStr">
-        <is>
-          <t>Jahnavi</t>
-        </is>
-      </c>
-      <c r="BC28" t="inlineStr"/>
       <c r="BD28" t="inlineStr"/>
       <c r="BE28" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Jahnavi</t>
         </is>
       </c>
       <c r="BF28" t="inlineStr"/>
       <c r="BG28" t="inlineStr"/>
-      <c r="BH28" t="n">
+      <c r="BH28" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="BI28" t="inlineStr"/>
+      <c r="BJ28" t="inlineStr"/>
+      <c r="BK28" t="n">
         <v>1</v>
       </c>
-      <c r="BI28" t="inlineStr">
+      <c r="BL28" t="inlineStr">
         <is>
           <t>Easy</t>
         </is>
       </c>
-      <c r="BJ28" t="inlineStr">
+      <c r="BM28" t="inlineStr">
         <is>
           <t>Very easy</t>
         </is>
       </c>
-      <c r="BK28" t="inlineStr"/>
-      <c r="BL28" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM28" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN28" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO28" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP28" t="n">
-        <v>0</v>
-      </c>
+      <c r="BN28" t="inlineStr"/>
+      <c r="BO28" t="inlineStr"/>
+      <c r="BP28" t="inlineStr"/>
       <c r="BQ28" t="n">
         <v>0</v>
       </c>
-      <c r="BR28" t="inlineStr"/>
-      <c r="BS28" t="inlineStr">
+      <c r="BR28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW28" t="inlineStr"/>
+      <c r="BX28" t="inlineStr">
         <is>
           <t>Daily</t>
-        </is>
-      </c>
-      <c r="BT28" t="inlineStr">
-        <is>
-          <t>Highly portable</t>
-        </is>
-      </c>
-      <c r="BU28" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="BV28" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="BW28" t="inlineStr">
-        <is>
-          <t>Always</t>
-        </is>
-      </c>
-      <c r="BX28" t="inlineStr">
-        <is>
-          <t>Very safe</t>
         </is>
       </c>
       <c r="BY28" t="inlineStr"/>
       <c r="BZ28" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="CA28" t="inlineStr"/>
-      <c r="CB28" t="inlineStr"/>
-      <c r="CC28" t="inlineStr"/>
+          <t>Highly portable</t>
+        </is>
+      </c>
+      <c r="CA28" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CB28" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CC28" t="inlineStr">
+        <is>
+          <t>Always</t>
+        </is>
+      </c>
       <c r="CD28" t="inlineStr">
         <is>
-          <t>Urban</t>
+          <t>Very safe</t>
         </is>
       </c>
       <c r="CE28" t="inlineStr"/>
@@ -8393,252 +10138,309 @@
       </c>
       <c r="CG28" t="inlineStr"/>
       <c r="CH28" t="inlineStr"/>
-      <c r="CI28" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
+      <c r="CI28" t="inlineStr"/>
       <c r="CJ28" t="inlineStr">
         <is>
-          <t>Very easy</t>
+          <t>Urban</t>
         </is>
       </c>
       <c r="CK28" t="inlineStr"/>
-      <c r="CL28" t="n">
-        <v>1</v>
-      </c>
-      <c r="CM28" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN28" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO28" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP28" t="n">
-        <v>2</v>
-      </c>
-      <c r="CQ28" t="n">
-        <v>2</v>
-      </c>
-      <c r="CR28" t="n">
-        <v>4</v>
-      </c>
-      <c r="CS28" t="inlineStr">
-        <is>
-          <t>Daily</t>
-        </is>
-      </c>
-      <c r="CT28" t="inlineStr">
-        <is>
-          <t>Highly portable</t>
-        </is>
-      </c>
-      <c r="CU28" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="CL28" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="CM28" t="inlineStr"/>
+      <c r="CN28" t="inlineStr"/>
+      <c r="CO28" t="inlineStr"/>
+      <c r="CP28" t="inlineStr"/>
+      <c r="CQ28" t="inlineStr"/>
+      <c r="CR28" t="inlineStr"/>
+      <c r="CS28" t="inlineStr"/>
+      <c r="CT28" t="inlineStr"/>
+      <c r="CU28" t="inlineStr"/>
       <c r="CV28" t="inlineStr"/>
       <c r="CW28" t="inlineStr"/>
       <c r="CX28" t="inlineStr"/>
       <c r="CY28" t="inlineStr"/>
-      <c r="CZ28" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="DA28" t="inlineStr">
-        <is>
-          <t>Always</t>
-        </is>
-      </c>
-      <c r="DB28" t="inlineStr">
-        <is>
-          <t>Very safe</t>
-        </is>
-      </c>
+      <c r="CZ28" t="inlineStr"/>
+      <c r="DA28" t="inlineStr"/>
+      <c r="DB28" t="inlineStr"/>
       <c r="DC28" t="inlineStr"/>
-      <c r="DD28" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="DD28" t="inlineStr"/>
       <c r="DE28" t="inlineStr"/>
-      <c r="DF28" t="inlineStr">
-        <is>
-          <t>Masimo Rad-67</t>
-        </is>
-      </c>
+      <c r="DF28" t="inlineStr"/>
       <c r="DG28" t="inlineStr"/>
       <c r="DH28" t="inlineStr"/>
-      <c r="DI28" t="n">
-        <v>10</v>
-      </c>
+      <c r="DI28" t="inlineStr"/>
       <c r="DJ28" t="inlineStr"/>
       <c r="DK28" t="inlineStr"/>
-      <c r="DL28" t="n">
-        <v>1</v>
-      </c>
-      <c r="DM28" t="n">
-        <v>1</v>
-      </c>
-      <c r="DN28" t="n">
-        <v>1</v>
-      </c>
-      <c r="DO28" t="n">
-        <v>1</v>
+      <c r="DL28" t="inlineStr"/>
+      <c r="DM28" t="inlineStr"/>
+      <c r="DN28" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="DO28" t="inlineStr">
+        <is>
+          <t>Very easy</t>
+        </is>
       </c>
       <c r="DP28" t="inlineStr"/>
       <c r="DQ28" t="n">
         <v>1</v>
       </c>
-      <c r="DR28" t="inlineStr">
-        <is>
-          <t>pallavi</t>
-        </is>
+      <c r="DR28" t="n">
+        <v>0</v>
       </c>
       <c r="DS28" t="n">
-        <v>1</v>
-      </c>
-      <c r="DT28" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
-      <c r="DU28" t="inlineStr">
-        <is>
-          <t>Very easy</t>
-        </is>
-      </c>
-      <c r="DV28" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="DT28" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU28" t="n">
+        <v>2</v>
+      </c>
+      <c r="DV28" t="n">
+        <v>2</v>
+      </c>
       <c r="DW28" t="n">
-        <v>1</v>
-      </c>
-      <c r="DX28" t="n">
-        <v>0</v>
-      </c>
-      <c r="DY28" t="n">
-        <v>0</v>
-      </c>
-      <c r="DZ28" t="n">
-        <v>0</v>
-      </c>
-      <c r="EA28" t="n">
-        <v>0</v>
-      </c>
-      <c r="EB28" t="n">
-        <v>0</v>
-      </c>
-      <c r="EC28" t="n">
-        <v>0</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="DX28" t="inlineStr">
+        <is>
+          <t>Daily</t>
+        </is>
+      </c>
+      <c r="DY28" t="inlineStr">
+        <is>
+          <t>Highly portable</t>
+        </is>
+      </c>
+      <c r="DZ28" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="EA28" t="inlineStr"/>
+      <c r="EB28" t="inlineStr"/>
+      <c r="EC28" t="inlineStr"/>
       <c r="ED28" t="inlineStr"/>
       <c r="EE28" t="inlineStr">
         <is>
-          <t>Daily</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="EF28" t="inlineStr">
         <is>
-          <t>Highly portable</t>
+          <t>Always</t>
         </is>
       </c>
       <c r="EG28" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="EH28" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>Very safe</t>
+        </is>
+      </c>
+      <c r="EH28" t="inlineStr"/>
       <c r="EI28" t="inlineStr">
         <is>
-          <t>Always</t>
-        </is>
-      </c>
-      <c r="EJ28" t="inlineStr">
-        <is>
-          <t>Very safe</t>
-        </is>
-      </c>
-      <c r="EK28" t="inlineStr"/>
-      <c r="EL28" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="EJ28" t="inlineStr"/>
+      <c r="EK28" t="inlineStr">
+        <is>
+          <t>Masimo Rad-67</t>
+        </is>
+      </c>
+      <c r="EL28" t="inlineStr"/>
       <c r="EM28" t="inlineStr"/>
-      <c r="EN28" t="inlineStr"/>
-      <c r="EO28" t="inlineStr">
-        <is>
-          <t>Non-invasive</t>
-        </is>
-      </c>
+      <c r="EN28" t="n">
+        <v>10</v>
+      </c>
+      <c r="EO28" t="inlineStr"/>
       <c r="EP28" t="inlineStr"/>
-      <c r="EQ28" t="inlineStr"/>
-      <c r="ER28" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="ES28" t="inlineStr">
-        <is>
-          <t>PV181122FDOH</t>
-        </is>
-      </c>
-      <c r="ET28" t="inlineStr">
-        <is>
-          <t>PV181122FDOH</t>
-        </is>
-      </c>
-      <c r="EU28" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="EQ28" t="n">
+        <v>1</v>
+      </c>
+      <c r="ER28" t="n">
+        <v>1</v>
+      </c>
+      <c r="ES28" t="n">
+        <v>1</v>
+      </c>
+      <c r="ET28" t="inlineStr"/>
+      <c r="EU28" t="inlineStr"/>
       <c r="EV28" t="inlineStr"/>
-      <c r="EW28" t="inlineStr">
-        <is>
-          <t>PHC</t>
-        </is>
-      </c>
+      <c r="EW28" t="inlineStr"/>
       <c r="EX28" t="inlineStr"/>
-      <c r="EY28" t="inlineStr">
-        <is>
-          <t>Hindu</t>
-        </is>
-      </c>
+      <c r="EY28" t="inlineStr"/>
       <c r="EZ28" t="inlineStr"/>
       <c r="FA28" t="inlineStr"/>
-      <c r="FB28" t="inlineStr">
-        <is>
-          <t>donbosco</t>
-        </is>
-      </c>
-      <c r="FC28" t="inlineStr"/>
+      <c r="FB28" t="inlineStr"/>
+      <c r="FC28" t="n">
+        <v>1</v>
+      </c>
       <c r="FD28" t="inlineStr"/>
-      <c r="FE28" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
-      </c>
-      <c r="FF28" t="inlineStr"/>
-      <c r="FG28" t="inlineStr">
-        <is>
-          <t>SC</t>
-        </is>
-      </c>
-      <c r="FH28" t="inlineStr"/>
-      <c r="FI28" t="inlineStr"/>
+      <c r="FE28" t="n">
+        <v>1</v>
+      </c>
+      <c r="FF28" t="inlineStr">
+        <is>
+          <t>pallavi</t>
+        </is>
+      </c>
+      <c r="FG28" t="n">
+        <v>1</v>
+      </c>
+      <c r="FH28" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="FI28" t="inlineStr">
+        <is>
+          <t>Very easy</t>
+        </is>
+      </c>
       <c r="FJ28" t="inlineStr"/>
       <c r="FK28" t="inlineStr"/>
       <c r="FL28" t="inlineStr"/>
-      <c r="FM28" t="inlineStr"/>
-      <c r="FN28" t="inlineStr">
+      <c r="FM28" t="n">
+        <v>1</v>
+      </c>
+      <c r="FN28" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO28" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP28" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="FR28" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS28" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT28" t="inlineStr"/>
+      <c r="FU28" t="inlineStr">
+        <is>
+          <t>Daily</t>
+        </is>
+      </c>
+      <c r="FV28" t="inlineStr"/>
+      <c r="FW28" t="inlineStr">
+        <is>
+          <t>Highly portable</t>
+        </is>
+      </c>
+      <c r="FX28" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="FY28" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="FZ28" t="inlineStr">
+        <is>
+          <t>Always</t>
+        </is>
+      </c>
+      <c r="GA28" t="inlineStr">
+        <is>
+          <t>Very safe</t>
+        </is>
+      </c>
+      <c r="GB28" t="inlineStr"/>
+      <c r="GC28" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="GD28" t="inlineStr"/>
+      <c r="GE28" t="inlineStr"/>
+      <c r="GF28" t="inlineStr"/>
+      <c r="GG28" t="inlineStr"/>
+      <c r="GH28" t="inlineStr">
+        <is>
+          <t>Non-invasive</t>
+        </is>
+      </c>
+      <c r="GI28" t="inlineStr"/>
+      <c r="GJ28" t="inlineStr"/>
+      <c r="GK28" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="GL28" t="inlineStr">
+        <is>
+          <t>PV181122FDOH</t>
+        </is>
+      </c>
+      <c r="GM28" t="inlineStr">
+        <is>
+          <t>PV181122FDOH</t>
+        </is>
+      </c>
+      <c r="GN28" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="GO28" t="inlineStr"/>
+      <c r="GP28" t="inlineStr">
+        <is>
+          <t>PHC</t>
+        </is>
+      </c>
+      <c r="GQ28" t="inlineStr"/>
+      <c r="GR28" t="inlineStr"/>
+      <c r="GS28" t="inlineStr">
+        <is>
+          <t>Hindu</t>
+        </is>
+      </c>
+      <c r="GT28" t="inlineStr"/>
+      <c r="GU28" t="inlineStr"/>
+      <c r="GV28" t="inlineStr"/>
+      <c r="GW28" t="inlineStr">
+        <is>
+          <t>donbosco</t>
+        </is>
+      </c>
+      <c r="GX28" t="inlineStr"/>
+      <c r="GY28" t="inlineStr"/>
+      <c r="GZ28" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="HA28" t="inlineStr"/>
+      <c r="HB28" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="HC28" t="inlineStr"/>
+      <c r="HD28" t="inlineStr"/>
+      <c r="HE28" t="inlineStr"/>
+      <c r="HF28" t="inlineStr"/>
+      <c r="HG28" t="inlineStr"/>
+      <c r="HH28" t="inlineStr"/>
+      <c r="HI28" t="inlineStr"/>
+      <c r="HJ28" t="inlineStr"/>
+      <c r="HK28" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
